--- a/Main bearing/01. 정리/Python 자동화/Results/DLC별해석/DLC별해석_총괄.xlsx
+++ b/Main bearing/01. 정리/Python 자동화/Results/DLC별해석/DLC별해석_총괄.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="총괄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'총괄'!$A$2:$T$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'총괄'!$A$2:$Y$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +56,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,14 +126,20 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T117"/>
+  <dimension ref="A1:Y117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -511,18 +522,23 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DLC별 해석 총괄 (초안) — 1단계 스크리닝 기준. 수명·손상 절대값은 핀지지 해석 경로(절대편향 내포), 상대지표·최적조합 탐색용. 2단계 MASTA에서 대체 예정</t>
+          <t>DLC별 해석 총괄 — 손상·수명 절대값은 MASTA 실측만 입력(음영 행, 참값 dt=0.1 + 최적조합 병기). 스크리닝 절대값은 핀지지 절대편향 ≈3~5×로 미기재(부록 1). 본해석 DLC의 최적 (dt,k)·ε = 확정값·실측, 그 외 = 스크리닝 예측</t>
         </is>
       </c>
     </row>
@@ -574,55 +590,80 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>UW 30년손상(scr)</t>
+          <t>UW 30년손상(참값)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>DW 30년손상(scr)</t>
+          <t>DW 30년손상(참값)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>UW 수명(scr, yr)</t>
+          <t>UW 수명(참값,yr)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>DW 수명(scr, yr)</t>
+          <t>DW 수명(참값,yr)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sys 수명(scr, yr)</t>
+          <t>Sys 수명(참값,yr)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>UW 30년손상(조합)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>DW 30년손상(조합)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>UW 수명(조합,yr)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>DW 수명(조합,yr)</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Sys 수명(조합,yr)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t>최적 dt [s]</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>최적 k</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>ε_UW@best</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>ε_DW@best</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>ε_Sys@best</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -659,36 +700,55 @@
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0.6308283722698879</v>
+        <v>0.2065131375394038</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0.1385763738459647</v>
+        <v>0.01378655132720269</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>47.55651666720703</v>
+        <v>145.2692083295468</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>216.4871194663144</v>
+        <v>2176.033678618816</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>40.99579374493918</v>
-      </c>
-      <c r="O3" s="6" t="n">
+        <v>139.3873806961601</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>0.2114388937432393</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>0.01359335850519638</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>141.8849648183956</v>
+      </c>
+      <c r="R3" s="9" t="n">
+        <v>2206.960111331706</v>
+      </c>
+      <c r="S3" s="9" t="n">
+        <v>136.3687878298307</v>
+      </c>
+      <c r="T3" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="U3" s="11" t="n">
         <v>0.21</v>
       </c>
-      <c r="Q3" s="10" t="n">
-        <v>0.01928784964110193</v>
-      </c>
-      <c r="R3" s="11" t="n">
-        <v>-0.008822902599632929</v>
-      </c>
-      <c r="S3" s="10" t="n">
-        <v>0.01497068860807593</v>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="V3" s="12" t="n">
+        <v>0.02385202347185111</v>
+      </c>
+      <c r="W3" s="13" t="n">
+        <v>-0.01401313623843836</v>
+      </c>
+      <c r="X3" s="12" t="n">
+        <v>0.02213551146392945</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -721,36 +781,55 @@
         <v>0</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.6342152959023264</v>
+        <v>0.2075409684054229</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0.1391965203522656</v>
+        <v>0.0138560025432764</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>47.30254882502899</v>
+        <v>144.5497736205809</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>215.5226288996218</v>
+        <v>2165.126623375041</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>40.78243910769722</v>
-      </c>
-      <c r="O4" s="6" t="n">
+        <v>138.6966957266158</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>0.21135980631825</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>0.01375350142496479</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>141.9380558800674</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>2181.262725253748</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>136.3474271368931</v>
+      </c>
+      <c r="T4" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="U4" s="11" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q4" s="10" t="n">
-        <v>0.01777091990879345</v>
-      </c>
-      <c r="R4" s="11" t="n">
-        <v>-0.0003105333595700954</v>
-      </c>
-      <c r="S4" s="10" t="n">
-        <v>0.01499496830520023</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
+      <c r="V4" s="12" t="n">
+        <v>0.01840040519309527</v>
+      </c>
+      <c r="W4" s="13" t="n">
+        <v>-0.007397596672739204</v>
+      </c>
+      <c r="X4" s="12" t="n">
+        <v>0.01723001774990607</v>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -783,36 +862,55 @@
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.6448595149996262</v>
+        <v>0.2102987632369595</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.1449218612557485</v>
+        <v>0.0144875224747863</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>46.52176063497704</v>
+        <v>142.6541912954416</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>207.0081058858193</v>
+        <v>2070.747434712264</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>39.96203161050511</v>
-      </c>
-      <c r="O5" s="6" t="n">
+        <v>136.6796006036861</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0.2143238275092453</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>0.01441865791619258</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>139.9751037887091</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>2080.637475025266</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>134.2604240548632</v>
+      </c>
+      <c r="T5" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="U5" s="11" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q5" s="10" t="n">
-        <v>0.01762450581883018</v>
-      </c>
-      <c r="R5" s="11" t="n">
-        <v>-0.0001128645977083109</v>
-      </c>
-      <c r="S5" s="10" t="n">
-        <v>0.0148394187329982</v>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
+      <c r="V5" s="12" t="n">
+        <v>0.01913974295583665</v>
+      </c>
+      <c r="W5" s="13" t="n">
+        <v>-0.004753370268350765</v>
+      </c>
+      <c r="X5" s="12" t="n">
+        <v>0.0180185379709088</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -845,36 +943,55 @@
         <v>0</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.6565449059983807</v>
+        <v>0.2140211452242045</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.1471031509402844</v>
+        <v>0.01469518691451268</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>45.69375183009034</v>
+        <v>140.1730654630998</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>203.9385275450579</v>
+        <v>2041.484751063125</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>39.26937859207545</v>
-      </c>
-      <c r="O6" s="6" t="n">
+        <v>134.3232639466377</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>0.2178813326588059</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>0.01463728120360099</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>137.6896296433935</v>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>2049.560952113125</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>132.0768049017946</v>
+      </c>
+      <c r="T6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="U6" s="11" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q6" s="10" t="n">
-        <v>0.01727614919932803</v>
-      </c>
-      <c r="R6" s="10" t="n">
-        <v>0.001799293395624022</v>
-      </c>
-      <c r="S6" s="10" t="n">
-        <v>0.01485265889772251</v>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
+      <c r="V6" s="12" t="n">
+        <v>0.01803647686567422</v>
+      </c>
+      <c r="W6" s="13" t="n">
+        <v>-0.003940454194189091</v>
+      </c>
+      <c r="X6" s="12" t="n">
+        <v>0.01700873250616119</v>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -907,36 +1024,55 @@
         <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.6850382715150248</v>
+        <v>0.2213650086751907</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.1622046906812963</v>
+        <v>0.01636889162095858</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>43.79317367721989</v>
+        <v>135.5227738093831</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>184.9514947686977</v>
+        <v>1832.744738903902</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>37.30300584930868</v>
-      </c>
-      <c r="O7" s="6" t="n">
+        <v>129.3987585747278</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0.2256744790866576</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>0.01624787957034658</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>132.9348365903624</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>1846.39477847632</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>127.0972473036408</v>
+      </c>
+      <c r="T7" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="U7" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="10" t="n">
-        <v>0.01788803157895041</v>
-      </c>
-      <c r="R7" s="10" t="n">
-        <v>4.338501125512643e-05</v>
-      </c>
-      <c r="S7" s="10" t="n">
-        <v>0.0149444320597617</v>
-      </c>
-      <c r="T7" s="3" t="inlineStr"/>
+      <c r="V7" s="12" t="n">
+        <v>0.01946771279371551</v>
+      </c>
+      <c r="W7" s="13" t="n">
+        <v>-0.007392806636770888</v>
+      </c>
+      <c r="X7" s="12" t="n">
+        <v>0.01810827000516047</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -969,36 +1105,55 @@
         <v>0</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.6446300551504297</v>
+        <v>0.2102598937484908</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.1435963137348313</v>
+        <v>0.01429373786256376</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>46.53832032854759</v>
+        <v>142.680562922216</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>208.9190120534624</v>
+        <v>2098.821196278685</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>40.03155971090443</v>
-      </c>
-      <c r="O8" s="6" t="n">
+        <v>136.7896092938192</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.2147096438847703</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>0.01418783074780985</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>139.7235795151349</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>2114.488150673143</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>134.1282845086582</v>
+      </c>
+      <c r="T8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="U8" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q8" s="10" t="n">
-        <v>0.01832336163645869</v>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>-0.003745134673393862</v>
-      </c>
-      <c r="S8" s="10" t="n">
-        <v>0.01488780765130796</v>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+      <c r="V8" s="12" t="n">
+        <v>0.02116309514358572</v>
+      </c>
+      <c r="W8" s="13" t="n">
+        <v>-0.00740933657607401</v>
+      </c>
+      <c r="X8" s="12" t="n">
+        <v>0.01984163739147249</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1031,36 +1186,55 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.6443354133968328</v>
+        <v>0.1970016810560663</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.1377581122097342</v>
+        <v>0.01398654777746147</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>46.55960137569472</v>
+        <v>152.2829644862881</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>217.7730190896167</v>
+        <v>2144.918136864573</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>40.3019474105141</v>
-      </c>
-      <c r="O9" s="6" t="n">
+        <v>145.6953367242825</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>0.2028067332949413</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>0.01330532857445778</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>147.9240827589836</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>2254.735749825146</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>142.0460854559618</v>
+      </c>
+      <c r="T9" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="U9" s="11" t="n">
         <v>0.23</v>
       </c>
-      <c r="Q9" s="10" t="n">
-        <v>0.02144625713715997</v>
-      </c>
-      <c r="R9" s="11" t="n">
-        <v>-0.02258565557181324</v>
-      </c>
-      <c r="S9" s="10" t="n">
-        <v>0.01486248844697358</v>
-      </c>
-      <c r="T9" s="3" t="inlineStr"/>
+      <c r="V9" s="12" t="n">
+        <v>0.02946701879778812</v>
+      </c>
+      <c r="W9" s="13" t="n">
+        <v>-0.04870531412343516</v>
+      </c>
+      <c r="X9" s="12" t="n">
+        <v>0.02569061482128698</v>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1093,36 +1267,55 @@
         <v>0</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.6208954742971209</v>
+        <v>0.1902103747051438</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.1280241816029159</v>
+        <v>0.01291712633726303</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>48.31731143468429</v>
+        <v>157.7201035774455</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>234.3307305259642</v>
+        <v>2322.497993493853</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>42.04718360996328</v>
-      </c>
-      <c r="O10" s="6" t="n">
+        <v>151.2155798302836</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>0.194836419384762</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>0.0123787450451988</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>153.975319884914</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>2423.50899792025</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>148.0649816275691</v>
+      </c>
+      <c r="T10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="U10" s="11" t="n">
         <v>0.22</v>
       </c>
-      <c r="Q10" s="10" t="n">
-        <v>0.02021337234626039</v>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>-0.01597928520155728</v>
-      </c>
-      <c r="S10" s="10" t="n">
-        <v>0.01498443375723729</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
+      <c r="V10" s="12" t="n">
+        <v>0.02432067486744272</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>-0.04167964901846055</v>
+      </c>
+      <c r="X10" s="12" t="n">
+        <v>0.02127848305576574</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1155,36 +1348,55 @@
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.6225998701706968</v>
+        <v>0.1898744289523417</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.1295344178879713</v>
+        <v>0.01326719292302449</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>48.18504056509836</v>
+        <v>157.9991585256063</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>231.5986784759068</v>
+        <v>2261.216835698277</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>41.87733045952093</v>
-      </c>
-      <c r="O11" s="6" t="n">
+        <v>151.2803385417978</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0.19486847417664</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>0.012551363407834</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>153.9499917919318</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>2390.178582613212</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>147.95273918329</v>
+      </c>
+      <c r="T11" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="U11" s="11" t="n">
         <v>0.22</v>
       </c>
-      <c r="Q11" s="10" t="n">
-        <v>0.02191856651357889</v>
-      </c>
-      <c r="R11" s="11" t="n">
-        <v>-0.02453728019179112</v>
-      </c>
-      <c r="S11" s="10" t="n">
-        <v>0.01515234296478721</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
+      <c r="V11" s="12" t="n">
+        <v>0.02630183143593223</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>-0.05395485837461555</v>
+      </c>
+      <c r="X11" s="12" t="n">
+        <v>0.02249096148456875</v>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1217,36 +1429,55 @@
         <v>0</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.6209478642125037</v>
+        <v>0.1900243746897275</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.1296603063733279</v>
+        <v>0.01315153506829104</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>48.31323486078254</v>
+        <v>157.8744834655244</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>231.3738170078181</v>
+        <v>2281.102536260682</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>41.96646531478569</v>
-      </c>
-      <c r="O12" s="6" t="n">
+        <v>151.2294705556766</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0.1953781923873314</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>0.01246309505181384</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>153.5483547750605</v>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>2407.106731937658</v>
+      </c>
+      <c r="S12" s="9" t="n">
+        <v>147.6288194502602</v>
+      </c>
+      <c r="T12" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="U12" s="11" t="n">
         <v>0.23</v>
       </c>
-      <c r="Q12" s="10" t="n">
-        <v>0.02175820164267326</v>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>-0.02458130135127948</v>
-      </c>
-      <c r="S12" s="10" t="n">
-        <v>0.01498528685681488</v>
-      </c>
-      <c r="T12" s="3" t="inlineStr"/>
+      <c r="V12" s="12" t="n">
+        <v>0.02817437345259366</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>-0.05234674225498336</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>0.02438989296821914</v>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1279,36 +1510,55 @@
         <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.6724454962214651</v>
+        <v>0.2022175467917771</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0.1482068111605728</v>
+        <v>0.01562078470483737</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>44.61328117828558</v>
+        <v>148.355078359698</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>202.4198467336085</v>
+        <v>1920.51811524614</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>38.43905160482379</v>
-      </c>
-      <c r="O13" s="6" t="n">
+        <v>141.3304284876639</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0.2074330836518758</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>0.01505009433346855</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>144.6249531263173</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>1993.342987444649</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>138.2213087669847</v>
+      </c>
+      <c r="T13" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="U13" s="11" t="n">
         <v>0.22</v>
       </c>
-      <c r="Q13" s="10" t="n">
-        <v>0.02066362307498388</v>
-      </c>
-      <c r="R13" s="11" t="n">
-        <v>-0.01664413215606735</v>
-      </c>
-      <c r="S13" s="10" t="n">
-        <v>0.01491894760832585</v>
-      </c>
-      <c r="T13" s="3" t="inlineStr"/>
+      <c r="V13" s="12" t="n">
+        <v>0.02579171265226132</v>
+      </c>
+      <c r="W13" s="13" t="n">
+        <v>-0.03653403988034531</v>
+      </c>
+      <c r="X13" s="12" t="n">
+        <v>0.02249378007207725</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1341,36 +1591,55 @@
         <v>0</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.6200733255596852</v>
+        <v>0.1896300337332349</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0.1274516835026312</v>
+        <v>0.01290649590399145</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>48.38137485259773</v>
+        <v>158.2027878674692</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>235.3833168424225</v>
+        <v>2324.410918591949</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>42.12214882443105</v>
-      </c>
-      <c r="O14" s="6" t="n">
+        <v>151.6626707704645</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>0.1948262700079445</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>0.01223932595399051</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>153.9833411519744</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>2451.115372919602</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>148.1441949806508</v>
+      </c>
+      <c r="T14" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="U14" s="11" t="n">
         <v>0.22</v>
       </c>
-      <c r="Q14" s="10" t="n">
-        <v>0.0214318874556022</v>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>-0.02175991730331837</v>
-      </c>
-      <c r="S14" s="10" t="n">
-        <v>0.01521300859336377</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+      <c r="V14" s="12" t="n">
+        <v>0.02740196883590396</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>-0.05169257054462162</v>
+      </c>
+      <c r="X14" s="12" t="n">
+        <v>0.02375034533262177</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1403,36 +1672,55 @@
         <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.7637728456722417</v>
+        <v>0.1751761715101735</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0.1843669739280771</v>
+        <v>0.03001746999242979</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>39.27869414314569</v>
+        <v>171.2561688120791</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>162.7189477639483</v>
+        <v>999.4180058334631</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>33.35030871248291</v>
-      </c>
-      <c r="O15" s="6" t="n">
+        <v>152.7318116179653</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>0.1796515443350982</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>0.02920625153335473</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>166.9899366077364</v>
+      </c>
+      <c r="R15" s="9" t="n">
+        <v>1027.177348169407</v>
+      </c>
+      <c r="S15" s="9" t="n">
+        <v>149.8526549922083</v>
+      </c>
+      <c r="T15" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="U15" s="11" t="n">
         <v>0.24</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>0.02265039598355435</v>
-      </c>
-      <c r="R15" s="11" t="n">
-        <v>-0.02204780024050807</v>
-      </c>
-      <c r="S15" s="10" t="n">
-        <v>0.01515342971633548</v>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
+      <c r="V15" s="12" t="n">
+        <v>0.02554784013340972</v>
+      </c>
+      <c r="W15" s="13" t="n">
+        <v>-0.02702487782213636</v>
+      </c>
+      <c r="X15" s="12" t="n">
+        <v>0.01921325068218982</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1465,36 +1753,55 @@
         <v>0</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.7661391623395439</v>
+        <v>0.1775598299396389</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.1868772858370541</v>
+        <v>0.02972620995061287</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>39.1573769814737</v>
+        <v>168.9571341119128</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>160.5331534307397</v>
+        <v>1009.210392103198</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>33.18876630559718</v>
-      </c>
-      <c r="O16" s="6" t="n">
+        <v>151.1008257640946</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>0.18189506416745</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>0.02810607956415933</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>164.9302587583269</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>1067.384724771639</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>148.8476747607216</v>
+      </c>
+      <c r="T16" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="U16" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>0.02557124396178635</v>
-      </c>
-      <c r="R16" s="11" t="n">
-        <v>-0.03502506417184262</v>
-      </c>
-      <c r="S16" s="10" t="n">
-        <v>0.01531651928058145</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
+      <c r="V16" s="12" t="n">
+        <v>0.02441562502782801</v>
+      </c>
+      <c r="W16" s="13" t="n">
+        <v>-0.05450174741903613</v>
+      </c>
+      <c r="X16" s="12" t="n">
+        <v>0.01513729392813823</v>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1527,36 +1834,55 @@
         <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.6879658319975651</v>
+        <v>0.1649313642871871</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.1558034788975695</v>
+        <v>0.02428605362232159</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>43.60681679916071</v>
+        <v>181.8938449315343</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>192.5502576211601</v>
+        <v>1235.276857514086</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>37.41266994903099</v>
-      </c>
-      <c r="O17" s="6" t="n">
+        <v>165.000989611851</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0.1691933739453443</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>0.02298136393591601</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>177.3119082647475</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>1305.405548759229</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>162.144844038881</v>
+      </c>
+      <c r="T17" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="U17" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q17" s="10" t="n">
-        <v>0.02423948655812301</v>
-      </c>
-      <c r="R17" s="11" t="n">
-        <v>-0.03558397106346749</v>
-      </c>
-      <c r="S17" s="10" t="n">
-        <v>0.01479805760248519</v>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
+      <c r="V17" s="12" t="n">
+        <v>0.02584111079525142</v>
+      </c>
+      <c r="W17" s="13" t="n">
+        <v>-0.0537217658618041</v>
+      </c>
+      <c r="X17" s="12" t="n">
+        <v>0.01761477887193941</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1589,36 +1915,55 @@
         <v>0</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.7275098087625573</v>
+        <v>0.1694506904705076</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.1765510512848004</v>
+        <v>0.02727911049356035</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>41.23655741635687</v>
+        <v>177.0426542181687</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>169.9225225886987</v>
+        <v>1099.742603670378</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>34.98126130938648</v>
-      </c>
-      <c r="O18" s="6" t="n">
+        <v>159.0515926269065</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0.1741048629354147</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>0.02615358313303813</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>172.3099486952796</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>1147.070359246605</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>155.9802816783744</v>
+      </c>
+      <c r="T18" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="U18" s="11" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q18" s="10" t="n">
-        <v>0.02494695968581379</v>
-      </c>
-      <c r="R18" s="11" t="n">
-        <v>-0.03247382001176084</v>
-      </c>
-      <c r="S18" s="10" t="n">
-        <v>0.01527440040697955</v>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
+      <c r="V18" s="12" t="n">
+        <v>0.02746623487920918</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>-0.04125967966543199</v>
+      </c>
+      <c r="X18" s="12" t="n">
+        <v>0.01969037954980113</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1651,36 +1996,55 @@
         <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.7666758686699727</v>
+        <v>0.1751392595582535</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0.1911301089334566</v>
+        <v>0.03127878653743989</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>39.12996512078034</v>
+        <v>171.2922623726271</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>156.9611411169379</v>
+        <v>959.1164914307267</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>33.04175342752668</v>
-      </c>
-      <c r="O19" s="6" t="n">
+        <v>151.9864721246686</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0.1798376266309751</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>0.03001396126934322</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>166.8171481241781</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>999.5348408289752</v>
+      </c>
+      <c r="S19" s="9" t="n">
+        <v>149.2417759292144</v>
+      </c>
+      <c r="T19" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="U19" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q19" s="10" t="n">
-        <v>0.02493404729360282</v>
-      </c>
-      <c r="R19" s="11" t="n">
-        <v>-0.03114766921308842</v>
-      </c>
-      <c r="S19" s="10" t="n">
-        <v>0.01524577605608868</v>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
+      <c r="V19" s="12" t="n">
+        <v>0.02682646417811774</v>
+      </c>
+      <c r="W19" s="13" t="n">
+        <v>-0.04043715911366041</v>
+      </c>
+      <c r="X19" s="12" t="n">
+        <v>0.0183909376470841</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1713,36 +2077,55 @@
         <v>0</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.8418322184467084</v>
+        <v>0.1892475139631258</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.2216724224389676</v>
+        <v>0.03747350025701497</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>35.63655481772123</v>
+        <v>158.5225579546868</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>135.3348317752958</v>
+        <v>800.5657276273266</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>29.80060680191553</v>
-      </c>
-      <c r="O20" s="6" t="n">
+        <v>138.7461641068536</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>0.1932856750748737</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>0.03584304009607617</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>155.2106745022816</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>836.9825751271632</v>
+      </c>
+      <c r="S20" s="9" t="n">
+        <v>137.0546425743052</v>
+      </c>
+      <c r="T20" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="U20" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q20" s="10" t="n">
-        <v>0.02442693801476452</v>
-      </c>
-      <c r="R20" s="11" t="n">
-        <v>-0.02860548153620572</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>0.01478797524759444</v>
-      </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="V20" s="12" t="n">
+        <v>0.02133798762891437</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>-0.04350968417031121</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>0.01234194990243664</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1775,36 +2158,55 @@
         <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>1.165240752300489</v>
+        <v>0.2346568508990807</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.3355753581401285</v>
+        <v>0.06753465760396005</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>25.74575249000876</v>
+        <v>127.8462567150965</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>89.39869770614294</v>
+        <v>444.2163633363987</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>21.16651828462421</v>
-      </c>
-      <c r="O21" s="6" t="n">
+        <v>105.1204932707448</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0.2409632009799954</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>0.06421907882269434</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>124.5003381345792</v>
+      </c>
+      <c r="R21" s="9" t="n">
+        <v>467.1508926938752</v>
+      </c>
+      <c r="S21" s="9" t="n">
+        <v>103.882400261751</v>
+      </c>
+      <c r="T21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="U21" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q21" s="10" t="n">
-        <v>0.02858856937706308</v>
-      </c>
-      <c r="R21" s="11" t="n">
-        <v>-0.04163446873466459</v>
-      </c>
-      <c r="S21" s="10" t="n">
-        <v>0.01475139310386895</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
+      <c r="V21" s="12" t="n">
+        <v>0.02687477504599611</v>
+      </c>
+      <c r="W21" s="13" t="n">
+        <v>-0.04909447828563939</v>
+      </c>
+      <c r="X21" s="12" t="n">
+        <v>0.01191821719438768</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1837,36 +2239,55 @@
         <v>0</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>1.052704778663269</v>
+        <v>0.212820429803557</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>0.2587828566602908</v>
+        <v>0.05091708283947326</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>28.49801825550196</v>
+        <v>140.9639104088427</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>115.9273082736759</v>
+        <v>589.1932201729087</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>24.12216391619376</v>
-      </c>
-      <c r="O22" s="6" t="n">
+        <v>119.8666753438231</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>0.2177372208008964</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>0.04784224387395324</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>137.78076109198</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>627.0608895151113</v>
+      </c>
+      <c r="S22" s="9" t="n">
+        <v>118.7687875599726</v>
+      </c>
+      <c r="T22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="U22" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q22" s="10" t="n">
-        <v>0.027654362469132</v>
-      </c>
-      <c r="R22" s="11" t="n">
-        <v>-0.04700489804021325</v>
-      </c>
-      <c r="S22" s="10" t="n">
-        <v>0.01493669742725844</v>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
+      <c r="V22" s="12" t="n">
+        <v>0.02310300285493216</v>
+      </c>
+      <c r="W22" s="13" t="n">
+        <v>-0.06038914238692938</v>
+      </c>
+      <c r="X22" s="12" t="n">
+        <v>0.009243908323103067</v>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1899,36 +2320,55 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>1.030491939700348</v>
+        <v>0.2089624669668686</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.2677088461803173</v>
+        <v>0.05318758010309472</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>29.11230922264521</v>
+        <v>143.5664520784805</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>112.0620421328673</v>
+        <v>564.0414536974666</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>24.40444125350274</v>
-      </c>
-      <c r="O23" s="6" t="n">
+        <v>120.7891334369157</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>0.213198131450098</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>0.05089554240719921</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>140.7141788530259</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>589.4425833991402</v>
+      </c>
+      <c r="S23" s="9" t="n">
+        <v>119.6980970388809</v>
+      </c>
+      <c r="T23" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="U23" s="11" t="n">
         <v>0.24</v>
       </c>
-      <c r="Q23" s="10" t="n">
-        <v>0.02661895829943325</v>
-      </c>
-      <c r="R23" s="11" t="n">
-        <v>-0.03696065186558357</v>
-      </c>
-      <c r="S23" s="10" t="n">
-        <v>0.01521243847202468</v>
-      </c>
-      <c r="T23" s="3" t="inlineStr"/>
+      <c r="V23" s="12" t="n">
+        <v>0.02026997740173564</v>
+      </c>
+      <c r="W23" s="13" t="n">
+        <v>-0.04309347579740974</v>
+      </c>
+      <c r="X23" s="12" t="n">
+        <v>0.009114901782276696</v>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1961,36 +2401,55 @@
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>1.021186694002471</v>
+        <v>0.2073175991960836</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>0.2680401116414075</v>
+        <v>0.05410354335915854</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>29.37758607333305</v>
+        <v>144.7055151918175</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>111.9235468762039</v>
+        <v>554.4923333551251</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>24.58095359485645</v>
-      </c>
-      <c r="O24" s="6" t="n">
+        <v>121.2053269688287</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>0.2130937497894884</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>0.05136152600318419</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>140.7831061663539</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>584.0947949665696</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>119.5646642471158</v>
+      </c>
+      <c r="T24" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="U24" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q24" s="10" t="n">
-        <v>0.0296020494448357</v>
-      </c>
-      <c r="R24" s="11" t="n">
-        <v>-0.04965533807479058</v>
-      </c>
-      <c r="S24" s="10" t="n">
-        <v>0.01525856529544941</v>
-      </c>
-      <c r="T24" s="3" t="inlineStr"/>
+      <c r="V24" s="12" t="n">
+        <v>0.02786136158147223</v>
+      </c>
+      <c r="W24" s="13" t="n">
+        <v>-0.0506809200604823</v>
+      </c>
+      <c r="X24" s="12" t="n">
+        <v>0.01372196988168684</v>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2023,36 +2482,55 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>1.149462559507056</v>
+        <v>0.2313235804502771</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0.3340399050865419</v>
+        <v>0.06738234957538623</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>26.09915368871642</v>
+        <v>129.6884647107928</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>89.80962915861116</v>
+        <v>445.2204499998402</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>21.41855230940193</v>
-      </c>
-      <c r="O25" s="6" t="n">
+        <v>106.3802300510513</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>0.2376986148526385</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0.06443696229914968</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>126.2102432468887</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>465.5712952563545</v>
+      </c>
+      <c r="S25" s="9" t="n">
+        <v>104.9766286656355</v>
+      </c>
+      <c r="T25" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="U25" s="11" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q25" s="10" t="n">
-        <v>0.02829416306933625</v>
-      </c>
-      <c r="R25" s="11" t="n">
-        <v>-0.03944214201003418</v>
-      </c>
-      <c r="S25" s="10" t="n">
-        <v>0.01483609014822318</v>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
+      <c r="V25" s="12" t="n">
+        <v>0.02755894747069121</v>
+      </c>
+      <c r="W25" s="13" t="n">
+        <v>-0.04371155495166146</v>
+      </c>
+      <c r="X25" s="12" t="n">
+        <v>0.01337060832736858</v>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2085,36 +2563,55 @@
         <v>0</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>1.027451221332199</v>
+        <v>0.2092422358886759</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>0.2731102856482064</v>
+        <v>0.05371251641425478</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>29.19846643532316</v>
+        <v>143.3744954625749</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>109.8457347690047</v>
+        <v>558.5290357395784</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>24.37477787063547</v>
-      </c>
-      <c r="O26" s="6" t="n">
+        <v>120.4463128215601</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>0.2147660995264481</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>0.05082464356080132</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>139.6868503276307</v>
+      </c>
+      <c r="R26" s="9" t="n">
+        <v>590.2648380428112</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>118.9960494539612</v>
+      </c>
+      <c r="T26" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="U26" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q26" s="10" t="n">
-        <v>0.02774258605243927</v>
-      </c>
-      <c r="R26" s="11" t="n">
-        <v>-0.04343043575000696</v>
-      </c>
-      <c r="S26" s="10" t="n">
-        <v>0.01470637055938248</v>
-      </c>
-      <c r="T26" s="3" t="inlineStr"/>
+      <c r="V26" s="12" t="n">
+        <v>0.02639937206898835</v>
+      </c>
+      <c r="W26" s="13" t="n">
+        <v>-0.05376536133926213</v>
+      </c>
+      <c r="X26" s="12" t="n">
+        <v>0.01218749172139577</v>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2147,36 +2644,55 @@
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.8575789307496179</v>
+        <v>0.1729741743213301</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>0.2485047222665097</v>
+        <v>0.05007853636171268</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>34.982202715471</v>
+        <v>173.4362954337317</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>120.7220519850983</v>
+        <v>599.059041648357</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>28.72488699092018</v>
-      </c>
-      <c r="O27" s="6" t="n">
+        <v>142.4389364937646</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>0.1769335052591513</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>0.04578621153479748</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>169.5552233369228</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>655.2190931368067</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>142.2353874343869</v>
+      </c>
+      <c r="T27" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="U27" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="Q27" s="10" t="n">
-        <v>0.02985383191167209</v>
-      </c>
-      <c r="R27" s="11" t="n">
-        <v>-0.07210960497365125</v>
-      </c>
-      <c r="S27" s="10" t="n">
-        <v>0.009683004016334724</v>
-      </c>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="V27" s="12" t="n">
+        <v>0.02288972300839598</v>
+      </c>
+      <c r="W27" s="13" t="n">
+        <v>-0.08571186657517572</v>
+      </c>
+      <c r="X27" s="12" t="n">
+        <v>0.001431071852435961</v>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2209,36 +2725,55 @@
         <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.8533285031336009</v>
+        <v>0.1715528109831687</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>0.2486509762158451</v>
+        <v>0.05000978785477827</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>35.1564489992233</v>
+        <v>174.8732639708442</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>120.651044514533</v>
+        <v>599.882568730665</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>28.83600358968594</v>
-      </c>
-      <c r="O28" s="6" t="n">
+        <v>143.4223564249688</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>0.1765130002614936</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>0.04615821272132162</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>169.9591528984085</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>649.9385099922263</v>
+      </c>
+      <c r="S28" s="9" t="n">
+        <v>142.3054308813319</v>
+      </c>
+      <c r="T28" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="U28" s="11" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q28" s="10" t="n">
-        <v>0.02911227150590144</v>
-      </c>
-      <c r="R28" s="11" t="n">
-        <v>-0.07097376399828452</v>
-      </c>
-      <c r="S28" s="10" t="n">
-        <v>0.009211435307955375</v>
-      </c>
-      <c r="T28" s="3" t="inlineStr"/>
+      <c r="V28" s="12" t="n">
+        <v>0.02891348296712826</v>
+      </c>
+      <c r="W28" s="13" t="n">
+        <v>-0.07701642615723747</v>
+      </c>
+      <c r="X28" s="12" t="n">
+        <v>0.007848790708264053</v>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2271,36 +2806,55 @@
         <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.645227931068923</v>
+        <v>0.1333837843494599</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>0.1662739774541561</v>
+        <v>0.03263349988085483</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>46.49519736428678</v>
+        <v>224.9148961121186</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>180.4251059566515</v>
+        <v>919.3007219431026</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>39.0327550118386</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P29" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q29" s="10" t="n">
-        <v>0.02985587511639006</v>
-      </c>
-      <c r="R29" s="11" t="n">
-        <v>-0.0633743513629756</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>0.0132800944058317</v>
-      </c>
-      <c r="T29" s="3" t="inlineStr"/>
+        <v>190.5341063688893</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>0.1370817798398971</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>0.03080988557239766</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>218.8474648858376</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>973.7134508177716</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>187.9863884855586</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>0.02772447571849201</v>
+      </c>
+      <c r="W29" s="13" t="n">
+        <v>-0.05588166501034819</v>
+      </c>
+      <c r="X29" s="12" t="n">
+        <v>0.0135526721049084</v>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2333,36 +2887,55 @@
         <v>0</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.7711821474526477</v>
+        <v>0.1542527595411182</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>0.2158864850749453</v>
+        <v>0.04464689014521068</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>38.90131546625575</v>
+        <v>194.4859857888189</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>138.9619178318895</v>
+        <v>671.9392975059907</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>32.15960111180181</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P30" s="7" t="n">
+        <v>159.7347164113665</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>0.1588555406468772</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>0.0413065682341827</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>188.8508255855396</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>726.2767468340277</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>158.2848393967071</v>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q30" s="10" t="n">
-        <v>0.02990362900651267</v>
-      </c>
-      <c r="R30" s="11" t="n">
-        <v>-0.09101353711422534</v>
-      </c>
-      <c r="S30" s="10" t="n">
-        <v>0.006743114603440801</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr"/>
+      <c r="V30" s="12" t="n">
+        <v>0.02983921402412304</v>
+      </c>
+      <c r="W30" s="13" t="n">
+        <v>-0.0748164519446668</v>
+      </c>
+      <c r="X30" s="12" t="n">
+        <v>0.009159923465730913</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2395,36 +2968,55 @@
         <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.7960092486612488</v>
+        <v>0.1603298917815599</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>0.2375664547869715</v>
+        <v>0.04860366573291901</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>37.68800431710418</v>
+        <v>187.1142035128</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>126.2804549863799</v>
+        <v>617.2373944972046</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>30.76335215980587</v>
-      </c>
-      <c r="O31" s="6" t="n">
+        <v>152.2444944456322</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>0.1643682817041188</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>0.04652989480227</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>182.5169654933994</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>644.746783277413</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>150.5604618146749</v>
+      </c>
+      <c r="T31" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="U31" s="11" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q31" s="10" t="n">
-        <v>0.02817122746808014</v>
-      </c>
-      <c r="R31" s="11" t="n">
-        <v>-0.03493845099331291</v>
-      </c>
-      <c r="S31" s="10" t="n">
-        <v>0.01532559725375421</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr"/>
+      <c r="V31" s="12" t="n">
+        <v>0.0251880037944574</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>-0.04266696553392801</v>
+      </c>
+      <c r="X31" s="12" t="n">
+        <v>0.01118509209297014</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2457,36 +3049,55 @@
         <v>0</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.769555180647707</v>
+        <v>0.1564356262017252</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>0.211953734982069</v>
+        <v>0.04170593709084065</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>38.98355927478791</v>
+        <v>191.7721731833305</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>141.5403224790446</v>
+        <v>719.3220460352279</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>32.32808203205771</v>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q32" s="10" t="n">
-        <v>0.02928917245374867</v>
-      </c>
-      <c r="R32" s="11" t="n">
-        <v>-0.06214354508578902</v>
-      </c>
-      <c r="S32" s="10" t="n">
-        <v>0.01200660968609309</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
+        <v>160.00354199475</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>0.161002894070545</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>0.03948259816601279</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>186.3320542974539</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>759.8284153909721</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>157.786448406418</v>
+      </c>
+      <c r="T32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>0.02919582949046573</v>
+      </c>
+      <c r="W32" s="13" t="n">
+        <v>-0.05330989014789789</v>
+      </c>
+      <c r="X32" s="12" t="n">
+        <v>0.01405122943525106</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2519,36 +3130,55 @@
         <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.353927553075298</v>
+        <v>0.07498875052292946</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0.1019802947913925</v>
+        <v>0.01973092173349805</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>84.76310967973015</v>
+        <v>400.0600062115562</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>294.1744781319469</v>
+        <v>1520.456084373782</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>69.67961158930505</v>
-      </c>
-      <c r="O33" s="6" t="n">
+        <v>334.5919907685167</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>0.07722817540999209</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>0.01795406984831538</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>388.4592616714661</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>1670.930337993248</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>331.8838599700537</v>
+      </c>
+      <c r="T33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="U33" s="11" t="n">
         <v>0.34</v>
       </c>
-      <c r="Q33" s="10" t="n">
-        <v>0.02988211504585338</v>
-      </c>
-      <c r="R33" s="11" t="n">
-        <v>-0.07653622822476529</v>
-      </c>
-      <c r="S33" s="10" t="n">
-        <v>0.008942407704304411</v>
-      </c>
-      <c r="T33" s="3" t="inlineStr"/>
+      <c r="V33" s="12" t="n">
+        <v>0.02986347780761966</v>
+      </c>
+      <c r="W33" s="13" t="n">
+        <v>-0.09005417532856719</v>
+      </c>
+      <c r="X33" s="12" t="n">
+        <v>0.008159874959593916</v>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2581,36 +3211,55 @@
         <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.3062181789854074</v>
+        <v>0.06566878843031351</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>0.08006631742393094</v>
+        <v>0.01517337133036798</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>97.969363214813</v>
+        <v>456.8380309290378</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>374.689394557234</v>
+        <v>1977.147948653837</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>82.03078586218082</v>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P34" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="Q34" s="10" t="n">
-        <v>0.02908397781855069</v>
-      </c>
-      <c r="R34" s="11" t="n">
-        <v>-0.09264016879229085</v>
-      </c>
-      <c r="S34" s="10" t="n">
-        <v>0.007183275658368702</v>
-      </c>
-      <c r="T34" s="3" t="inlineStr"/>
+        <v>390.6915282996466</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>0.06797563064404817</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>0.0138749751622995</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>441.334632952416</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>2162.166032665394</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>384.6229748437335</v>
+      </c>
+      <c r="T34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>0.03512844181955077</v>
+      </c>
+      <c r="W34" s="13" t="n">
+        <v>-0.08557071067455324</v>
+      </c>
+      <c r="X34" s="12" t="n">
+        <v>0.01577792761438301</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2643,36 +3292,55 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.4253178038059103</v>
+        <v>0.08883705924665226</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>0.1413400726737141</v>
+        <v>0.02771254361676974</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>70.53549071199994</v>
+        <v>337.6969054852018</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>212.2540298196641</v>
+        <v>1082.542274533257</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>56.26469843322163</v>
-      </c>
-      <c r="O35" s="6" t="n">
+        <v>273.1212982816868</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>0.09125853627720064</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>0.02617711975721449</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>328.7363705776966</v>
+      </c>
+      <c r="R35" s="9" t="n">
+        <v>1146.038994291261</v>
+      </c>
+      <c r="S35" s="9" t="n">
+        <v>270.4782187585116</v>
+      </c>
+      <c r="T35" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="U35" s="11" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q35" s="10" t="n">
-        <v>0.02900221023619638</v>
-      </c>
-      <c r="R35" s="11" t="n">
-        <v>-0.05693973224053989</v>
-      </c>
-      <c r="S35" s="10" t="n">
-        <v>0.009785709776932418</v>
-      </c>
-      <c r="T35" s="3" t="inlineStr"/>
+      <c r="V35" s="12" t="n">
+        <v>0.02725750999732268</v>
+      </c>
+      <c r="W35" s="13" t="n">
+        <v>-0.05540537457651906</v>
+      </c>
+      <c r="X35" s="12" t="n">
+        <v>0.009771875662694329</v>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2705,36 +3373,55 @@
         <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.3715749785067545</v>
+        <v>0.07865803262222035</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>0.1120955070441912</v>
+        <v>0.02159724776573188</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>80.73740627143616</v>
+        <v>381.3977924426908</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>267.628924575658</v>
+        <v>1389.065881236991</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>65.75763165130748</v>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P36" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q36" s="10" t="n">
-        <v>0.02992039399576661</v>
-      </c>
-      <c r="R36" s="11" t="n">
-        <v>-0.06788486027567643</v>
-      </c>
-      <c r="S36" s="10" t="n">
-        <v>0.009855419052450689</v>
-      </c>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>316.4695091371738</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>0.0811772979718513</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>0.02009172005629346</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>369.5614506706379</v>
+      </c>
+      <c r="R36" s="9" t="n">
+        <v>1493.152398895927</v>
+      </c>
+      <c r="S36" s="9" t="n">
+        <v>312.4507550637986</v>
+      </c>
+      <c r="T36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" s="11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>0.03202807476422032</v>
+      </c>
+      <c r="W36" s="13" t="n">
+        <v>-0.06970923914792637</v>
+      </c>
+      <c r="X36" s="12" t="n">
+        <v>0.01286203988386769</v>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2767,36 +3454,55 @@
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>0.382718394711453</v>
+        <v>0.08048463336101902</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>0.1165866111091201</v>
+        <v>0.02234785059944144</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>78.38661641183519</v>
+        <v>372.7419601383169</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>257.3194272875921</v>
+        <v>1342.410978922054</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>63.71444568758935</v>
-      </c>
-      <c r="O37" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P37" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>0.0297506066559761</v>
-      </c>
-      <c r="R37" s="11" t="n">
-        <v>-0.05799499503929192</v>
-      </c>
-      <c r="S37" s="10" t="n">
-        <v>0.01158246607150163</v>
-      </c>
-      <c r="T37" s="3" t="inlineStr"/>
+        <v>308.6281331114231</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>0.08309539370102784</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>0.02146158726161693</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>361.0308425511307</v>
+      </c>
+      <c r="R37" s="9" t="n">
+        <v>1397.8462838885</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>302.9641658712347</v>
+      </c>
+      <c r="T37" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U37" s="11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <v>0.03243799755287546</v>
+      </c>
+      <c r="W37" s="13" t="n">
+        <v>-0.03965765449705738</v>
+      </c>
+      <c r="X37" s="12" t="n">
+        <v>0.01869517216301952</v>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2829,36 +3535,55 @@
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.3721396290954024</v>
+        <v>0.07808256884925013</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>0.1137471095991767</v>
+        <v>0.02261514747383335</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>80.61490272595812</v>
+        <v>384.2086709252536</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>263.7429654759081</v>
+        <v>1326.544522192979</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>65.47962427604381</v>
-      </c>
-      <c r="O38" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P38" s="7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Q38" s="10" t="n">
-        <v>0.02982228051046457</v>
-      </c>
-      <c r="R38" s="11" t="n">
-        <v>-0.06140914931985293</v>
-      </c>
-      <c r="S38" s="10" t="n">
-        <v>0.01087948849638378</v>
-      </c>
-      <c r="T38" s="3" t="inlineStr"/>
+        <v>315.515808894922</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>0.0808184391529187</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>0.02164547053831938</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>371.2024175972541</v>
+      </c>
+      <c r="R38" s="9" t="n">
+        <v>1385.971256521795</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>309.4470872421286</v>
+      </c>
+      <c r="T38" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" s="11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V38" s="12" t="n">
+        <v>0.03503816977321228</v>
+      </c>
+      <c r="W38" s="13" t="n">
+        <v>-0.04287732090343111</v>
+      </c>
+      <c r="X38" s="12" t="n">
+        <v>0.01961150032750147</v>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2891,36 +3616,55 @@
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.1655455574770621</v>
+        <v>0.03615475779944064</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0.05221128911844812</v>
+        <v>0.01016525044715908</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>181.2189977019273</v>
+        <v>829.7663108799511</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>574.5883793817288</v>
+        <v>2951.230779403395</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>146.2228608340268</v>
-      </c>
-      <c r="O39" s="6" t="n">
+        <v>685.3908519047621</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>0.03708792587516115</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>0.009531184403570057</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>808.8885881885312</v>
+      </c>
+      <c r="R39" s="9" t="n">
+        <v>3147.562645914501</v>
+      </c>
+      <c r="S39" s="9" t="n">
+        <v>679.3965939126344</v>
+      </c>
+      <c r="T39" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="U39" s="11" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q39" s="10" t="n">
-        <v>0.02974512519098053</v>
-      </c>
-      <c r="R39" s="11" t="n">
-        <v>-0.05700561606734759</v>
-      </c>
-      <c r="S39" s="10" t="n">
-        <v>0.01121976986576054</v>
-      </c>
-      <c r="T39" s="3" t="inlineStr"/>
+      <c r="V39" s="12" t="n">
+        <v>0.02581038105405176</v>
+      </c>
+      <c r="W39" s="13" t="n">
+        <v>-0.06237584080048197</v>
+      </c>
+      <c r="X39" s="12" t="n">
+        <v>0.008822914400566706</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2953,36 +3697,55 @@
         <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.1869857643155603</v>
+        <v>0.04046975404314607</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0.06196866315129767</v>
+        <v>0.01199101205463226</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>160.4400212487379</v>
+        <v>741.2943495533988</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>484.1156557912897</v>
+        <v>2501.873892154971</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>128.058229148514</v>
-      </c>
-      <c r="O40" s="6" t="n">
+        <v>605.983280215386</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>0.04126344667465223</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>0.01116898470915271</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>727.0357281721873</v>
+      </c>
+      <c r="R40" s="9" t="n">
+        <v>2686.009586477072</v>
+      </c>
+      <c r="S40" s="9" t="n">
+        <v>604.8911905119774</v>
+      </c>
+      <c r="T40" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P40" s="7" t="n">
+      <c r="U40" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q40" s="10" t="n">
-        <v>0.02942411804011082</v>
-      </c>
-      <c r="R40" s="11" t="n">
-        <v>-0.06701721454015261</v>
-      </c>
-      <c r="S40" s="10" t="n">
-        <v>0.007922323891408763</v>
-      </c>
-      <c r="T40" s="3" t="inlineStr"/>
+      <c r="V40" s="12" t="n">
+        <v>0.01961199543392267</v>
+      </c>
+      <c r="W40" s="13" t="n">
+        <v>-0.06855362514309193</v>
+      </c>
+      <c r="X40" s="12" t="n">
+        <v>0.001805431655376388</v>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3015,36 +3778,55 @@
         <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0.1565658563474557</v>
+        <v>0.03453673025186024</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>0.04936443075165916</v>
+        <v>0.009143630293169133</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>191.6126587231325</v>
+        <v>868.6404237234971</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>607.7250267692327</v>
+        <v>3280.972550083514</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>154.6192584700805</v>
-      </c>
-      <c r="O41" s="6" t="n">
+        <v>725.6711141981932</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>0.03540550627012114</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>0.008261354520944481</v>
+      </c>
+      <c r="Q41" s="9" t="n">
+        <v>847.3258303699821</v>
+      </c>
+      <c r="R41" s="9" t="n">
+        <v>3631.365767434739</v>
+      </c>
+      <c r="S41" s="9" t="n">
+        <v>723.4892421560197</v>
+      </c>
+      <c r="T41" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="U41" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="Q41" s="10" t="n">
-        <v>0.02961737379400427</v>
-      </c>
-      <c r="R41" s="11" t="n">
-        <v>-0.06480396125139727</v>
-      </c>
-      <c r="S41" s="10" t="n">
-        <v>0.009466971389407339</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="V41" s="12" t="n">
+        <v>0.02515513228743171</v>
+      </c>
+      <c r="W41" s="13" t="n">
+        <v>-0.09649075300909404</v>
+      </c>
+      <c r="X41" s="12" t="n">
+        <v>0.003015762937499167</v>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3077,36 +3859,55 @@
         <v>0</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0.1883648412532545</v>
+        <v>0.04191813177234687</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>0.05894377758234862</v>
+        <v>0.01114703223139695</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>159.2653905070603</v>
+        <v>715.6807503475337</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>508.9595752170428</v>
+        <v>2691.299296282773</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>128.7245873739055</v>
-      </c>
-      <c r="O42" s="6" t="n">
+        <v>597.4021390845541</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>0.04299963052295148</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>0.01025069260904783</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>697.6804134162782</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>2926.63151107666</v>
+      </c>
+      <c r="S42" s="9" t="n">
+        <v>593.6178980150895</v>
+      </c>
+      <c r="T42" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P42" s="7" t="n">
+      <c r="U42" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q42" s="10" t="n">
-        <v>0.02904319332944598</v>
-      </c>
-      <c r="R42" s="11" t="n">
-        <v>-0.07752603943357332</v>
-      </c>
-      <c r="S42" s="10" t="n">
-        <v>0.006466631803770766</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
+      <c r="V42" s="12" t="n">
+        <v>0.02580026124442103</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>-0.0804106064952852</v>
+      </c>
+      <c r="X42" s="12" t="n">
+        <v>0.006374876974090782</v>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -3139,36 +3940,55 @@
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0.1722615628042504</v>
+        <v>0.03839692922399451</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>0.05291419292255337</v>
+        <v>0.009718797898425481</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>174.1537665839624</v>
+        <v>781.3124800941839</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>566.9556378552122</v>
+        <v>3086.801507093817</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>141.3104887055725</v>
-      </c>
-      <c r="O43" s="6" t="n">
+        <v>658.0017196372287</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>0.03945367405417789</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>0.008968117110025641</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>760.3854576079258</v>
+      </c>
+      <c r="R43" s="9" t="n">
+        <v>3345.183791864447</v>
+      </c>
+      <c r="S43" s="9" t="n">
+        <v>651.9943084555068</v>
+      </c>
+      <c r="T43" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P43" s="7" t="n">
+      <c r="U43" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="Q43" s="10" t="n">
-        <v>0.02950740604457277</v>
-      </c>
-      <c r="R43" s="11" t="n">
-        <v>-0.05513388503478261</v>
-      </c>
-      <c r="S43" s="10" t="n">
-        <v>0.01184869135423099</v>
-      </c>
-      <c r="T43" s="3" t="inlineStr"/>
+      <c r="V43" s="12" t="n">
+        <v>0.02752159746990923</v>
+      </c>
+      <c r="W43" s="13" t="n">
+        <v>-0.07724008629930013</v>
+      </c>
+      <c r="X43" s="12" t="n">
+        <v>0.009213901262348001</v>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3201,36 +4021,55 @@
         <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.1944298845316371</v>
+        <v>0.04266592344963928</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>0.06429100699956346</v>
+        <v>0.01187304244477679</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>154.297267995952</v>
+        <v>703.1372480525471</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>466.6282486476484</v>
+        <v>2526.732313097865</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>123.2172521754903</v>
-      </c>
-      <c r="O44" s="6" t="n">
+        <v>581.9475643760869</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>0.04374927868446112</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>0.01063325873829864</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>685.7255914177027</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>2821.33640667904</v>
+      </c>
+      <c r="S44" s="9" t="n">
+        <v>581.5554719606447</v>
+      </c>
+      <c r="T44" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="U44" s="11" t="n">
         <v>0.39</v>
       </c>
-      <c r="Q44" s="10" t="n">
-        <v>0.02985969481985592</v>
-      </c>
-      <c r="R44" s="11" t="n">
-        <v>-0.07869769311346991</v>
-      </c>
-      <c r="S44" s="10" t="n">
-        <v>0.00571936159145264</v>
-      </c>
-      <c r="T44" s="3" t="inlineStr"/>
+      <c r="V44" s="12" t="n">
+        <v>0.02539158061586511</v>
+      </c>
+      <c r="W44" s="13" t="n">
+        <v>-0.1044200517470194</v>
+      </c>
+      <c r="X44" s="12" t="n">
+        <v>0.0006742132682895363</v>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3263,36 +4102,55 @@
         <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.1028698380694428</v>
+        <v>0.02268771581302175</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>0.04107950385694992</v>
+        <v>0.008414257331065574</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>291.6306719540896</v>
+        <v>1322.301471300223</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>730.2911959323611</v>
+        <v>3565.37705226099</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>222.4622692626896</v>
-      </c>
-      <c r="O45" s="6" t="n">
+        <v>1027.850290246908</v>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>0.02324677619415892</v>
+      </c>
+      <c r="P45" s="8" t="n">
+        <v>0.008056292450452208</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>1290.50151941231</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>3723.797290689971</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>1019.576772814381</v>
+      </c>
+      <c r="T45" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P45" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>0.02895266282850384</v>
-      </c>
-      <c r="R45" s="11" t="n">
-        <v>-0.05919847378862687</v>
-      </c>
-      <c r="S45" s="10" t="n">
-        <v>0.005902646147198249</v>
-      </c>
-      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <v>0.02464154548411157</v>
+      </c>
+      <c r="W45" s="13" t="n">
+        <v>-0.04254265902847454</v>
+      </c>
+      <c r="X45" s="12" t="n">
+        <v>0.008114658604559288</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -3325,36 +4183,55 @@
         <v>0</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.08105076535409833</v>
+        <v>0.0185027818816111</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>0.02671862979932708</v>
+        <v>0.00525483738069427</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>370.1383925115896</v>
+        <v>1621.377811831385</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>1122.812068781894</v>
+        <v>5709.025384918076</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>295.7838113588605</v>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" s="7" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="Q46" s="10" t="n">
-        <v>0.02930431056590301</v>
-      </c>
-      <c r="R46" s="11" t="n">
-        <v>-0.04887476994260147</v>
-      </c>
-      <c r="S46" s="10" t="n">
-        <v>0.01193917542651897</v>
-      </c>
-      <c r="T46" s="3" t="inlineStr"/>
+        <v>1336.648907787563</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>0.0190150077449085</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>0.0051046706558481</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>1577.701171751185</v>
+      </c>
+      <c r="R46" s="9" t="n">
+        <v>5876.9707239841</v>
+      </c>
+      <c r="S46" s="9" t="n">
+        <v>1314.656598650427</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>0.02768372164655286</v>
+      </c>
+      <c r="W46" s="13" t="n">
+        <v>-0.02857685480389294</v>
+      </c>
+      <c r="X46" s="12" t="n">
+        <v>0.01672855798214701</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3387,36 +4264,55 @@
         <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.08129904629709121</v>
+        <v>0.01821886668556758</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0.02798446757001229</v>
+        <v>0.005715872048499289</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>369.0080187456438</v>
+        <v>1646.644685301149</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>1072.023254505207</v>
+        <v>5248.542959927969</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>291.9981251228874</v>
-      </c>
-      <c r="O47" s="6" t="n">
+        <v>1330.149738393451</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>0.01873211489296829</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>0.005335856896684422</v>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>1601.527652986021</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>5622.339688052974</v>
+      </c>
+      <c r="S47" s="9" t="n">
+        <v>1319.514981769547</v>
+      </c>
+      <c r="T47" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="U47" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q47" s="10" t="n">
-        <v>0.0293424017975382</v>
-      </c>
-      <c r="R47" s="11" t="n">
-        <v>-0.05048182463126549</v>
-      </c>
-      <c r="S47" s="10" t="n">
-        <v>0.01093377055077442</v>
-      </c>
-      <c r="T47" s="3" t="inlineStr"/>
+      <c r="V47" s="12" t="n">
+        <v>0.02817124776522428</v>
+      </c>
+      <c r="W47" s="13" t="n">
+        <v>-0.06648419499079594</v>
+      </c>
+      <c r="X47" s="12" t="n">
+        <v>0.008059595207962067</v>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3449,36 +4345,55 @@
         <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.08518345912372982</v>
+        <v>0.01902923300896286</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>0.03050149994533769</v>
+        <v>0.005890617493095739</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>352.1810490980967</v>
+        <v>1576.521764480463</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>983.5581874256533</v>
+        <v>5092.844686514161</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>276.1056264745245</v>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P48" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q48" s="10" t="n">
-        <v>0.02982272200667227</v>
-      </c>
-      <c r="R48" s="11" t="n">
-        <v>-0.06410342172084256</v>
-      </c>
-      <c r="S48" s="10" t="n">
-        <v>0.007428976745296354</v>
-      </c>
-      <c r="T48" s="3" t="inlineStr"/>
+        <v>1277.132678595532</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>0.0193997893723907</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>0.005560821603346876</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>1546.408542079083</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>5394.886248813302</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>1272.533245890664</v>
+      </c>
+      <c r="T48" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>0.01947300573035737</v>
+      </c>
+      <c r="W48" s="13" t="n">
+        <v>-0.0559866414913901</v>
+      </c>
+      <c r="X48" s="12" t="n">
+        <v>0.003614390995064998</v>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -3511,36 +4426,55 @@
         <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.08344074501087224</v>
+        <v>0.01853826677467095</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>0.02846077559848266</v>
+        <v>0.005617750712340876</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>359.5365788751171</v>
+        <v>1618.274262887907</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>1054.08230693472</v>
+        <v>5340.215601610278</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>285.1026264186392</v>
-      </c>
-      <c r="O49" s="6" t="n">
+        <v>1316.801580257239</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>0.01902066642006214</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>0.005167886511647529</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>1577.231803421848</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>5805.081038909262</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>1311.324401706269</v>
+      </c>
+      <c r="T49" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="U49" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q49" s="10" t="n">
-        <v>0.02936785749348284</v>
-      </c>
-      <c r="R49" s="11" t="n">
-        <v>-0.06561401316833787</v>
-      </c>
-      <c r="S49" s="10" t="n">
-        <v>0.007652669964358974</v>
-      </c>
-      <c r="T49" s="3" t="inlineStr"/>
+      <c r="V49" s="12" t="n">
+        <v>0.02602183101876099</v>
+      </c>
+      <c r="W49" s="13" t="n">
+        <v>-0.0800790607716183</v>
+      </c>
+      <c r="X49" s="12" t="n">
+        <v>0.004176829580722963</v>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -3573,36 +4507,55 @@
         <v>0</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.07293503242294594</v>
+        <v>0.01709656843709927</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>0.02352178994394296</v>
+        <v>0.004670869334834303</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>411.3249696803009</v>
+        <v>1754.738099073759</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>1275.413141240351</v>
+        <v>6422.787247818449</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>330.2922778729543</v>
-      </c>
-      <c r="O50" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q50" s="10" t="n">
-        <v>0.02898218200252286</v>
-      </c>
-      <c r="R50" s="11" t="n">
-        <v>-0.06194975306772522</v>
-      </c>
-      <c r="S50" s="10" t="n">
-        <v>0.009182021237813339</v>
-      </c>
-      <c r="T50" s="3" t="inlineStr"/>
+        <v>1457.388548437557</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>0.01765735246821254</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>0.004475725572973202</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>1699.008956977394</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>6702.823823952896</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>1430.502438849223</v>
+      </c>
+      <c r="T50" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" s="11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>0.03280097015822059</v>
+      </c>
+      <c r="W50" s="13" t="n">
+        <v>-0.04177889550576008</v>
+      </c>
+      <c r="X50" s="12" t="n">
+        <v>0.01879487154874249</v>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3635,36 +4588,55 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.03187817967419618</v>
+        <v>0.007420796505717107</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>0.01172099050422965</v>
+        <v>0.002495443238793799</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>941.0825933791799</v>
+        <v>4042.692718616862</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>2559.510647941757</v>
+        <v>12021.91239360782</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>733.0779963802053</v>
-      </c>
-      <c r="O51" s="6" t="n">
+        <v>3216.160196406939</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>0.007576757459205601</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>0.002350586049456554</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>3959.477409897901</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>12762.77463100569</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>3206.06729458519</v>
+      </c>
+      <c r="T51" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P51" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q51" s="10" t="n">
-        <v>0.02982082827961146</v>
-      </c>
-      <c r="R51" s="11" t="n">
-        <v>-0.05226488992372846</v>
-      </c>
-      <c r="S51" s="10" t="n">
-        <v>0.00979068294516749</v>
-      </c>
-      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V51" s="12" t="n">
+        <v>0.02101674036854928</v>
+      </c>
+      <c r="W51" s="13" t="n">
+        <v>-0.05804868132655406</v>
+      </c>
+      <c r="X51" s="12" t="n">
+        <v>0.003148062998800771</v>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -3697,36 +4669,55 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.03506575335952218</v>
+        <v>0.007805125970617882</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>0.01428621791617541</v>
+        <v>0.003072573827510244</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>855.5355903070434</v>
+        <v>3843.627907215583</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>2099.925968932116</v>
+        <v>9763.801192145636</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>649.1704244417721</v>
-      </c>
-      <c r="O52" s="6" t="n">
+        <v>2942.975087235755</v>
+      </c>
+      <c r="O52" s="8" t="n">
+        <v>0.007966771986440673</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>0.00291342922165452</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>3765.640594592082</v>
+      </c>
+      <c r="R52" s="9" t="n">
+        <v>10297.14392133514</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>2937.212456668048</v>
+      </c>
+      <c r="T52" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P52" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q52" s="10" t="n">
-        <v>0.02970064621830427</v>
-      </c>
-      <c r="R52" s="11" t="n">
-        <v>-0.04065190076747136</v>
-      </c>
-      <c r="S52" s="10" t="n">
-        <v>0.01098089867625914</v>
-      </c>
-      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V52" s="12" t="n">
+        <v>0.02071023791688975</v>
+      </c>
+      <c r="W52" s="13" t="n">
+        <v>-0.05179520974592212</v>
+      </c>
+      <c r="X52" s="12" t="n">
+        <v>0.001961938624706949</v>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -3759,36 +4750,55 @@
         <v>0</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.03519324649345896</v>
+        <v>0.008109182928349848</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>0.01360318715870576</v>
+        <v>0.002801979139171521</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>852.4362765332213</v>
+        <v>3699.509588705844</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>2205.365525740092</v>
+        <v>10706.71782691084</v>
       </c>
       <c r="N53" s="9" t="n">
-        <v>655.7705169174203</v>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P53" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q53" s="10" t="n">
-        <v>0.02956342875450798</v>
-      </c>
-      <c r="R53" s="11" t="n">
-        <v>-0.04254247297046002</v>
-      </c>
-      <c r="S53" s="10" t="n">
-        <v>0.01120063534598472</v>
-      </c>
-      <c r="T53" s="3" t="inlineStr"/>
+        <v>2924.855087248998</v>
+      </c>
+      <c r="O53" s="8" t="n">
+        <v>0.008299267113841505</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>0.002727473066973159</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>3614.777014462644</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>10999.19202256058</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>2890.608951656794</v>
+      </c>
+      <c r="T53" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V53" s="12" t="n">
+        <v>0.02344060889625754</v>
+      </c>
+      <c r="W53" s="13" t="n">
+        <v>-0.02659051638064358</v>
+      </c>
+      <c r="X53" s="12" t="n">
+        <v>0.01184737754741083</v>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3821,36 +4831,55 @@
         <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.02795944415051102</v>
+        <v>0.006339362406510892</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>0.01121889535692367</v>
+        <v>0.002614136236574159</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>1072.982704466665</v>
+        <v>4732.337114721232</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>2674.060060778238</v>
+        <v>11476.06600615245</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>817.4618714939268</v>
-      </c>
-      <c r="O54" s="6" t="n">
+        <v>3579.21876440214</v>
+      </c>
+      <c r="O54" s="8" t="n">
+        <v>0.006443878174309244</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>0.002557621337615149</v>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>4655.581497428894</v>
+      </c>
+      <c r="R54" s="9" t="n">
+        <v>11729.64877903837</v>
+      </c>
+      <c r="S54" s="9" t="n">
+        <v>3557.055632002685</v>
+      </c>
+      <c r="T54" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P54" s="7" t="n">
+      <c r="U54" s="11" t="n">
         <v>0.43</v>
       </c>
-      <c r="Q54" s="10" t="n">
-        <v>0.02980217839036866</v>
-      </c>
-      <c r="R54" s="11" t="n">
-        <v>-0.02971390086992997</v>
-      </c>
-      <c r="S54" s="10" t="n">
-        <v>0.01415635719744124</v>
-      </c>
-      <c r="T54" s="3" t="inlineStr"/>
+      <c r="V54" s="12" t="n">
+        <v>0.01648679490085758</v>
+      </c>
+      <c r="W54" s="13" t="n">
+        <v>-0.02161895702615457</v>
+      </c>
+      <c r="X54" s="12" t="n">
+        <v>0.00623075225477332</v>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3883,36 +4912,55 @@
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.0360237777054229</v>
+        <v>0.007972027730817181</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>0.01737866156945207</v>
+        <v>0.004167728743135334</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>832.7832867868241</v>
+        <v>3763.158008599253</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>1726.254917854751</v>
+        <v>7198.165199549756</v>
       </c>
       <c r="N55" s="9" t="n">
-        <v>602.0823678451145</v>
-      </c>
-      <c r="O55" s="6" t="n">
+        <v>2652.563068723176</v>
+      </c>
+      <c r="O55" s="8" t="n">
+        <v>0.008099208794141078</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>0.004163995011366703</v>
+      </c>
+      <c r="Q55" s="9" t="n">
+        <v>3704.065515844194</v>
+      </c>
+      <c r="R55" s="9" t="n">
+        <v>7204.619582421984</v>
+      </c>
+      <c r="S55" s="9" t="n">
+        <v>2625.061244151455</v>
+      </c>
+      <c r="T55" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="U55" s="11" t="n">
         <v>0.48</v>
       </c>
-      <c r="Q55" s="10" t="n">
-        <v>0.02925197420876574</v>
-      </c>
-      <c r="R55" s="11" t="n">
-        <v>-0.04411065442273848</v>
-      </c>
-      <c r="S55" s="10" t="n">
-        <v>0.006893085300686433</v>
-      </c>
-      <c r="T55" s="3" t="inlineStr"/>
+      <c r="V55" s="12" t="n">
+        <v>0.01595341456631627</v>
+      </c>
+      <c r="W55" s="13" t="n">
+        <v>-0.0008958672693802905</v>
+      </c>
+      <c r="X55" s="12" t="n">
+        <v>0.01047664111951407</v>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3945,36 +4993,55 @@
         <v>0</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.03087745544847888</v>
+        <v>0.006872727184712378</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>0.01270952177192889</v>
+        <v>0.002856077911080103</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>971.5826503274219</v>
+        <v>4365.079420980319</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>2360.43499813345</v>
+        <v>10503.91513607368</v>
       </c>
       <c r="N56" s="9" t="n">
-        <v>735.2016693843141</v>
-      </c>
-      <c r="O56" s="6" t="n">
+        <v>3294.552153948786</v>
+      </c>
+      <c r="O56" s="8" t="n">
+        <v>0.007067285976573705</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>0.00276625716084973</v>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>4244.911002532307</v>
+      </c>
+      <c r="R56" s="9" t="n">
+        <v>10844.97870428818</v>
+      </c>
+      <c r="S56" s="9" t="n">
+        <v>3255.040606229464</v>
+      </c>
+      <c r="T56" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P56" s="7" t="n">
+      <c r="U56" s="11" t="n">
         <v>0.44</v>
       </c>
-      <c r="Q56" s="10" t="n">
-        <v>0.0295799709130365</v>
-      </c>
-      <c r="R56" s="11" t="n">
-        <v>-0.04622770517285171</v>
-      </c>
-      <c r="S56" s="10" t="n">
-        <v>0.00924273862855181</v>
-      </c>
-      <c r="T56" s="3" t="inlineStr"/>
+      <c r="V56" s="12" t="n">
+        <v>0.02830881928415585</v>
+      </c>
+      <c r="W56" s="13" t="n">
+        <v>-0.0314489845959437</v>
+      </c>
+      <c r="X56" s="12" t="n">
+        <v>0.01213857290864673</v>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -4007,36 +5074,55 @@
         <v>0</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>0.01205780308317683</v>
+        <v>0.002663488269772567</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>0.006410985183573256</v>
+        <v>0.001680592883472415</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>2488.015419811948</v>
+        <v>11263.42486297553</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>4679.467997659459</v>
+        <v>17850.84317268705</v>
       </c>
       <c r="N57" s="9" t="n">
-        <v>1744.086835862845</v>
-      </c>
-      <c r="O57" s="6" t="n">
+        <v>7434.883000146612</v>
+      </c>
+      <c r="O57" s="8" t="n">
+        <v>0.00270714708544361</v>
+      </c>
+      <c r="P57" s="8" t="n">
+        <v>0.00171436268317362</v>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>11081.7768865647</v>
+      </c>
+      <c r="R57" s="9" t="n">
+        <v>17499.21431121222</v>
+      </c>
+      <c r="S57" s="9" t="n">
+        <v>7305.043732523341</v>
+      </c>
+      <c r="T57" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="U57" s="11" t="n">
         <v>0.44</v>
       </c>
-      <c r="Q57" s="10" t="n">
-        <v>0.0296825775708691</v>
-      </c>
-      <c r="R57" s="11" t="n">
-        <v>-0.01321265509945659</v>
-      </c>
-      <c r="S57" s="10" t="n">
-        <v>0.01557585190707182</v>
-      </c>
-      <c r="T57" s="3" t="inlineStr"/>
+      <c r="V57" s="12" t="n">
+        <v>0.01639159299724313</v>
+      </c>
+      <c r="W57" s="12" t="n">
+        <v>0.02009397994797557</v>
+      </c>
+      <c r="X57" s="12" t="n">
+        <v>0.01777392064679972</v>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -4069,36 +5155,55 @@
         <v>0</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>0.01251051863807266</v>
+        <v>0.002779167191814859</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>0.006178601389018827</v>
+        <v>0.001591815882536749</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>2397.982119518405</v>
+        <v>10794.60065891513</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>4855.46778488069</v>
+        <v>18846.40072329936</v>
       </c>
       <c r="N58" s="9" t="n">
-        <v>1721.179935889988</v>
-      </c>
-      <c r="O58" s="6" t="n">
+        <v>7378.557849632783</v>
+      </c>
+      <c r="O58" s="8" t="n">
+        <v>0.002812593433032454</v>
+      </c>
+      <c r="P58" s="8" t="n">
+        <v>0.001639694375503229</v>
+      </c>
+      <c r="Q58" s="9" t="n">
+        <v>10666.31232501133</v>
+      </c>
+      <c r="R58" s="9" t="n">
+        <v>18296.09252077411</v>
+      </c>
+      <c r="S58" s="9" t="n">
+        <v>7245.834146563547</v>
+      </c>
+      <c r="T58" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P58" s="7" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="Q58" s="10" t="n">
-        <v>0.02952714318181072</v>
-      </c>
-      <c r="R58" s="11" t="n">
-        <v>-0.03298783274577797</v>
-      </c>
-      <c r="S58" s="10" t="n">
-        <v>0.01011345497332319</v>
-      </c>
-      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <v>0.01202743084908331</v>
+      </c>
+      <c r="W58" s="12" t="n">
+        <v>0.03007790881579808</v>
+      </c>
+      <c r="X58" s="12" t="n">
+        <v>0.01831724276109514</v>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -4131,36 +5236,55 @@
         <v>0</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>0.01249004724448641</v>
+        <v>0.002803114610978181</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>0.00586767490411092</v>
+        <v>0.001479757367379972</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>2401.912451791819</v>
+        <v>10702.3808025927</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>5112.757691974697</v>
+        <v>20273.59394271332</v>
       </c>
       <c r="N59" s="9" t="n">
-        <v>1750.525876224883</v>
-      </c>
-      <c r="O59" s="6" t="n">
+        <v>7519.972686724029</v>
+      </c>
+      <c r="O59" s="8" t="n">
+        <v>0.002853367755632203</v>
+      </c>
+      <c r="P59" s="8" t="n">
+        <v>0.001485986301262578</v>
+      </c>
+      <c r="Q59" s="9" t="n">
+        <v>10513.8918531562</v>
+      </c>
+      <c r="R59" s="9" t="n">
+        <v>20188.61141217136</v>
+      </c>
+      <c r="S59" s="9" t="n">
+        <v>7420.28095093208</v>
+      </c>
+      <c r="T59" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="U59" s="11" t="n">
         <v>0.41</v>
       </c>
-      <c r="Q59" s="10" t="n">
-        <v>0.02974515490366139</v>
-      </c>
-      <c r="R59" s="11" t="n">
-        <v>-0.02453783660186913</v>
-      </c>
-      <c r="S59" s="10" t="n">
-        <v>0.01352866202555431</v>
-      </c>
-      <c r="T59" s="3" t="inlineStr"/>
+      <c r="V59" s="12" t="n">
+        <v>0.01792760968717055</v>
+      </c>
+      <c r="W59" s="12" t="n">
+        <v>0.004209429207732374</v>
+      </c>
+      <c r="X59" s="12" t="n">
+        <v>0.01343503520300349</v>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -4193,36 +5317,55 @@
         <v>0</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>0.01173019204540529</v>
+        <v>0.002657772798488506</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>0.005403142309641721</v>
+        <v>0.001387870546575118</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>2557.502885193681</v>
+        <v>11287.64656522228</v>
       </c>
       <c r="M60" s="9" t="n">
-        <v>5552.324606824817</v>
+        <v>21615.84888016517</v>
       </c>
       <c r="N60" s="9" t="n">
-        <v>1874.869977218487</v>
-      </c>
-      <c r="O60" s="6" t="n">
+        <v>7959.377129203775</v>
+      </c>
+      <c r="O60" s="8" t="n">
+        <v>0.002717129001450579</v>
+      </c>
+      <c r="P60" s="8" t="n">
+        <v>0.001386296817919996</v>
+      </c>
+      <c r="Q60" s="9" t="n">
+        <v>11041.0657661024</v>
+      </c>
+      <c r="R60" s="9" t="n">
+        <v>21640.38726209593</v>
+      </c>
+      <c r="S60" s="9" t="n">
+        <v>7843.961203661018</v>
+      </c>
+      <c r="T60" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="7" t="n">
+      <c r="U60" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q60" s="10" t="n">
-        <v>0.02923122789130461</v>
-      </c>
-      <c r="R60" s="11" t="n">
-        <v>-0.04499792523060025</v>
-      </c>
-      <c r="S60" s="10" t="n">
-        <v>0.007418835757197133</v>
-      </c>
-      <c r="T60" s="3" t="inlineStr"/>
+      <c r="V60" s="12" t="n">
+        <v>0.0223330613496493</v>
+      </c>
+      <c r="W60" s="13" t="n">
+        <v>-0.001133916026250681</v>
+      </c>
+      <c r="X60" s="12" t="n">
+        <v>0.01471398475159313</v>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4255,36 +5398,55 @@
         <v>0</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>0.01310017027951786</v>
+        <v>0.00281788559163627</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>0.007032120989508094</v>
+        <v>0.001816816489395453</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>2290.046568853007</v>
+        <v>10646.28034901155</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>4266.138202792575</v>
+        <v>16512.39967003081</v>
       </c>
       <c r="N61" s="9" t="n">
-        <v>1600.244179633578</v>
-      </c>
-      <c r="O61" s="6" t="n">
+        <v>6970.673679215787</v>
+      </c>
+      <c r="O61" s="8" t="n">
+        <v>0.002858575279046611</v>
+      </c>
+      <c r="P61" s="8" t="n">
+        <v>0.001845118007752506</v>
+      </c>
+      <c r="Q61" s="9" t="n">
+        <v>10494.73848735079</v>
+      </c>
+      <c r="R61" s="9" t="n">
+        <v>16259.12265445953</v>
+      </c>
+      <c r="S61" s="9" t="n">
+        <v>6868.531580578248</v>
+      </c>
+      <c r="T61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="U61" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="Q61" s="10" t="n">
-        <v>0.02972549498724254</v>
-      </c>
-      <c r="R61" s="11" t="n">
-        <v>-0.01272973774635961</v>
-      </c>
-      <c r="S61" s="10" t="n">
-        <v>0.01566228112105555</v>
-      </c>
-      <c r="T61" s="3" t="inlineStr"/>
+      <c r="V61" s="12" t="n">
+        <v>0.01443979398280471</v>
+      </c>
+      <c r="W61" s="12" t="n">
+        <v>0.01557753274601237</v>
+      </c>
+      <c r="X61" s="12" t="n">
+        <v>0.01487102409579943</v>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -4317,36 +5479,55 @@
         <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>0.01174566375176589</v>
+        <v>0.00281653190467165</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>0.00466148964178836</v>
+        <v>0.001069520215031677</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>2554.13407313739</v>
+        <v>10651.39718468674</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>6435.710964808802</v>
+        <v>28049.96070047302</v>
       </c>
       <c r="N62" s="9" t="n">
-        <v>1951.512444475497</v>
-      </c>
-      <c r="O62" s="6" t="n">
+        <v>8230.974908282578</v>
+      </c>
+      <c r="O62" s="8" t="n">
+        <v>0.002878334381682966</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>0.001018772474264641</v>
+      </c>
+      <c r="Q62" s="9" t="n">
+        <v>10422.69452462259</v>
+      </c>
+      <c r="R62" s="9" t="n">
+        <v>29447.20313694603</v>
+      </c>
+      <c r="S62" s="9" t="n">
+        <v>8193.850140771672</v>
+      </c>
+      <c r="T62" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="P62" s="7" t="n">
+      <c r="U62" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="Q62" s="10" t="n">
-        <v>0.02984414527075973</v>
-      </c>
-      <c r="R62" s="11" t="n">
-        <v>-0.0600001060106078</v>
-      </c>
-      <c r="S62" s="10" t="n">
-        <v>0.006474414445152108</v>
-      </c>
-      <c r="T62" s="3" t="inlineStr"/>
+      <c r="V62" s="12" t="n">
+        <v>0.02194275765483344</v>
+      </c>
+      <c r="W62" s="13" t="n">
+        <v>-0.0474490711384391</v>
+      </c>
+      <c r="X62" s="12" t="n">
+        <v>0.004530808700805578</v>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -4378,37 +5559,72 @@
       <c r="I63" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="8" t="n">
-        <v>0.005237005150670506</v>
-      </c>
-      <c r="K63" s="8" t="n">
-        <v>0.003356996694118491</v>
-      </c>
-      <c r="L63" s="9" t="n">
-        <v>5728.464864343131</v>
-      </c>
-      <c r="M63" s="9" t="n">
-        <v>8936.559291988717</v>
-      </c>
-      <c r="N63" s="9" t="n">
-        <v>3758.964235954635</v>
-      </c>
-      <c r="O63" s="6" t="n">
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P63" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S63" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T63" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="U63" s="7" t="n">
         <v>0.63</v>
       </c>
-      <c r="Q63" s="10" t="n">
+      <c r="V63" s="16" t="n">
         <v>0.0297648138405532</v>
       </c>
-      <c r="R63" s="11" t="n">
+      <c r="W63" s="17" t="n">
         <v>-0.01224838125321857</v>
       </c>
-      <c r="S63" s="10" t="n">
+      <c r="X63" s="16" t="n">
         <v>0.01393232549435173</v>
       </c>
-      <c r="T63" s="3" t="inlineStr"/>
+      <c r="Y63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4440,37 +5656,72 @@
       <c r="I64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="8" t="n">
-        <v>0.003554926453920935</v>
-      </c>
-      <c r="K64" s="8" t="n">
-        <v>0.002212182316496033</v>
-      </c>
-      <c r="L64" s="9" t="n">
-        <v>8438.993151858671</v>
-      </c>
-      <c r="M64" s="9" t="n">
-        <v>13561.26923910966</v>
-      </c>
-      <c r="N64" s="9" t="n">
-        <v>5599.267101147152</v>
-      </c>
-      <c r="O64" s="6" t="n">
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O64" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P64" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S64" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T64" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P64" s="7" t="n">
+      <c r="U64" s="7" t="n">
         <v>0.65</v>
       </c>
-      <c r="Q64" s="10" t="n">
+      <c r="V64" s="16" t="n">
         <v>0.01770983796492704</v>
       </c>
-      <c r="R64" s="10" t="n">
+      <c r="W64" s="16" t="n">
         <v>0.01176372539037115</v>
       </c>
-      <c r="S64" s="10" t="n">
+      <c r="X64" s="16" t="n">
         <v>0.01551235223705889</v>
       </c>
-      <c r="T64" s="3" t="inlineStr"/>
+      <c r="Y64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -4502,37 +5753,72 @@
       <c r="I65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="8" t="n">
-        <v>0.005399471577227513</v>
-      </c>
-      <c r="K65" s="8" t="n">
-        <v>0.003587531067881582</v>
-      </c>
-      <c r="L65" s="9" t="n">
-        <v>5556.099253587369</v>
-      </c>
-      <c r="M65" s="9" t="n">
-        <v>8362.296920181056</v>
-      </c>
-      <c r="N65" s="9" t="n">
-        <v>3596.219190420141</v>
-      </c>
-      <c r="O65" s="6" t="n">
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K65" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P65" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S65" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="U65" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="Q65" s="10" t="n">
+      <c r="V65" s="16" t="n">
         <v>0.02692228121628935</v>
       </c>
-      <c r="R65" s="11" t="n">
+      <c r="W65" s="17" t="n">
         <v>-0.002906216398351509</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="X65" s="16" t="n">
         <v>0.01539205710892509</v>
       </c>
-      <c r="T65" s="3" t="inlineStr"/>
+      <c r="Y65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -4565,36 +5851,55 @@
         <v>0</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>0.008145115105453443</v>
+        <v>0.001709216927202214</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>0.005399199254484914</v>
+        <v>0.00136818263320438</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>3683.189201330493</v>
+        <v>17551.89731774214</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>5556.379489991987</v>
+        <v>21926.89723720429</v>
       </c>
       <c r="N66" s="9" t="n">
-        <v>2386.11639998102</v>
-      </c>
-      <c r="O66" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P66" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="Q66" s="10" t="n">
-        <v>0.02759010413071592</v>
-      </c>
-      <c r="R66" s="11" t="n">
-        <v>-0.002527538845889996</v>
-      </c>
-      <c r="S66" s="10" t="n">
-        <v>0.01596692347354426</v>
-      </c>
-      <c r="T66" s="3" t="inlineStr"/>
+        <v>10520.8634187727</v>
+      </c>
+      <c r="O66" s="8" t="n">
+        <v>0.001705257437179909</v>
+      </c>
+      <c r="P66" s="8" t="n">
+        <v>0.001412823948295891</v>
+      </c>
+      <c r="Q66" s="9" t="n">
+        <v>17592.65161136777</v>
+      </c>
+      <c r="R66" s="9" t="n">
+        <v>21234.06814853696</v>
+      </c>
+      <c r="S66" s="9" t="n">
+        <v>10385.86375797472</v>
+      </c>
+      <c r="T66" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U66" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="V66" s="13" t="n">
+        <v>-0.002316552076737421</v>
+      </c>
+      <c r="W66" s="12" t="n">
+        <v>0.03262818428484082</v>
+      </c>
+      <c r="X66" s="12" t="n">
+        <v>0.01299840474937097</v>
+      </c>
+      <c r="Y66" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -4626,37 +5931,72 @@
       <c r="I67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="8" t="n">
-        <v>0.005821309157672544</v>
-      </c>
-      <c r="K67" s="8" t="n">
-        <v>0.004707232258161106</v>
-      </c>
-      <c r="L67" s="9" t="n">
-        <v>5153.479945393331</v>
-      </c>
-      <c r="M67" s="9" t="n">
-        <v>6373.171824693347</v>
-      </c>
-      <c r="N67" s="9" t="n">
-        <v>3075.364208249028</v>
-      </c>
-      <c r="O67" s="6" t="n">
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O67" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P67" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S67" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T67" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="U67" s="7" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q67" s="10" t="n">
+      <c r="V67" s="16" t="n">
         <v>0.008575092414852256</v>
       </c>
-      <c r="R67" s="10" t="n">
+      <c r="W67" s="16" t="n">
         <v>0.02381204549934055</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="X67" s="16" t="n">
         <v>0.01529113129939663</v>
       </c>
-      <c r="T67" s="3" t="inlineStr"/>
+      <c r="Y67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -4688,37 +6028,72 @@
       <c r="I68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="8" t="n">
-        <v>0.004904440042442964</v>
-      </c>
-      <c r="K68" s="8" t="n">
-        <v>0.003438885514719977</v>
-      </c>
-      <c r="L68" s="9" t="n">
-        <v>6116.90626052727</v>
-      </c>
-      <c r="M68" s="9" t="n">
-        <v>8723.756540189113</v>
-      </c>
-      <c r="N68" s="9" t="n">
-        <v>3876.05269686136</v>
-      </c>
-      <c r="O68" s="6" t="n">
+      <c r="J68" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K68" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P68" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S68" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T68" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P68" s="7" t="n">
+      <c r="U68" s="7" t="n">
         <v>0.59</v>
       </c>
-      <c r="Q68" s="10" t="n">
+      <c r="V68" s="16" t="n">
         <v>0.02909518043863094</v>
       </c>
-      <c r="R68" s="11" t="n">
+      <c r="W68" s="17" t="n">
         <v>-0.02341673665618458</v>
       </c>
-      <c r="S68" s="10" t="n">
+      <c r="X68" s="16" t="n">
         <v>0.008054942956428439</v>
       </c>
-      <c r="T68" s="3" t="inlineStr"/>
+      <c r="Y68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -4750,37 +6125,72 @@
       <c r="I69" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J69" s="8" t="n">
-        <v>0.0001907301724873491</v>
-      </c>
-      <c r="K69" s="8" t="n">
-        <v>9.388890072945136e-05</v>
-      </c>
-      <c r="L69" s="9" t="n">
-        <v>157290.2682819618</v>
-      </c>
-      <c r="M69" s="9" t="n">
-        <v>319526.5869226383</v>
-      </c>
-      <c r="N69" s="9" t="n">
-        <v>113011.8006317662</v>
-      </c>
-      <c r="O69" s="6" t="n">
+      <c r="J69" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K69" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P69" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S69" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T69" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="U69" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="Q69" s="10" t="n">
+      <c r="V69" s="16" t="n">
         <v>0.02537105988406112</v>
       </c>
-      <c r="R69" s="11" t="n">
+      <c r="W69" s="17" t="n">
         <v>-0.007091588740911248</v>
       </c>
-      <c r="S69" s="10" t="n">
+      <c r="X69" s="16" t="n">
         <v>0.01530257381782674</v>
       </c>
-      <c r="T69" s="12" t="inlineStr">
+      <c r="Y69" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -4816,37 +6226,72 @@
       <c r="I70" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="J70" s="8" t="n">
-        <v>0.0002470163072359627</v>
-      </c>
-      <c r="K70" s="8" t="n">
-        <v>0.0001220272880018447</v>
-      </c>
-      <c r="L70" s="9" t="n">
-        <v>121449.4716389006</v>
-      </c>
-      <c r="M70" s="9" t="n">
-        <v>245846.6502963378</v>
-      </c>
-      <c r="N70" s="9" t="n">
-        <v>87164.51003388288</v>
-      </c>
-      <c r="O70" s="6" t="n">
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K70" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O70" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P70" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S70" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T70" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P70" s="7" t="n">
+      <c r="U70" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q70" s="10" t="n">
+      <c r="V70" s="16" t="n">
         <v>0.02887614810497588</v>
       </c>
-      <c r="R70" s="11" t="n">
+      <c r="W70" s="17" t="n">
         <v>-0.03365897331391343</v>
       </c>
-      <c r="S70" s="10" t="n">
+      <c r="X70" s="16" t="n">
         <v>0.009452094625905216</v>
       </c>
-      <c r="T70" s="12" t="inlineStr">
+      <c r="Y70" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -4882,37 +6327,72 @@
       <c r="I71" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="J71" s="8" t="n">
-        <v>0.0002693715986718771</v>
-      </c>
-      <c r="K71" s="8" t="n">
-        <v>0.0001327810193216453</v>
-      </c>
-      <c r="L71" s="9" t="n">
-        <v>111370.3157567965</v>
-      </c>
-      <c r="M71" s="9" t="n">
-        <v>225935.9067528227</v>
-      </c>
-      <c r="N71" s="9" t="n">
-        <v>79984.94485446451</v>
-      </c>
-      <c r="O71" s="6" t="n">
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O71" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P71" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S71" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T71" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="U71" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="Q71" s="10" t="n">
+      <c r="V71" s="16" t="n">
         <v>0.02875254354440783</v>
       </c>
-      <c r="R71" s="11" t="n">
+      <c r="W71" s="17" t="n">
         <v>-0.03602147991427669</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="X71" s="16" t="n">
         <v>0.008669294045401888</v>
       </c>
-      <c r="T71" s="12" t="inlineStr">
+      <c r="Y71" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -4948,37 +6428,72 @@
       <c r="I72" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J72" s="8" t="n">
-        <v>0.0002550973410756117</v>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>0.0001254766756223815</v>
-      </c>
-      <c r="L72" s="9" t="n">
-        <v>117602.1665827865</v>
-      </c>
-      <c r="M72" s="9" t="n">
-        <v>239088.259640255</v>
-      </c>
-      <c r="N72" s="9" t="n">
-        <v>84516.62488871721</v>
-      </c>
-      <c r="O72" s="6" t="n">
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K72" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O72" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P72" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S72" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T72" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="P72" s="7" t="n">
+      <c r="U72" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q72" s="10" t="n">
+      <c r="V72" s="16" t="n">
         <v>0.02970775806231845</v>
       </c>
-      <c r="R72" s="11" t="n">
+      <c r="W72" s="17" t="n">
         <v>-0.04843977976254273</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="X72" s="16" t="n">
         <v>0.005532200352118438</v>
       </c>
-      <c r="T72" s="12" t="inlineStr">
+      <c r="Y72" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5014,37 +6529,72 @@
       <c r="I73" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J73" s="8" t="n">
-        <v>0.0002501271833151098</v>
-      </c>
-      <c r="K73" s="8" t="n">
-        <v>0.0001246433488159365</v>
-      </c>
-      <c r="L73" s="9" t="n">
-        <v>119938.9830500992</v>
-      </c>
-      <c r="M73" s="9" t="n">
-        <v>240686.7296569642</v>
-      </c>
-      <c r="N73" s="9" t="n">
-        <v>85846.80933343123</v>
-      </c>
-      <c r="O73" s="6" t="n">
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P73" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S73" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T73" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="U73" s="7" t="n">
         <v>0.52</v>
       </c>
-      <c r="Q73" s="10" t="n">
+      <c r="V73" s="16" t="n">
         <v>0.02928280720016551</v>
       </c>
-      <c r="R73" s="11" t="n">
+      <c r="W73" s="17" t="n">
         <v>-0.03708666304070915</v>
       </c>
-      <c r="S73" s="10" t="n">
+      <c r="X73" s="16" t="n">
         <v>0.008532020540458993</v>
       </c>
-      <c r="T73" s="12" t="inlineStr">
+      <c r="Y73" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5080,37 +6630,72 @@
       <c r="I74" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="J74" s="8" t="n">
-        <v>0.0001941971437592962</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>9.170869889248906e-05</v>
-      </c>
-      <c r="L74" s="9" t="n">
-        <v>154482.1896926787</v>
-      </c>
-      <c r="M74" s="9" t="n">
-        <v>327122.730583816</v>
-      </c>
-      <c r="N74" s="9" t="n">
-        <v>112411.2828100246</v>
-      </c>
-      <c r="O74" s="6" t="n">
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O74" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P74" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S74" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T74" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P74" s="7" t="n">
+      <c r="U74" s="7" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q74" s="10" t="n">
+      <c r="V74" s="16" t="n">
         <v>0.02712887717991412</v>
       </c>
-      <c r="R74" s="11" t="n">
+      <c r="W74" s="17" t="n">
         <v>-0.01508977047310502</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="X74" s="16" t="n">
         <v>0.01445774206499895</v>
       </c>
-      <c r="T74" s="12" t="inlineStr">
+      <c r="Y74" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5146,37 +6731,72 @@
       <c r="I75" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="J75" s="8" t="n">
-        <v>0.0002212005386798807</v>
-      </c>
-      <c r="K75" s="8" t="n">
-        <v>0.0001134568791085073</v>
-      </c>
-      <c r="L75" s="9" t="n">
-        <v>135623.5395222781</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>264417.6380993941</v>
-      </c>
-      <c r="N75" s="9" t="n">
-        <v>96188.70759369589</v>
-      </c>
-      <c r="O75" s="6" t="n">
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P75" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S75" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T75" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="U75" s="7" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q75" s="10" t="n">
+      <c r="V75" s="16" t="n">
         <v>0.02691917900304437</v>
       </c>
-      <c r="R75" s="11" t="n">
+      <c r="W75" s="17" t="n">
         <v>-0.009004231791526459</v>
       </c>
-      <c r="S75" s="10" t="n">
+      <c r="X75" s="16" t="n">
         <v>0.01542029392274613</v>
       </c>
-      <c r="T75" s="12" t="inlineStr">
+      <c r="Y75" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5212,37 +6832,72 @@
       <c r="I76" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="J76" s="8" t="n">
-        <v>0.0001601395927879973</v>
-      </c>
-      <c r="K76" s="8" t="n">
-        <v>8.681701986778204e-05</v>
-      </c>
-      <c r="L76" s="9" t="n">
-        <v>187336.557297956</v>
-      </c>
-      <c r="M76" s="9" t="n">
-        <v>345554.3630233852</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>130476.8188379812</v>
-      </c>
-      <c r="O76" s="6" t="n">
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O76" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P76" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S76" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T76" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="P76" s="7" t="n">
+      <c r="U76" s="7" t="n">
         <v>0.76</v>
       </c>
-      <c r="Q76" s="10" t="n">
+      <c r="V76" s="16" t="n">
         <v>0.007592711530289886</v>
       </c>
-      <c r="R76" s="10" t="n">
+      <c r="W76" s="16" t="n">
         <v>0.03120525859684893</v>
       </c>
-      <c r="S76" s="10" t="n">
+      <c r="X76" s="16" t="n">
         <v>0.0154973921720118</v>
       </c>
-      <c r="T76" s="12" t="inlineStr">
+      <c r="Y76" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5278,37 +6933,72 @@
       <c r="I77" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="J77" s="8" t="n">
-        <v>0.0002383034519908039</v>
-      </c>
-      <c r="K77" s="8" t="n">
-        <v>0.0001165399691045118</v>
-      </c>
-      <c r="L77" s="9" t="n">
-        <v>125889.9094804455</v>
-      </c>
-      <c r="M77" s="9" t="n">
-        <v>257422.4125037851</v>
-      </c>
-      <c r="N77" s="9" t="n">
-        <v>90634.99093139808</v>
-      </c>
-      <c r="O77" s="6" t="n">
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O77" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P77" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S77" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T77" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="U77" s="7" t="n">
         <v>0.34</v>
       </c>
-      <c r="Q77" s="10" t="n">
+      <c r="V77" s="16" t="n">
         <v>0.02807785643577917</v>
       </c>
-      <c r="R77" s="11" t="n">
+      <c r="W77" s="17" t="n">
         <v>-0.01584523996540423</v>
       </c>
-      <c r="S77" s="10" t="n">
+      <c r="X77" s="16" t="n">
         <v>0.01453057245152338</v>
       </c>
-      <c r="T77" s="12" t="inlineStr">
+      <c r="Y77" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5344,37 +7034,72 @@
       <c r="I78" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J78" s="8" t="n">
-        <v>0.0001828653973128859</v>
-      </c>
-      <c r="K78" s="8" t="n">
-        <v>8.954569431361155e-05</v>
-      </c>
-      <c r="L78" s="9" t="n">
-        <v>164055.0942979632</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>335024.4836444336</v>
-      </c>
-      <c r="N78" s="9" t="n">
-        <v>118064.3815471201</v>
-      </c>
-      <c r="O78" s="6" t="n">
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O78" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P78" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S78" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T78" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P78" s="7" t="n">
+      <c r="U78" s="7" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q78" s="10" t="n">
+      <c r="V78" s="16" t="n">
         <v>0.02908480028841356</v>
       </c>
-      <c r="R78" s="11" t="n">
+      <c r="W78" s="17" t="n">
         <v>-0.01703599285621407</v>
       </c>
-      <c r="S78" s="10" t="n">
+      <c r="X78" s="16" t="n">
         <v>0.01484651375692345</v>
       </c>
-      <c r="T78" s="12" t="inlineStr">
+      <c r="Y78" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5410,37 +7135,72 @@
       <c r="I79" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="J79" s="8" t="n">
-        <v>0.0003355376988971184</v>
-      </c>
-      <c r="K79" s="8" t="n">
-        <v>0.0002034505534405084</v>
-      </c>
-      <c r="L79" s="9" t="n">
-        <v>89408.73141410711</v>
-      </c>
-      <c r="M79" s="9" t="n">
-        <v>147455.9763671147</v>
-      </c>
-      <c r="N79" s="9" t="n">
-        <v>59889.32003334352</v>
-      </c>
-      <c r="O79" s="6" t="n">
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P79" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S79" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T79" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P79" s="7" t="n">
+      <c r="U79" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q79" s="10" t="n">
+      <c r="V79" s="16" t="n">
         <v>0.02384259700177809</v>
       </c>
-      <c r="R79" s="11" t="n">
+      <c r="W79" s="17" t="n">
         <v>-6.673742502801977e-05</v>
       </c>
-      <c r="S79" s="10" t="n">
+      <c r="X79" s="16" t="n">
         <v>0.01517433803412101</v>
       </c>
-      <c r="T79" s="12" t="inlineStr">
+      <c r="Y79" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5476,37 +7236,72 @@
       <c r="I80" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="J80" s="8" t="n">
-        <v>0.0002355799894147013</v>
-      </c>
-      <c r="K80" s="8" t="n">
-        <v>0.0001252164376358165</v>
-      </c>
-      <c r="L80" s="9" t="n">
-        <v>127345.2812122754</v>
-      </c>
-      <c r="M80" s="9" t="n">
-        <v>239585.1580385393</v>
-      </c>
-      <c r="N80" s="9" t="n">
-        <v>89277.47857800884</v>
-      </c>
-      <c r="O80" s="6" t="n">
+      <c r="J80" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K80" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O80" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P80" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S80" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P80" s="7" t="n">
+      <c r="U80" s="7" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q80" s="10" t="n">
+      <c r="V80" s="16" t="n">
         <v>0.02956925545762166</v>
       </c>
-      <c r="R80" s="11" t="n">
+      <c r="W80" s="17" t="n">
         <v>-0.03587168994499602</v>
       </c>
-      <c r="S80" s="10" t="n">
+      <c r="X80" s="16" t="n">
         <v>0.008073716354650809</v>
       </c>
-      <c r="T80" s="12" t="inlineStr">
+      <c r="Y80" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5542,37 +7337,72 @@
       <c r="I81" s="3" t="n">
         <v>894</v>
       </c>
-      <c r="J81" s="8" t="n">
-        <v>0.0004281671320873167</v>
-      </c>
-      <c r="K81" s="8" t="n">
-        <v>0.0001322950686430878</v>
-      </c>
-      <c r="L81" s="9" t="n">
-        <v>70066.09744598999</v>
-      </c>
-      <c r="M81" s="9" t="n">
-        <v>226765.8220952702</v>
-      </c>
-      <c r="N81" s="9" t="n">
-        <v>56782.50387379317</v>
-      </c>
-      <c r="O81" s="6" t="n">
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K81" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P81" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S81" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="P81" s="7" t="n">
+      <c r="U81" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="Q81" s="10" t="n">
+      <c r="V81" s="16" t="n">
         <v>0.02944499699501742</v>
       </c>
-      <c r="R81" s="11" t="n">
+      <c r="W81" s="17" t="n">
         <v>-0.04778155168784919</v>
       </c>
-      <c r="S81" s="10" t="n">
+      <c r="X81" s="16" t="n">
         <v>0.01324325682337814</v>
       </c>
-      <c r="T81" s="12" t="inlineStr">
+      <c r="Y81" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5608,37 +7438,72 @@
       <c r="I82" s="3" t="n">
         <v>1251</v>
       </c>
-      <c r="J82" s="8" t="n">
-        <v>0.000225655601558998</v>
-      </c>
-      <c r="K82" s="8" t="n">
-        <v>6.46162338180165e-05</v>
-      </c>
-      <c r="L82" s="9" t="n">
-        <v>132945.957435745</v>
-      </c>
-      <c r="M82" s="9" t="n">
-        <v>464279.6125272673</v>
-      </c>
-      <c r="N82" s="9" t="n">
-        <v>109422.8190439995</v>
-      </c>
-      <c r="O82" s="6" t="n">
+      <c r="J82" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K82" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O82" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P82" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S82" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P82" s="7" t="n">
+      <c r="U82" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="Q82" s="10" t="n">
+      <c r="V82" s="16" t="n">
         <v>0.02466009849518867</v>
       </c>
-      <c r="R82" s="11" t="n">
+      <c r="W82" s="17" t="n">
         <v>-0.02590025761712069</v>
       </c>
-      <c r="S82" s="10" t="n">
+      <c r="X82" s="16" t="n">
         <v>0.01473871975418196</v>
       </c>
-      <c r="T82" s="12" t="inlineStr">
+      <c r="Y82" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5674,37 +7539,72 @@
       <c r="I83" s="3" t="n">
         <v>1090</v>
       </c>
-      <c r="J83" s="8" t="n">
-        <v>0.0002451639264434937</v>
-      </c>
-      <c r="K83" s="8" t="n">
-        <v>7.512695871728962e-05</v>
-      </c>
-      <c r="L83" s="9" t="n">
-        <v>122367.1052882836</v>
-      </c>
-      <c r="M83" s="9" t="n">
-        <v>399324.0311096985</v>
-      </c>
-      <c r="N83" s="9" t="n">
-        <v>99340.15262984837</v>
-      </c>
-      <c r="O83" s="6" t="n">
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K83" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P83" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S83" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T83" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="U83" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="Q83" s="10" t="n">
+      <c r="V83" s="16" t="n">
         <v>0.02947546312149713</v>
       </c>
-      <c r="R83" s="11" t="n">
+      <c r="W83" s="17" t="n">
         <v>-0.0691440972024365</v>
       </c>
-      <c r="S83" s="10" t="n">
+      <c r="X83" s="16" t="n">
         <v>0.008959474068941549</v>
       </c>
-      <c r="T83" s="12" t="inlineStr">
+      <c r="Y83" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5740,37 +7640,72 @@
       <c r="I84" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="J84" s="8" t="n">
-        <v>0.000166038861339944</v>
-      </c>
-      <c r="K84" s="8" t="n">
-        <v>4.658420803073064e-05</v>
-      </c>
-      <c r="L84" s="9" t="n">
-        <v>180680.5934339596</v>
-      </c>
-      <c r="M84" s="9" t="n">
-        <v>643995.0633100732</v>
-      </c>
-      <c r="N84" s="9" t="n">
-        <v>149304.3864480457</v>
-      </c>
-      <c r="O84" s="6" t="n">
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O84" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P84" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S84" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T84" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P84" s="7" t="n">
+      <c r="U84" s="7" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q84" s="10" t="n">
+      <c r="V84" s="16" t="n">
         <v>0.02785531471099252</v>
       </c>
-      <c r="R84" s="11" t="n">
+      <c r="W84" s="17" t="n">
         <v>-0.03895646647620556</v>
       </c>
-      <c r="S84" s="10" t="n">
+      <c r="X84" s="16" t="n">
         <v>0.01499565586382907</v>
       </c>
-      <c r="T84" s="12" t="inlineStr">
+      <c r="Y84" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5806,37 +7741,72 @@
       <c r="I85" s="3" t="n">
         <v>933</v>
       </c>
-      <c r="J85" s="8" t="n">
-        <v>0.0002638304441198718</v>
-      </c>
-      <c r="K85" s="8" t="n">
-        <v>7.916140696267185e-05</v>
-      </c>
-      <c r="L85" s="9" t="n">
-        <v>113709.3943046597</v>
-      </c>
-      <c r="M85" s="9" t="n">
-        <v>378972.5467379116</v>
-      </c>
-      <c r="N85" s="9" t="n">
-        <v>92715.35813474646</v>
-      </c>
-      <c r="O85" s="6" t="n">
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K85" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O85" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P85" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S85" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P85" s="7" t="n">
+      <c r="U85" s="7" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q85" s="10" t="n">
+      <c r="V85" s="16" t="n">
         <v>0.02974681935876975</v>
       </c>
-      <c r="R85" s="11" t="n">
+      <c r="W85" s="17" t="n">
         <v>-0.06397784909054448</v>
       </c>
-      <c r="S85" s="10" t="n">
+      <c r="X85" s="16" t="n">
         <v>0.01060840497871276</v>
       </c>
-      <c r="T85" s="12" t="inlineStr">
+      <c r="Y85" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5872,37 +7842,72 @@
       <c r="I86" s="3" t="n">
         <v>887</v>
       </c>
-      <c r="J86" s="8" t="n">
-        <v>0.0002139883032155538</v>
-      </c>
-      <c r="K86" s="8" t="n">
-        <v>5.842325922480695e-05</v>
-      </c>
-      <c r="L86" s="9" t="n">
-        <v>140194.5786250781</v>
-      </c>
-      <c r="M86" s="9" t="n">
-        <v>513494.1185763525</v>
-      </c>
-      <c r="N86" s="9" t="n">
-        <v>116452.6799113019</v>
-      </c>
-      <c r="O86" s="6" t="n">
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K86" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O86" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P86" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S86" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T86" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P86" s="7" t="n">
+      <c r="U86" s="7" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q86" s="10" t="n">
+      <c r="V86" s="16" t="n">
         <v>0.02942884838337945</v>
       </c>
-      <c r="R86" s="11" t="n">
+      <c r="W86" s="17" t="n">
         <v>-0.06652006692015577</v>
       </c>
-      <c r="S86" s="10" t="n">
+      <c r="X86" s="16" t="n">
         <v>0.01144138106274604</v>
       </c>
-      <c r="T86" s="12" t="inlineStr">
+      <c r="Y86" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -5938,37 +7943,72 @@
       <c r="I87" s="3" t="n">
         <v>824</v>
       </c>
-      <c r="J87" s="8" t="n">
-        <v>0.0001075459146376672</v>
-      </c>
-      <c r="K87" s="8" t="n">
-        <v>6.173378652342915e-05</v>
-      </c>
-      <c r="L87" s="9" t="n">
-        <v>278950.6240294945</v>
-      </c>
-      <c r="M87" s="9" t="n">
-        <v>485957.5556508984</v>
-      </c>
-      <c r="N87" s="9" t="n">
-        <v>190528.9131045005</v>
-      </c>
-      <c r="O87" s="6" t="n">
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K87" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O87" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P87" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S87" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T87" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P87" s="7" t="n">
+      <c r="U87" s="7" t="n">
         <v>0.46</v>
       </c>
-      <c r="Q87" s="10" t="n">
+      <c r="V87" s="16" t="n">
         <v>0.02866748414870605</v>
       </c>
-      <c r="R87" s="11" t="n">
+      <c r="W87" s="17" t="n">
         <v>-0.03838887373040601</v>
       </c>
-      <c r="S87" s="10" t="n">
+      <c r="X87" s="16" t="n">
         <v>0.005344650798675589</v>
       </c>
-      <c r="T87" s="12" t="inlineStr">
+      <c r="Y87" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6004,37 +8044,72 @@
       <c r="I88" s="3" t="n">
         <v>794</v>
       </c>
-      <c r="J88" s="8" t="n">
-        <v>0.0001508648869848555</v>
-      </c>
-      <c r="K88" s="8" t="n">
-        <v>8.790982638658875e-05</v>
-      </c>
-      <c r="L88" s="9" t="n">
-        <v>198853.4283859672</v>
-      </c>
-      <c r="M88" s="9" t="n">
-        <v>341258.7788317678</v>
-      </c>
-      <c r="N88" s="9" t="n">
-        <v>135107.6911083763</v>
-      </c>
-      <c r="O88" s="6" t="n">
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K88" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O88" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P88" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S88" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T88" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="P88" s="7" t="n">
+      <c r="U88" s="7" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q88" s="10" t="n">
+      <c r="V88" s="16" t="n">
         <v>0.02612879221121276</v>
       </c>
-      <c r="R88" s="11" t="n">
+      <c r="W88" s="17" t="n">
         <v>-0.006826624824500502</v>
       </c>
-      <c r="S88" s="10" t="n">
+      <c r="X88" s="16" t="n">
         <v>0.01452374068536581</v>
       </c>
-      <c r="T88" s="12" t="inlineStr">
+      <c r="Y88" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6070,37 +8145,72 @@
       <c r="I89" s="3" t="n">
         <v>597</v>
       </c>
-      <c r="J89" s="8" t="n">
-        <v>0.0001297281514316475</v>
-      </c>
-      <c r="K89" s="8" t="n">
-        <v>5.487791740820867e-05</v>
-      </c>
-      <c r="L89" s="9" t="n">
-        <v>231252.8134327629</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>546667.9753323253</v>
-      </c>
-      <c r="N89" s="9" t="n">
-        <v>173692.312901763</v>
-      </c>
-      <c r="O89" s="6" t="n">
+      <c r="J89" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K89" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O89" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P89" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S89" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T89" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P89" s="7" t="n">
+      <c r="U89" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q89" s="10" t="n">
+      <c r="V89" s="16" t="n">
         <v>0.02907545796689225</v>
       </c>
-      <c r="R89" s="11" t="n">
+      <c r="W89" s="17" t="n">
         <v>-0.03832303552206908</v>
       </c>
-      <c r="S89" s="10" t="n">
+      <c r="X89" s="16" t="n">
         <v>0.01057698075853308</v>
       </c>
-      <c r="T89" s="12" t="inlineStr">
+      <c r="Y89" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6136,37 +8246,72 @@
       <c r="I90" s="3" t="n">
         <v>821</v>
       </c>
-      <c r="J90" s="8" t="n">
-        <v>0.0001092907922415393</v>
-      </c>
-      <c r="K90" s="8" t="n">
-        <v>5.029828096235934e-05</v>
-      </c>
-      <c r="L90" s="9" t="n">
-        <v>274497.0494284474</v>
-      </c>
-      <c r="M90" s="9" t="n">
-        <v>596441.8549900436</v>
-      </c>
-      <c r="N90" s="9" t="n">
-        <v>201280.7561301735</v>
-      </c>
-      <c r="O90" s="6" t="n">
+      <c r="J90" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K90" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O90" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P90" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S90" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T90" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P90" s="7" t="n">
+      <c r="U90" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q90" s="10" t="n">
+      <c r="V90" s="16" t="n">
         <v>0.02972514556506745</v>
       </c>
-      <c r="R90" s="11" t="n">
+      <c r="W90" s="17" t="n">
         <v>-0.03055503967544428</v>
       </c>
-      <c r="S90" s="10" t="n">
+      <c r="X90" s="16" t="n">
         <v>0.01201241110171115</v>
       </c>
-      <c r="T90" s="12" t="inlineStr">
+      <c r="Y90" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6202,37 +8347,72 @@
       <c r="I91" s="3" t="n">
         <v>386</v>
       </c>
-      <c r="J91" s="8" t="n">
-        <v>0.0001657892058186163</v>
-      </c>
-      <c r="K91" s="8" t="n">
-        <v>9.17296130361599e-05</v>
-      </c>
-      <c r="L91" s="9" t="n">
-        <v>180952.6733171149</v>
-      </c>
-      <c r="M91" s="9" t="n">
-        <v>327048.1473433663</v>
-      </c>
-      <c r="N91" s="9" t="n">
-        <v>125168.6456964934</v>
-      </c>
-      <c r="O91" s="6" t="n">
+      <c r="J91" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K91" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O91" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P91" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S91" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T91" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P91" s="7" t="n">
+      <c r="U91" s="7" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q91" s="10" t="n">
+      <c r="V91" s="16" t="n">
         <v>0.02355500554369445</v>
       </c>
-      <c r="R91" s="11" t="n">
+      <c r="W91" s="17" t="n">
         <v>-0.001920721751912629</v>
       </c>
-      <c r="S91" s="10" t="n">
+      <c r="X91" s="16" t="n">
         <v>0.01491744813313128</v>
       </c>
-      <c r="T91" s="12" t="inlineStr">
+      <c r="Y91" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6268,37 +8448,72 @@
       <c r="I92" s="3" t="n">
         <v>673</v>
       </c>
-      <c r="J92" s="8" t="n">
-        <v>0.0001068137590781001</v>
-      </c>
-      <c r="K92" s="8" t="n">
-        <v>6.228644089147159e-05</v>
-      </c>
-      <c r="L92" s="9" t="n">
-        <v>280862.692774108</v>
-      </c>
-      <c r="M92" s="9" t="n">
-        <v>481645.7574172885</v>
-      </c>
-      <c r="N92" s="9" t="n">
-        <v>190778.405254078</v>
-      </c>
-      <c r="O92" s="6" t="n">
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K92" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O92" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P92" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S92" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T92" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P92" s="7" t="n">
+      <c r="U92" s="7" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q92" s="10" t="n">
+      <c r="V92" s="16" t="n">
         <v>0.02931514578294265</v>
       </c>
-      <c r="R92" s="11" t="n">
+      <c r="W92" s="17" t="n">
         <v>-0.01392091417200891</v>
       </c>
-      <c r="S92" s="10" t="n">
+      <c r="X92" s="16" t="n">
         <v>0.01408833019756016</v>
       </c>
-      <c r="T92" s="12" t="inlineStr">
+      <c r="Y92" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6335,38 +8550,53 @@
         <v>1012</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>0.03960357507610895</v>
+        <v>0.01417559474597384</v>
       </c>
       <c r="K93" s="8" t="n">
-        <v>0.01453586542127732</v>
+        <v>0.001800958627545976</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>757.5073700378542</v>
+        <v>2116.313321423118</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>2063.860604824159</v>
+        <v>16657.79521036451</v>
       </c>
       <c r="N93" s="9" t="n">
-        <v>590.3320990677724</v>
-      </c>
-      <c r="O93" s="6" t="n">
+        <v>1947.291210870099</v>
+      </c>
+      <c r="O93" s="8" t="n">
+        <v>0.01444346724817535</v>
+      </c>
+      <c r="P93" s="8" t="n">
+        <v>0.001815563655607303</v>
+      </c>
+      <c r="Q93" s="9" t="n">
+        <v>2077.063594531979</v>
+      </c>
+      <c r="R93" s="9" t="n">
+        <v>16523.79408859947</v>
+      </c>
+      <c r="S93" s="9" t="n">
+        <v>1912.985535761369</v>
+      </c>
+      <c r="T93" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="U93" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q93" s="10" t="n">
-        <v>0.01707656409680756</v>
-      </c>
-      <c r="R93" s="10" t="n">
-        <v>0.008779434680167321</v>
-      </c>
-      <c r="S93" s="10" t="n">
-        <v>0.01504781959399677</v>
-      </c>
-      <c r="T93" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V93" s="12" t="n">
+        <v>0.01889673816173287</v>
+      </c>
+      <c r="W93" s="12" t="n">
+        <v>0.008109585549573417</v>
+      </c>
+      <c r="X93" s="12" t="n">
+        <v>0.01793305514726562</v>
+      </c>
+      <c r="Y93" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6401,38 +8631,53 @@
         <v>1012</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>0.03846257496029813</v>
+        <v>0.01379740170164189</v>
       </c>
       <c r="K94" s="8" t="n">
-        <v>0.01402744539340736</v>
+        <v>0.001738771058752968</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>779.9789803716112</v>
+        <v>2174.322430318892</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>2138.664536459322</v>
+        <v>17253.56529773146</v>
       </c>
       <c r="N94" s="9" t="n">
-        <v>608.7896404193447</v>
-      </c>
-      <c r="O94" s="6" t="n">
+        <v>2002.110300168628</v>
+      </c>
+      <c r="O94" s="8" t="n">
+        <v>0.01406548743222319</v>
+      </c>
+      <c r="P94" s="8" t="n">
+        <v>0.001754490315306046</v>
+      </c>
+      <c r="Q94" s="9" t="n">
+        <v>2132.880225058663</v>
+      </c>
+      <c r="R94" s="9" t="n">
+        <v>17098.9829572054</v>
+      </c>
+      <c r="S94" s="9" t="n">
+        <v>1965.725440742463</v>
+      </c>
+      <c r="T94" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P94" s="7" t="n">
+      <c r="U94" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q94" s="10" t="n">
-        <v>0.01680478298524609</v>
-      </c>
-      <c r="R94" s="10" t="n">
-        <v>0.009326672393441005</v>
-      </c>
-      <c r="S94" s="10" t="n">
-        <v>0.01498610893515727</v>
-      </c>
-      <c r="T94" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V94" s="12" t="n">
+        <v>0.0194301605750451</v>
+      </c>
+      <c r="W94" s="12" t="n">
+        <v>0.009040440645677661</v>
+      </c>
+      <c r="X94" s="12" t="n">
+        <v>0.01850963449525356</v>
+      </c>
+      <c r="Y94" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6467,38 +8712,53 @@
         <v>1012</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>0.03800651645438113</v>
+        <v>0.01367033415229143</v>
       </c>
       <c r="K95" s="8" t="n">
-        <v>0.01379699854461241</v>
+        <v>0.00171416610769429</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>789.3383240215851</v>
+        <v>2194.533042557075</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>2174.385965396417</v>
+        <v>17501.22106914874</v>
       </c>
       <c r="N95" s="9" t="n">
-        <v>616.7887946912396</v>
-      </c>
-      <c r="O95" s="6" t="n">
+        <v>2021.613718724305</v>
+      </c>
+      <c r="O95" s="8" t="n">
+        <v>0.01392173362203007</v>
+      </c>
+      <c r="P95" s="8" t="n">
+        <v>0.001728314282397638</v>
+      </c>
+      <c r="Q95" s="9" t="n">
+        <v>2154.904038138419</v>
+      </c>
+      <c r="R95" s="9" t="n">
+        <v>17357.95410912297</v>
+      </c>
+      <c r="S95" s="9" t="n">
+        <v>1986.850508954805</v>
+      </c>
+      <c r="T95" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="U95" s="11" t="n">
         <v>0.11</v>
       </c>
-      <c r="Q95" s="10" t="n">
-        <v>0.01667222483631126</v>
-      </c>
-      <c r="R95" s="10" t="n">
-        <v>0.01005323503860768</v>
-      </c>
-      <c r="S95" s="10" t="n">
-        <v>0.0150687700879052</v>
-      </c>
-      <c r="T95" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V95" s="12" t="n">
+        <v>0.01839014810742623</v>
+      </c>
+      <c r="W95" s="12" t="n">
+        <v>0.00825367777360797</v>
+      </c>
+      <c r="X95" s="12" t="n">
+        <v>0.01749664084581148</v>
+      </c>
+      <c r="Y95" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6532,37 +8792,72 @@
       <c r="I96" s="3" t="n">
         <v>924</v>
       </c>
-      <c r="J96" s="8" t="n">
-        <v>0.002088622103210463</v>
-      </c>
-      <c r="K96" s="8" t="n">
-        <v>0.0006484330678911772</v>
-      </c>
-      <c r="L96" s="9" t="n">
-        <v>14363.53658897241</v>
-      </c>
-      <c r="M96" s="9" t="n">
-        <v>46265.37646755968</v>
-      </c>
-      <c r="N96" s="9" t="n">
-        <v>11628.67073722744</v>
-      </c>
-      <c r="O96" s="6" t="n">
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K96" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O96" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P96" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S96" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T96" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P96" s="7" t="n">
+      <c r="U96" s="7" t="n">
         <v>0.19</v>
       </c>
-      <c r="Q96" s="10" t="n">
+      <c r="V96" s="16" t="n">
         <v>0.01867401552135085</v>
       </c>
-      <c r="R96" s="10" t="n">
+      <c r="W96" s="16" t="n">
         <v>0.00175453053249147</v>
       </c>
-      <c r="S96" s="10" t="n">
+      <c r="X96" s="16" t="n">
         <v>0.01509851746875004</v>
       </c>
-      <c r="T96" s="12" t="inlineStr">
+      <c r="Y96" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6598,37 +8893,72 @@
       <c r="I97" s="3" t="n">
         <v>935</v>
       </c>
-      <c r="J97" s="8" t="n">
-        <v>0.001758829058575272</v>
-      </c>
-      <c r="K97" s="8" t="n">
-        <v>0.0005210458373711691</v>
-      </c>
-      <c r="L97" s="9" t="n">
-        <v>17056.80256630585</v>
-      </c>
-      <c r="M97" s="9" t="n">
-        <v>57576.5083382278</v>
-      </c>
-      <c r="N97" s="9" t="n">
-        <v>13943.83958966672</v>
-      </c>
-      <c r="O97" s="6" t="n">
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K97" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O97" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P97" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S97" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T97" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P97" s="7" t="n">
+      <c r="U97" s="7" t="n">
         <v>0.17</v>
       </c>
-      <c r="Q97" s="10" t="n">
+      <c r="V97" s="16" t="n">
         <v>0.01793395011190457</v>
       </c>
-      <c r="R97" s="10" t="n">
+      <c r="W97" s="16" t="n">
         <v>0.003137755108694362</v>
       </c>
-      <c r="S97" s="10" t="n">
+      <c r="X97" s="16" t="n">
         <v>0.01493487641320354</v>
       </c>
-      <c r="T97" s="12" t="inlineStr">
+      <c r="Y97" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6664,37 +8994,72 @@
       <c r="I98" s="3" t="n">
         <v>911</v>
       </c>
-      <c r="J98" s="8" t="n">
-        <v>0.001705390856158816</v>
-      </c>
-      <c r="K98" s="8" t="n">
-        <v>0.0004890633983564306</v>
-      </c>
-      <c r="L98" s="9" t="n">
-        <v>17591.2752737348</v>
-      </c>
-      <c r="M98" s="9" t="n">
-        <v>61341.74035681142</v>
-      </c>
-      <c r="N98" s="9" t="n">
-        <v>14474.48007014102</v>
-      </c>
-      <c r="O98" s="6" t="n">
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K98" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O98" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P98" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S98" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P98" s="7" t="n">
+      <c r="U98" s="7" t="n">
         <v>0.16</v>
       </c>
-      <c r="Q98" s="10" t="n">
+      <c r="V98" s="16" t="n">
         <v>0.01689460780279663</v>
       </c>
-      <c r="R98" s="10" t="n">
+      <c r="W98" s="16" t="n">
         <v>0.00645313627565719</v>
       </c>
-      <c r="S98" s="10" t="n">
+      <c r="X98" s="16" t="n">
         <v>0.01483877013054853</v>
       </c>
-      <c r="T98" s="12" t="inlineStr">
+      <c r="Y98" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6730,37 +9095,72 @@
       <c r="I99" s="3" t="n">
         <v>881</v>
       </c>
-      <c r="J99" s="8" t="n">
-        <v>0.001556260433688404</v>
-      </c>
-      <c r="K99" s="8" t="n">
-        <v>0.0006467560796896961</v>
-      </c>
-      <c r="L99" s="9" t="n">
-        <v>19276.97919357797</v>
-      </c>
-      <c r="M99" s="9" t="n">
-        <v>46385.33898961345</v>
-      </c>
-      <c r="N99" s="9" t="n">
-        <v>14549.1801709129</v>
-      </c>
-      <c r="O99" s="6" t="n">
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K99" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O99" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P99" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S99" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T99" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P99" s="7" t="n">
+      <c r="U99" s="7" t="n">
         <v>0.21</v>
       </c>
-      <c r="Q99" s="10" t="n">
+      <c r="V99" s="16" t="n">
         <v>0.02574779277206688</v>
       </c>
-      <c r="R99" s="11" t="n">
+      <c r="W99" s="17" t="n">
         <v>-0.01369104192130139</v>
       </c>
-      <c r="S99" s="10" t="n">
+      <c r="X99" s="16" t="n">
         <v>0.01506559469777546</v>
       </c>
-      <c r="T99" s="12" t="inlineStr">
+      <c r="Y99" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6796,37 +9196,72 @@
       <c r="I100" s="3" t="n">
         <v>797</v>
       </c>
-      <c r="J100" s="8" t="n">
-        <v>0.001083776353455107</v>
-      </c>
-      <c r="K100" s="8" t="n">
-        <v>0.0004388287974908955</v>
-      </c>
-      <c r="L100" s="9" t="n">
-        <v>27680.98778346586</v>
-      </c>
-      <c r="M100" s="9" t="n">
-        <v>68363.79055233361</v>
-      </c>
-      <c r="N100" s="9" t="n">
-        <v>21038.53365986431</v>
-      </c>
-      <c r="O100" s="6" t="n">
+      <c r="J100" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K100" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O100" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P100" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S100" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T100" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P100" s="7" t="n">
+      <c r="U100" s="7" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q100" s="10" t="n">
+      <c r="V100" s="16" t="n">
         <v>0.02963984666987799</v>
       </c>
-      <c r="R100" s="11" t="n">
+      <c r="W100" s="17" t="n">
         <v>-0.02456489365686738</v>
       </c>
-      <c r="S100" s="10" t="n">
+      <c r="X100" s="16" t="n">
         <v>0.01527920665522548</v>
       </c>
-      <c r="T100" s="12" t="inlineStr">
+      <c r="Y100" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6862,37 +9297,72 @@
       <c r="I101" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J101" s="8" t="n">
-        <v>0.001790608536417824</v>
-      </c>
-      <c r="K101" s="8" t="n">
-        <v>0.0008785488080948825</v>
-      </c>
-      <c r="L101" s="9" t="n">
-        <v>16754.08074397772</v>
-      </c>
-      <c r="M101" s="9" t="n">
-        <v>34147.22064793926</v>
-      </c>
-      <c r="N101" s="9" t="n">
-        <v>12049.97117456768</v>
-      </c>
-      <c r="O101" s="6" t="n">
+      <c r="J101" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K101" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O101" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P101" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S101" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T101" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P101" s="7" t="n">
+      <c r="U101" s="7" t="n">
         <v>0.46</v>
       </c>
-      <c r="Q101" s="10" t="n">
+      <c r="V101" s="16" t="n">
         <v>0.02924870948886847</v>
       </c>
-      <c r="R101" s="11" t="n">
+      <c r="W101" s="17" t="n">
         <v>-0.04782450641342928</v>
       </c>
-      <c r="S101" s="10" t="n">
+      <c r="X101" s="16" t="n">
         <v>0.005451314681941837</v>
       </c>
-      <c r="T101" s="12" t="inlineStr">
+      <c r="Y101" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -6929,38 +9399,53 @@
         <v>6001</v>
       </c>
       <c r="J102" s="8" t="n">
-        <v>0.03001566543800551</v>
+        <v>0.0109796903733588</v>
       </c>
       <c r="K102" s="8" t="n">
-        <v>0.01165668247495262</v>
+        <v>0.00155622777271171</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>999.4780912641145</v>
+        <v>2732.317486182691</v>
       </c>
       <c r="M102" s="9" t="n">
-        <v>2573.631053643498</v>
+        <v>19277.3837647977</v>
       </c>
       <c r="N102" s="9" t="n">
-        <v>767.9615915757369</v>
-      </c>
-      <c r="O102" s="6" t="n">
+        <v>2488.215337413833</v>
+      </c>
+      <c r="O102" s="8" t="n">
+        <v>0.01103486176230086</v>
+      </c>
+      <c r="P102" s="8" t="n">
+        <v>0.00156658607875356</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>2718.656621734131</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>19149.92122480063</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>2475.373406396621</v>
+      </c>
+      <c r="T102" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P102" s="7" t="n">
+      <c r="U102" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q102" s="10" t="n">
-        <v>0.00518820346935378</v>
-      </c>
-      <c r="R102" s="10" t="n">
-        <v>0.00576487123269831</v>
-      </c>
-      <c r="S102" s="10" t="n">
-        <v>0.005336141424722607</v>
-      </c>
-      <c r="T102" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V102" s="12" t="n">
+        <v>0.005024858358112949</v>
+      </c>
+      <c r="W102" s="12" t="n">
+        <v>0.006656034690732504</v>
+      </c>
+      <c r="X102" s="12" t="n">
+        <v>0.005187876295360772</v>
+      </c>
+      <c r="Y102" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6995,38 +9480,53 @@
         <v>6001</v>
       </c>
       <c r="J103" s="8" t="n">
-        <v>0.04639107135927203</v>
+        <v>0.01696833122860295</v>
       </c>
       <c r="K103" s="8" t="n">
-        <v>0.01801858503354914</v>
+        <v>0.002405704402561088</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>646.6761624810805</v>
+        <v>1767.999433522962</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>1664.94760516114</v>
+        <v>12470.36001932004</v>
       </c>
       <c r="N103" s="9" t="n">
-        <v>496.8643792630337</v>
-      </c>
-      <c r="O103" s="6" t="n">
+        <v>1610.003882691835</v>
+      </c>
+      <c r="O103" s="8" t="n">
+        <v>0.01709102547969332</v>
+      </c>
+      <c r="P103" s="8" t="n">
+        <v>0.002426361772179684</v>
+      </c>
+      <c r="Q103" s="9" t="n">
+        <v>1755.307195325667</v>
+      </c>
+      <c r="R103" s="9" t="n">
+        <v>12364.19084077885</v>
+      </c>
+      <c r="S103" s="9" t="n">
+        <v>1598.230776614734</v>
+      </c>
+      <c r="T103" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P103" s="7" t="n">
+      <c r="U103" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q103" s="10" t="n">
-        <v>0.007340605012796209</v>
-      </c>
-      <c r="R103" s="10" t="n">
-        <v>0.007836193902045041</v>
-      </c>
-      <c r="S103" s="10" t="n">
-        <v>0.0074677570843944</v>
-      </c>
-      <c r="T103" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V103" s="12" t="n">
+        <v>0.007230778880809918</v>
+      </c>
+      <c r="W103" s="12" t="n">
+        <v>0.008586827873201974</v>
+      </c>
+      <c r="X103" s="12" t="n">
+        <v>0.007366336732694601</v>
+      </c>
+      <c r="Y103" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7061,38 +9561,53 @@
         <v>6001</v>
       </c>
       <c r="J104" s="8" t="n">
-        <v>0.05051217868000064</v>
+        <v>0.01847584649372766</v>
       </c>
       <c r="K104" s="8" t="n">
-        <v>0.01962103859559337</v>
+        <v>0.002619738244932373</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>593.9161759395254</v>
+        <v>1623.741570389463</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>1528.971050836096</v>
+        <v>11451.52576141226</v>
       </c>
       <c r="N104" s="9" t="n">
-        <v>456.3163200736294</v>
-      </c>
-      <c r="O104" s="6" t="n">
+        <v>1478.620321390246</v>
+      </c>
+      <c r="O104" s="8" t="n">
+        <v>0.01860284415438286</v>
+      </c>
+      <c r="P104" s="8" t="n">
+        <v>0.002644814315046759</v>
+      </c>
+      <c r="Q104" s="9" t="n">
+        <v>1612.65663202</v>
+      </c>
+      <c r="R104" s="9" t="n">
+        <v>11342.95131016395</v>
+      </c>
+      <c r="S104" s="9" t="n">
+        <v>1468.132719308044</v>
+      </c>
+      <c r="T104" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P104" s="7" t="n">
+      <c r="U104" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q104" s="10" t="n">
-        <v>0.007206238191344916</v>
-      </c>
-      <c r="R104" s="10" t="n">
-        <v>0.008434228689544687</v>
-      </c>
-      <c r="S104" s="10" t="n">
-        <v>0.007521335487978176</v>
-      </c>
-      <c r="T104" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V104" s="12" t="n">
+        <v>0.006873712698268752</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>0.009571975430329172</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>0.007143497276693722</v>
+      </c>
+      <c r="Y104" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7127,38 +9642,53 @@
         <v>6001</v>
       </c>
       <c r="J105" s="8" t="n">
-        <v>0.03200449198621933</v>
+        <v>0.01170627276999039</v>
       </c>
       <c r="K105" s="8" t="n">
-        <v>0.01243511209453136</v>
+        <v>0.001660592014795444</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>937.3684173120937</v>
+        <v>2562.728597688795</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>2412.52348768076</v>
+        <v>18065.84623598559</v>
       </c>
       <c r="N105" s="9" t="n">
-        <v>720.1487306587435</v>
-      </c>
-      <c r="O105" s="6" t="n">
+        <v>2333.583271889014</v>
+      </c>
+      <c r="O105" s="8" t="n">
+        <v>0.01179970037720444</v>
+      </c>
+      <c r="P105" s="8" t="n">
+        <v>0.001677712468221937</v>
+      </c>
+      <c r="Q105" s="9" t="n">
+        <v>2542.43743832312</v>
+      </c>
+      <c r="R105" s="9" t="n">
+        <v>17881.49076092546</v>
+      </c>
+      <c r="S105" s="9" t="n">
+        <v>2314.571530145387</v>
+      </c>
+      <c r="T105" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P105" s="7" t="n">
+      <c r="U105" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q105" s="10" t="n">
-        <v>0.008030790365714635</v>
-      </c>
-      <c r="R105" s="10" t="n">
-        <v>0.009071240327956698</v>
-      </c>
-      <c r="S105" s="10" t="n">
-        <v>0.008297821251586068</v>
-      </c>
-      <c r="T105" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V105" s="12" t="n">
+        <v>0.007980986694035686</v>
+      </c>
+      <c r="W105" s="12" t="n">
+        <v>0.01030984930311241</v>
+      </c>
+      <c r="X105" s="12" t="n">
+        <v>0.008213935709489029</v>
+      </c>
+      <c r="Y105" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7193,38 +9723,53 @@
         <v>6001</v>
       </c>
       <c r="J106" s="8" t="n">
-        <v>0.03278242333068332</v>
+        <v>0.01199142661017657</v>
       </c>
       <c r="K106" s="8" t="n">
-        <v>0.01273118705285807</v>
+        <v>0.00169965348491419</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>915.1245378471134</v>
+        <v>2501.787399886213</v>
       </c>
       <c r="M106" s="9" t="n">
-        <v>2356.41813096016</v>
+        <v>17650.65659928595</v>
       </c>
       <c r="N106" s="9" t="n">
-        <v>703.1471205662066</v>
-      </c>
-      <c r="O106" s="6" t="n">
+        <v>2278.277157725136</v>
+      </c>
+      <c r="O106" s="8" t="n">
+        <v>0.01206621181524514</v>
+      </c>
+      <c r="P106" s="8" t="n">
+        <v>0.001712548933896117</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>2486.281565362237</v>
+      </c>
+      <c r="R106" s="9" t="n">
+        <v>17517.74761363975</v>
+      </c>
+      <c r="S106" s="9" t="n">
+        <v>2263.852954456722</v>
+      </c>
+      <c r="T106" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="P106" s="7" t="n">
+      <c r="U106" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q106" s="10" t="n">
-        <v>0.00646453937365532</v>
-      </c>
-      <c r="R106" s="10" t="n">
-        <v>0.007000676871237621</v>
-      </c>
-      <c r="S106" s="10" t="n">
-        <v>0.006602079686633511</v>
-      </c>
-      <c r="T106" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V106" s="12" t="n">
+        <v>0.006236556124614934</v>
+      </c>
+      <c r="W106" s="12" t="n">
+        <v>0.007587104722453608</v>
+      </c>
+      <c r="X106" s="12" t="n">
+        <v>0.006371528345079591</v>
+      </c>
+      <c r="Y106" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7259,38 +9804,53 @@
         <v>6001</v>
       </c>
       <c r="J107" s="8" t="n">
-        <v>0.03202540178156797</v>
+        <v>0.01171439123941857</v>
       </c>
       <c r="K107" s="8" t="n">
-        <v>0.01243796871821411</v>
+        <v>0.001660580514611703</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>936.7563974565441</v>
+        <v>2560.952540073181</v>
       </c>
       <c r="M107" s="9" t="n">
-        <v>2411.969404302178</v>
+        <v>18065.97134919107</v>
       </c>
       <c r="N107" s="9" t="n">
-        <v>719.756732657394</v>
-      </c>
-      <c r="O107" s="6" t="n">
+        <v>2332.129274503332</v>
+      </c>
+      <c r="O107" s="8" t="n">
+        <v>0.01179855625406106</v>
+      </c>
+      <c r="P107" s="8" t="n">
+        <v>0.001675644509862569</v>
+      </c>
+      <c r="Q107" s="9" t="n">
+        <v>2542.683982175701</v>
+      </c>
+      <c r="R107" s="9" t="n">
+        <v>17903.55879389985</v>
+      </c>
+      <c r="S107" s="9" t="n">
+        <v>2315.059546275935</v>
+      </c>
+      <c r="T107" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="P107" s="7" t="n">
+      <c r="U107" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" s="10" t="n">
-        <v>0.00737739322818487</v>
-      </c>
-      <c r="R107" s="10" t="n">
-        <v>0.008178477667937001</v>
-      </c>
-      <c r="S107" s="10" t="n">
-        <v>0.007582916034923448</v>
-      </c>
-      <c r="T107" s="12" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V107" s="12" t="n">
+        <v>0.007184753601133131</v>
+      </c>
+      <c r="W107" s="12" t="n">
+        <v>0.009071523553549454</v>
+      </c>
+      <c r="X107" s="12" t="n">
+        <v>0.007373343054979165</v>
+      </c>
+      <c r="Y107" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7324,37 +9884,72 @@
       <c r="I108" s="3" t="n">
         <v>1553</v>
       </c>
-      <c r="J108" s="8" t="n">
-        <v>0.001934852915069811</v>
-      </c>
-      <c r="K108" s="8" t="n">
-        <v>0.0008053215209173767</v>
-      </c>
-      <c r="L108" s="9" t="n">
-        <v>15505.05455290258</v>
-      </c>
-      <c r="M108" s="9" t="n">
-        <v>37252.20203456838</v>
-      </c>
-      <c r="N108" s="9" t="n">
-        <v>11697.49321447231</v>
-      </c>
-      <c r="O108" s="6" t="n">
+      <c r="J108" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K108" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O108" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P108" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S108" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T108" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P108" s="7" t="n">
+      <c r="U108" s="7" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q108" s="10" t="n">
+      <c r="V108" s="16" t="n">
         <v>0.02974507459287388</v>
       </c>
-      <c r="R108" s="11" t="n">
+      <c r="W108" s="17" t="n">
         <v>-0.02513603623759195</v>
       </c>
-      <c r="S108" s="10" t="n">
+      <c r="X108" s="16" t="n">
         <v>0.0148719916698425</v>
       </c>
-      <c r="T108" s="12" t="inlineStr">
+      <c r="Y108" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -7390,37 +9985,72 @@
       <c r="I109" s="3" t="n">
         <v>1568</v>
       </c>
-      <c r="J109" s="8" t="n">
-        <v>0.002111396039528798</v>
-      </c>
-      <c r="K109" s="8" t="n">
-        <v>0.0008833617581232051</v>
-      </c>
-      <c r="L109" s="9" t="n">
-        <v>14208.60863540083</v>
-      </c>
-      <c r="M109" s="9" t="n">
-        <v>33961.1713141603</v>
-      </c>
-      <c r="N109" s="9" t="n">
-        <v>10704.32154333191</v>
-      </c>
-      <c r="O109" s="6" t="n">
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O109" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P109" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S109" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T109" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P109" s="7" t="n">
+      <c r="U109" s="7" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q109" s="10" t="n">
+      <c r="V109" s="16" t="n">
         <v>0.02950243701682774</v>
       </c>
-      <c r="R109" s="11" t="n">
+      <c r="W109" s="17" t="n">
         <v>-0.02735801428920922</v>
       </c>
-      <c r="S109" s="10" t="n">
+      <c r="X109" s="16" t="n">
         <v>0.01402890785031544</v>
       </c>
-      <c r="T109" s="12" t="inlineStr">
+      <c r="Y109" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -7456,37 +10086,72 @@
       <c r="I110" s="3" t="n">
         <v>1727</v>
       </c>
-      <c r="J110" s="8" t="n">
-        <v>0.001776047215961111</v>
-      </c>
-      <c r="K110" s="8" t="n">
-        <v>0.0007168918660543074</v>
-      </c>
-      <c r="L110" s="9" t="n">
-        <v>16891.44282336292</v>
-      </c>
-      <c r="M110" s="9" t="n">
-        <v>41847.3153630779</v>
-      </c>
-      <c r="N110" s="9" t="n">
-        <v>12848.7354741647</v>
-      </c>
-      <c r="O110" s="6" t="n">
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K110" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O110" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P110" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S110" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T110" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P110" s="7" t="n">
+      <c r="U110" s="7" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q110" s="10" t="n">
+      <c r="V110" s="16" t="n">
         <v>0.02551239961796974</v>
       </c>
-      <c r="R110" s="11" t="n">
+      <c r="W110" s="17" t="n">
         <v>-0.01336712455814691</v>
       </c>
-      <c r="S110" s="10" t="n">
+      <c r="X110" s="16" t="n">
         <v>0.01523126619972368</v>
       </c>
-      <c r="T110" s="12" t="inlineStr">
+      <c r="Y110" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -7522,37 +10187,72 @@
       <c r="I111" s="3" t="n">
         <v>1742</v>
       </c>
-      <c r="J111" s="8" t="n">
-        <v>0.002722223974663548</v>
-      </c>
-      <c r="K111" s="8" t="n">
-        <v>0.001285553504946959</v>
-      </c>
-      <c r="L111" s="9" t="n">
-        <v>11020.40106883852</v>
-      </c>
-      <c r="M111" s="9" t="n">
-        <v>23336.25157144881</v>
-      </c>
-      <c r="N111" s="9" t="n">
-        <v>8019.167888139399</v>
-      </c>
-      <c r="O111" s="6" t="n">
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O111" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P111" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S111" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T111" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P111" s="7" t="n">
+      <c r="U111" s="7" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q111" s="10" t="n">
+      <c r="V111" s="16" t="n">
         <v>0.02936986803801268</v>
       </c>
-      <c r="R111" s="11" t="n">
+      <c r="W111" s="17" t="n">
         <v>-0.04548635785371302</v>
       </c>
-      <c r="S111" s="10" t="n">
+      <c r="X111" s="16" t="n">
         <v>0.006935690923445379</v>
       </c>
-      <c r="T111" s="12" t="inlineStr">
+      <c r="Y111" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -7588,37 +10288,72 @@
       <c r="I112" s="3" t="n">
         <v>1826</v>
       </c>
-      <c r="J112" s="8" t="n">
-        <v>0.003892444699917626</v>
-      </c>
-      <c r="K112" s="8" t="n">
-        <v>0.002132038411897311</v>
-      </c>
-      <c r="L112" s="9" t="n">
-        <v>7707.238589834013</v>
-      </c>
-      <c r="M112" s="9" t="n">
-        <v>14071.04104344108</v>
-      </c>
-      <c r="N112" s="9" t="n">
-        <v>5349.469554139938</v>
-      </c>
-      <c r="O112" s="6" t="n">
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K112" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O112" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P112" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S112" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T112" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P112" s="7" t="n">
+      <c r="U112" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="Q112" s="10" t="n">
+      <c r="V112" s="16" t="n">
         <v>0.02416387611193758</v>
       </c>
-      <c r="R112" s="11" t="n">
+      <c r="W112" s="17" t="n">
         <v>-0.003744039362997077</v>
       </c>
-      <c r="S112" s="10" t="n">
+      <c r="X112" s="16" t="n">
         <v>0.01477285728386729</v>
       </c>
-      <c r="T112" s="12" t="inlineStr">
+      <c r="Y112" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
@@ -7654,80 +10389,115 @@
       <c r="I113" s="3" t="n">
         <v>1671</v>
       </c>
-      <c r="J113" s="8" t="n">
-        <v>0.001734463596290902</v>
-      </c>
-      <c r="K113" s="8" t="n">
-        <v>0.0006977362354264142</v>
-      </c>
-      <c r="L113" s="9" t="n">
-        <v>17296.41375244433</v>
-      </c>
-      <c r="M113" s="9" t="n">
-        <v>42996.19036076837</v>
-      </c>
-      <c r="N113" s="9" t="n">
-        <v>13168.59317600027</v>
-      </c>
-      <c r="O113" s="6" t="n">
+      <c r="J113" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K113" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O113" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P113" s="14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S113" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T113" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="P113" s="7" t="n">
+      <c r="U113" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q113" s="10" t="n">
+      <c r="V113" s="16" t="n">
         <v>0.02574682808752476</v>
       </c>
-      <c r="R113" s="11" t="n">
+      <c r="W113" s="17" t="n">
         <v>-0.01473735185138939</v>
       </c>
-      <c r="S113" s="10" t="n">
+      <c r="X113" s="16" t="n">
         <v>0.01507211403847456</v>
       </c>
-      <c r="T113" s="12" t="inlineStr">
+      <c r="Y113" s="18" t="inlineStr">
         <is>
           <t>저속, κ클립</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>■ 전 DLC 합산 (MASTA 기반) — 2단계 배치 완료 후 입력</t>
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>■ 전 DLC 합산 (MASTA 기반)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="14" t="inlineStr">
-        <is>
-          <t>Σ D30 (상위 25 DLC 부분합, MASTA 참값)</t>
-        </is>
-      </c>
-      <c r="J116" s="8" t="n">
-        <v>4.767462047249903</v>
-      </c>
-      <c r="K116" s="8" t="n">
-        <v>0.8978858517134197</v>
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>Σ D30 (상위 70 DLC 부분합, MASTA 참값)</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>6.734895578379972</v>
+      </c>
+      <c r="K116" s="14" t="n">
+        <v>1.237953692805305</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="14" t="inlineStr">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>수명 [yr] = 30/ΣD30 · Sys=와이블(e=9/8) — 부분합 기준</t>
         </is>
       </c>
-      <c r="L117" s="15" t="n">
-        <v>6.292656281827228</v>
-      </c>
-      <c r="M117" s="15" t="n">
-        <v>33.41181948991793</v>
-      </c>
-      <c r="N117" s="15" t="n">
-        <v>5.545244573633031</v>
+      <c r="L117" s="21" t="n">
+        <v>4.454412047056009</v>
+      </c>
+      <c r="M117" s="21" t="n">
+        <v>24.23353973121363</v>
+      </c>
+      <c r="N117" s="21" t="n">
+        <v>3.93786495573634</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T116"/>
+  <autoFilter ref="A2:Y116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Main bearing/01. 정리/Python 자동화/Results/DLC별해석/DLC별해석_총괄.xlsx
+++ b/Main bearing/01. 정리/Python 자동화/Results/DLC별해석/DLC별해석_총괄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="총괄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'총괄'!$A$2:$Y$116</definedName>
@@ -56,7 +56,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,14 +127,10 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5559,72 +5550,56 @@
       <c r="I63" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K63" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P63" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S63" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T63" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U63" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="V63" s="16" t="n">
-        <v>0.0297648138405532</v>
-      </c>
-      <c r="W63" s="17" t="n">
-        <v>-0.01224838125321857</v>
-      </c>
-      <c r="X63" s="16" t="n">
-        <v>0.01393232549435173</v>
-      </c>
-      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="J63" s="8" t="n">
+        <v>0.001115180316019416</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>0.0009408600401186838</v>
+      </c>
+      <c r="L63" s="9" t="n">
+        <v>26901.47913216724</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>31885.7202142581</v>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>15752.23334450198</v>
+      </c>
+      <c r="O63" s="8" t="n">
+        <v>0.001120210050821028</v>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>0.0009922841152481146</v>
+      </c>
+      <c r="Q63" s="9" t="n">
+        <v>26780.69169082379</v>
+      </c>
+      <c r="R63" s="9" t="n">
+        <v>30233.27647696817</v>
+      </c>
+      <c r="S63" s="9" t="n">
+        <v>15334.6524794698</v>
+      </c>
+      <c r="T63" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U63" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="V63" s="12" t="n">
+        <v>0.004510243526863134</v>
+      </c>
+      <c r="W63" s="12" t="n">
+        <v>0.05465645572846722</v>
+      </c>
+      <c r="X63" s="12" t="n">
+        <v>0.02723119194199186</v>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5656,72 +5631,56 @@
       <c r="I64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K64" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P64" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S64" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T64" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U64" s="7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="V64" s="16" t="n">
-        <v>0.01770983796492704</v>
-      </c>
-      <c r="W64" s="16" t="n">
-        <v>0.01176372539037115</v>
-      </c>
-      <c r="X64" s="16" t="n">
-        <v>0.01551235223705889</v>
-      </c>
-      <c r="Y64" s="3" t="inlineStr"/>
+      <c r="J64" s="8" t="n">
+        <v>0.0007652873593390052</v>
+      </c>
+      <c r="K64" s="8" t="n">
+        <v>0.0006631786152405957</v>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>39200.96109507366</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>45236.68180874054</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>22675.68253158874</v>
+      </c>
+      <c r="O64" s="8" t="n">
+        <v>0.0007407748973023724</v>
+      </c>
+      <c r="P64" s="8" t="n">
+        <v>0.0007191445808395346</v>
+      </c>
+      <c r="Q64" s="9" t="n">
+        <v>40498.13257610224</v>
+      </c>
+      <c r="R64" s="9" t="n">
+        <v>41716.2289743987</v>
+      </c>
+      <c r="S64" s="9" t="n">
+        <v>22193.92788351249</v>
+      </c>
+      <c r="T64" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U64" s="11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="V64" s="13" t="n">
+        <v>-0.0320304023547503</v>
+      </c>
+      <c r="W64" s="12" t="n">
+        <v>0.08439048593060396</v>
+      </c>
+      <c r="X64" s="12" t="n">
+        <v>0.02170659698476074</v>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -5753,72 +5712,56 @@
       <c r="I65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K65" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O65" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P65" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S65" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T65" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U65" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="V65" s="16" t="n">
-        <v>0.02692228121628935</v>
-      </c>
-      <c r="W65" s="17" t="n">
-        <v>-0.002906216398351509</v>
-      </c>
-      <c r="X65" s="16" t="n">
-        <v>0.01539205710892509</v>
-      </c>
-      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="J65" s="8" t="n">
+        <v>0.001104941765022946</v>
+      </c>
+      <c r="K65" s="8" t="n">
+        <v>0.000989253601314336</v>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>27150.75214789893</v>
+      </c>
+      <c r="M65" s="9" t="n">
+        <v>30325.89414902466</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>15469.24002496958</v>
+      </c>
+      <c r="O65" s="8" t="n">
+        <v>0.001081019928920828</v>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>0.001034299838457213</v>
+      </c>
+      <c r="Q65" s="9" t="n">
+        <v>27751.56978830975</v>
+      </c>
+      <c r="R65" s="9" t="n">
+        <v>29005.12876879952</v>
+      </c>
+      <c r="S65" s="9" t="n">
+        <v>15317.21338409986</v>
+      </c>
+      <c r="T65" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U65" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="V65" s="13" t="n">
+        <v>-0.02164986143104286</v>
+      </c>
+      <c r="W65" s="12" t="n">
+        <v>0.04553558064689134</v>
+      </c>
+      <c r="X65" s="12" t="n">
+        <v>0.00992521531543944</v>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -5931,72 +5874,56 @@
       <c r="I67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K67" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P67" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S67" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T67" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U67" s="7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="V67" s="16" t="n">
-        <v>0.008575092414852256</v>
-      </c>
-      <c r="W67" s="16" t="n">
-        <v>0.02381204549934055</v>
-      </c>
-      <c r="X67" s="16" t="n">
-        <v>0.01529113129939663</v>
-      </c>
-      <c r="Y67" s="3" t="inlineStr"/>
+      <c r="J67" s="8" t="n">
+        <v>0.001150217560171262</v>
+      </c>
+      <c r="K67" s="8" t="n">
+        <v>0.001341750676258366</v>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>26082.02225284505</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>22358.84842902307</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>12997.68728448772</v>
+      </c>
+      <c r="O67" s="8" t="n">
+        <v>0.001105021566914498</v>
+      </c>
+      <c r="P67" s="8" t="n">
+        <v>0.001422776930773369</v>
+      </c>
+      <c r="Q67" s="9" t="n">
+        <v>27148.79138854064</v>
+      </c>
+      <c r="R67" s="9" t="n">
+        <v>21085.52602388142</v>
+      </c>
+      <c r="S67" s="9" t="n">
+        <v>12805.51291867554</v>
+      </c>
+      <c r="T67" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U67" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V67" s="13" t="n">
+        <v>-0.03929343006207864</v>
+      </c>
+      <c r="W67" s="12" t="n">
+        <v>0.06038845811574656</v>
+      </c>
+      <c r="X67" s="12" t="n">
+        <v>0.01500715879423398</v>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -6028,72 +5955,56 @@
       <c r="I68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K68" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O68" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P68" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S68" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T68" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U68" s="7" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="V68" s="16" t="n">
-        <v>0.02909518043863094</v>
-      </c>
-      <c r="W68" s="17" t="n">
-        <v>-0.02341673665618458</v>
-      </c>
-      <c r="X68" s="16" t="n">
-        <v>0.008054942956428439</v>
-      </c>
-      <c r="Y68" s="3" t="inlineStr"/>
+      <c r="J68" s="8" t="n">
+        <v>0.001012272168298236</v>
+      </c>
+      <c r="K68" s="8" t="n">
+        <v>0.001004420405125424</v>
+      </c>
+      <c r="L68" s="9" t="n">
+        <v>29636.29835880401</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>29867.97146584636</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>16066.78275913748</v>
+      </c>
+      <c r="O68" s="8" t="n">
+        <v>0.00100958733954195</v>
+      </c>
+      <c r="P68" s="8" t="n">
+        <v>0.001028827685292678</v>
+      </c>
+      <c r="Q68" s="9" t="n">
+        <v>29715.11113997429</v>
+      </c>
+      <c r="R68" s="9" t="n">
+        <v>29159.40193761959</v>
+      </c>
+      <c r="S68" s="9" t="n">
+        <v>15895.49299276553</v>
+      </c>
+      <c r="T68" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U68" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="V68" s="13" t="n">
+        <v>-0.002652279535453661</v>
+      </c>
+      <c r="W68" s="12" t="n">
+        <v>0.02429986491981562</v>
+      </c>
+      <c r="X68" s="12" t="n">
+        <v>0.0107759958404503</v>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -6125,74 +6036,54 @@
       <c r="I69" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J69" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K69" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O69" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P69" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S69" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T69" s="6" t="n">
+      <c r="J69" s="8" t="n">
+        <v>6.200964464045625e-05</v>
+      </c>
+      <c r="K69" s="8" t="n">
+        <v>1.276541434040214e-05</v>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>483795.70910212</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>2350099.981091168</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>421111.5022436272</v>
+      </c>
+      <c r="O69" s="8" t="n">
+        <v>6.31196132058103e-05</v>
+      </c>
+      <c r="P69" s="8" t="n">
+        <v>1.186413852327784e-05</v>
+      </c>
+      <c r="Q69" s="9" t="n">
+        <v>475288.0836291062</v>
+      </c>
+      <c r="R69" s="9" t="n">
+        <v>2528628.601321451</v>
+      </c>
+      <c r="S69" s="9" t="n">
+        <v>418945.7670856027</v>
+      </c>
+      <c r="T69" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U69" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="V69" s="16" t="n">
-        <v>0.02537105988406112</v>
-      </c>
-      <c r="W69" s="17" t="n">
-        <v>-0.007091588740911248</v>
-      </c>
-      <c r="X69" s="16" t="n">
-        <v>0.01530257381782674</v>
-      </c>
-      <c r="Y69" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U69" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V69" s="12" t="n">
+        <v>0.01789993430521752</v>
+      </c>
+      <c r="W69" s="13" t="n">
+        <v>-0.07060294269272482</v>
+      </c>
+      <c r="X69" s="12" t="n">
+        <v>0.005169488101265163</v>
+      </c>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6226,74 +6117,54 @@
       <c r="I70" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="J70" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K70" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O70" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P70" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S70" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T70" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U70" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V70" s="16" t="n">
-        <v>0.02887614810497588</v>
-      </c>
-      <c r="W70" s="17" t="n">
-        <v>-0.03365897331391343</v>
-      </c>
-      <c r="X70" s="16" t="n">
-        <v>0.009452094625905216</v>
-      </c>
-      <c r="Y70" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J70" s="8" t="n">
+        <v>7.503651823156765e-05</v>
+      </c>
+      <c r="K70" s="8" t="n">
+        <v>1.789668329725321e-05</v>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>399805.330884597</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>1676288.254181959</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>340144.8525948331</v>
+      </c>
+      <c r="O70" s="8" t="n">
+        <v>7.67663119441556e-05</v>
+      </c>
+      <c r="P70" s="8" t="n">
+        <v>1.699530471050775e-05</v>
+      </c>
+      <c r="Q70" s="9" t="n">
+        <v>390796.4215061392</v>
+      </c>
+      <c r="R70" s="9" t="n">
+        <v>1765193.417300237</v>
+      </c>
+      <c r="S70" s="9" t="n">
+        <v>336479.0297778254</v>
+      </c>
+      <c r="T70" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U70" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V70" s="12" t="n">
+        <v>0.02305269158744383</v>
+      </c>
+      <c r="W70" s="13" t="n">
+        <v>-0.05036567791775138</v>
+      </c>
+      <c r="X70" s="12" t="n">
+        <v>0.01089465462209693</v>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6327,74 +6198,54 @@
       <c r="I71" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="J71" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K71" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O71" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P71" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S71" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T71" s="6" t="n">
+      <c r="J71" s="8" t="n">
+        <v>8.336489985103044e-05</v>
+      </c>
+      <c r="K71" s="8" t="n">
+        <v>1.898804046729888e-05</v>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>359863.6842796997</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>1579941.861387217</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>308466.2034286536</v>
+      </c>
+      <c r="O71" s="8" t="n">
+        <v>8.51992063782282e-05</v>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>1.799787677315041e-05</v>
+      </c>
+      <c r="Q71" s="9" t="n">
+        <v>352115.9559493996</v>
+      </c>
+      <c r="R71" s="9" t="n">
+        <v>1666863.284937843</v>
+      </c>
+      <c r="S71" s="9" t="n">
+        <v>305337.5965875937</v>
+      </c>
+      <c r="T71" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U71" s="7" t="n">
+      <c r="U71" s="11" t="n">
         <v>0.43</v>
       </c>
-      <c r="V71" s="16" t="n">
-        <v>0.02875254354440783</v>
-      </c>
-      <c r="W71" s="17" t="n">
-        <v>-0.03602147991427669</v>
-      </c>
-      <c r="X71" s="16" t="n">
-        <v>0.008669294045401888</v>
-      </c>
-      <c r="Y71" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V71" s="12" t="n">
+        <v>0.02200334349918975</v>
+      </c>
+      <c r="W71" s="13" t="n">
+        <v>-0.05214670233369945</v>
+      </c>
+      <c r="X71" s="12" t="n">
+        <v>0.01024638588901183</v>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6428,74 +6279,54 @@
       <c r="I72" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J72" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K72" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O72" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P72" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S72" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T72" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U72" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V72" s="16" t="n">
-        <v>0.02970775806231845</v>
-      </c>
-      <c r="W72" s="17" t="n">
-        <v>-0.04843977976254273</v>
-      </c>
-      <c r="X72" s="16" t="n">
-        <v>0.005532200352118438</v>
-      </c>
-      <c r="Y72" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J72" s="8" t="n">
+        <v>8.248975278455109e-05</v>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>1.70833717925836e-05</v>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>363681.536037025</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>1756093.607529158</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>316285.8555040548</v>
+      </c>
+      <c r="O72" s="8" t="n">
+        <v>8.387322812280044e-05</v>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>1.628780574469538e-05</v>
+      </c>
+      <c r="Q72" s="9" t="n">
+        <v>357682.6678958441</v>
+      </c>
+      <c r="R72" s="9" t="n">
+        <v>1841868.724998173</v>
+      </c>
+      <c r="S72" s="9" t="n">
+        <v>313901.7892937718</v>
+      </c>
+      <c r="T72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V72" s="12" t="n">
+        <v>0.01677148120279548</v>
+      </c>
+      <c r="W72" s="13" t="n">
+        <v>-0.04656961503545798</v>
+      </c>
+      <c r="X72" s="12" t="n">
+        <v>0.007594943041410174</v>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6529,74 +6360,54 @@
       <c r="I73" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J73" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K73" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O73" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P73" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S73" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T73" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U73" s="7" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="V73" s="16" t="n">
-        <v>0.02928280720016551</v>
-      </c>
-      <c r="W73" s="17" t="n">
-        <v>-0.03708666304070915</v>
-      </c>
-      <c r="X73" s="16" t="n">
-        <v>0.008532020540458993</v>
-      </c>
-      <c r="Y73" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J73" s="8" t="n">
+        <v>7.752681804163778e-05</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>1.772178445395437e-05</v>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>386962.8698534709</v>
+      </c>
+      <c r="M73" s="9" t="n">
+        <v>1692831.7844034</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>331505.2012990123</v>
+      </c>
+      <c r="O73" s="8" t="n">
+        <v>8.020894932171622e-05</v>
+      </c>
+      <c r="P73" s="8" t="n">
+        <v>1.673765255698627e-05</v>
+      </c>
+      <c r="Q73" s="9" t="n">
+        <v>374023.1015827261</v>
+      </c>
+      <c r="R73" s="9" t="n">
+        <v>1792366.038060579</v>
+      </c>
+      <c r="S73" s="9" t="n">
+        <v>324919.4753054369</v>
+      </c>
+      <c r="T73" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U73" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V73" s="12" t="n">
+        <v>0.03459617391543057</v>
+      </c>
+      <c r="W73" s="13" t="n">
+        <v>-0.05553232517442675</v>
+      </c>
+      <c r="X73" s="12" t="n">
+        <v>0.020268794252436</v>
+      </c>
+      <c r="Y73" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6630,74 +6441,54 @@
       <c r="I74" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="J74" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K74" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O74" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P74" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S74" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T74" s="6" t="n">
+      <c r="J74" s="8" t="n">
+        <v>6.085451909977859e-05</v>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>1.249869269603536e-05</v>
+      </c>
+      <c r="L74" s="9" t="n">
+        <v>492979.000471785</v>
+      </c>
+      <c r="M74" s="9" t="n">
+        <v>2400251.028614866</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>429248.1698151773</v>
+      </c>
+      <c r="O74" s="8" t="n">
+        <v>6.196684172323149e-05</v>
+      </c>
+      <c r="P74" s="8" t="n">
+        <v>1.147819944869917e-05</v>
+      </c>
+      <c r="Q74" s="9" t="n">
+        <v>484129.8856893806</v>
+      </c>
+      <c r="R74" s="9" t="n">
+        <v>2613650.349436985</v>
+      </c>
+      <c r="S74" s="9" t="n">
+        <v>427561.0326331753</v>
+      </c>
+      <c r="T74" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U74" s="7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="V74" s="16" t="n">
-        <v>0.02712887717991412</v>
-      </c>
-      <c r="W74" s="17" t="n">
-        <v>-0.01508977047310502</v>
-      </c>
-      <c r="X74" s="16" t="n">
-        <v>0.01445774206499895</v>
-      </c>
-      <c r="Y74" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U74" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V74" s="12" t="n">
+        <v>0.01827838983706553</v>
+      </c>
+      <c r="W74" s="13" t="n">
+        <v>-0.0816479988871075</v>
+      </c>
+      <c r="X74" s="12" t="n">
+        <v>0.003945956374021398</v>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6731,74 +6522,54 @@
       <c r="I75" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="J75" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K75" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O75" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P75" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S75" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T75" s="6" t="n">
+      <c r="J75" s="8" t="n">
+        <v>7.311346847993478e-05</v>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>1.608552583195047e-05</v>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>410321.1162555253</v>
+      </c>
+      <c r="M75" s="9" t="n">
+        <v>1865030.73094517</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>353632.0029412066</v>
+      </c>
+      <c r="O75" s="8" t="n">
+        <v>7.489190651832033e-05</v>
+      </c>
+      <c r="P75" s="8" t="n">
+        <v>1.543777501988897e-05</v>
+      </c>
+      <c r="Q75" s="9" t="n">
+        <v>400577.3306446844</v>
+      </c>
+      <c r="R75" s="9" t="n">
+        <v>1943285.21832648</v>
+      </c>
+      <c r="S75" s="9" t="n">
+        <v>348608.8613681519</v>
+      </c>
+      <c r="T75" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U75" s="7" t="n">
+      <c r="U75" s="11" t="n">
         <v>0.36</v>
       </c>
-      <c r="V75" s="16" t="n">
-        <v>0.02691917900304437</v>
-      </c>
-      <c r="W75" s="17" t="n">
-        <v>-0.009004231791526459</v>
-      </c>
-      <c r="X75" s="16" t="n">
-        <v>0.01542029392274613</v>
-      </c>
-      <c r="Y75" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V75" s="12" t="n">
+        <v>0.02432435603672167</v>
+      </c>
+      <c r="W75" s="13" t="n">
+        <v>-0.04026917234964655</v>
+      </c>
+      <c r="X75" s="12" t="n">
+        <v>0.01440910467204071</v>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6832,74 +6603,54 @@
       <c r="I76" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="J76" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K76" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O76" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P76" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S76" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T76" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U76" s="7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="V76" s="16" t="n">
-        <v>0.007592711530289886</v>
-      </c>
-      <c r="W76" s="16" t="n">
-        <v>0.03120525859684893</v>
-      </c>
-      <c r="X76" s="16" t="n">
-        <v>0.0154973921720118</v>
-      </c>
-      <c r="Y76" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J76" s="8" t="n">
+        <v>5.117770991375779e-05</v>
+      </c>
+      <c r="K76" s="8" t="n">
+        <v>1.389106786874661e-05</v>
+      </c>
+      <c r="L76" s="9" t="n">
+        <v>586192.7008956546</v>
+      </c>
+      <c r="M76" s="9" t="n">
+        <v>2159661.178209109</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>487456.7601426307</v>
+      </c>
+      <c r="O76" s="8" t="n">
+        <v>5.322455842323026e-05</v>
+      </c>
+      <c r="P76" s="8" t="n">
+        <v>1.290195882855432e-05</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>563649.5799823541</v>
+      </c>
+      <c r="R76" s="9" t="n">
+        <v>2325228.315998396</v>
+      </c>
+      <c r="S76" s="9" t="n">
+        <v>478238.6126218481</v>
+      </c>
+      <c r="T76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V76" s="12" t="n">
+        <v>0.03999492186973042</v>
+      </c>
+      <c r="W76" s="13" t="n">
+        <v>-0.07120467983729861</v>
+      </c>
+      <c r="X76" s="12" t="n">
+        <v>0.01927520546750894</v>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -6933,74 +6684,54 @@
       <c r="I77" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K77" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O77" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P77" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S77" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T77" s="6" t="n">
+      <c r="J77" s="8" t="n">
+        <v>7.609450288744647e-05</v>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>1.595268676633212e-05</v>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>394246.6125887418</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>1880560.963769093</v>
+      </c>
+      <c r="N77" s="9" t="n">
+        <v>342255.5272447443</v>
+      </c>
+      <c r="O77" s="8" t="n">
+        <v>7.747369455731815e-05</v>
+      </c>
+      <c r="P77" s="8" t="n">
+        <v>1.49375038261601e-05</v>
+      </c>
+      <c r="Q77" s="9" t="n">
+        <v>387228.2091543317</v>
+      </c>
+      <c r="R77" s="9" t="n">
+        <v>2008367.686404264</v>
+      </c>
+      <c r="S77" s="9" t="n">
+        <v>340162.9431920218</v>
+      </c>
+      <c r="T77" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U77" s="7" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V77" s="16" t="n">
-        <v>0.02807785643577917</v>
-      </c>
-      <c r="W77" s="17" t="n">
-        <v>-0.01584523996540423</v>
-      </c>
-      <c r="X77" s="16" t="n">
-        <v>0.01453057245152338</v>
-      </c>
-      <c r="Y77" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U77" s="11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V77" s="12" t="n">
+        <v>0.01812472146525046</v>
+      </c>
+      <c r="W77" s="13" t="n">
+        <v>-0.06363711361239488</v>
+      </c>
+      <c r="X77" s="12" t="n">
+        <v>0.006151710803905086</v>
+      </c>
+      <c r="Y77" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7034,74 +6765,54 @@
       <c r="I78" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J78" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K78" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O78" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P78" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S78" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T78" s="6" t="n">
+      <c r="J78" s="8" t="n">
+        <v>6.078624389462273e-05</v>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>1.265101452080475e-05</v>
+      </c>
+      <c r="L78" s="9" t="n">
+        <v>493532.7152637878</v>
+      </c>
+      <c r="M78" s="9" t="n">
+        <v>2371351.321324042</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>428905.5761751996</v>
+      </c>
+      <c r="O78" s="8" t="n">
+        <v>6.182389580642018e-05</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>1.147777168684755e-05</v>
+      </c>
+      <c r="Q78" s="9" t="n">
+        <v>485249.2650080555</v>
+      </c>
+      <c r="R78" s="9" t="n">
+        <v>2613747.756838306</v>
+      </c>
+      <c r="S78" s="9" t="n">
+        <v>428422.4603481162</v>
+      </c>
+      <c r="T78" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U78" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="V78" s="16" t="n">
-        <v>0.02908480028841356</v>
-      </c>
-      <c r="W78" s="17" t="n">
-        <v>-0.01703599285621407</v>
-      </c>
-      <c r="X78" s="16" t="n">
-        <v>0.01484651375692345</v>
-      </c>
-      <c r="Y78" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U78" s="11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V78" s="12" t="n">
+        <v>0.0170705055176017</v>
+      </c>
+      <c r="W78" s="13" t="n">
+        <v>-0.09273903148461284</v>
+      </c>
+      <c r="X78" s="12" t="n">
+        <v>0.001127662230152149</v>
+      </c>
+      <c r="Y78" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7135,74 +6846,54 @@
       <c r="I79" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="J79" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K79" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O79" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P79" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S79" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T79" s="6" t="n">
+      <c r="J79" s="8" t="n">
+        <v>0.0001057373753459552</v>
+      </c>
+      <c r="K79" s="8" t="n">
+        <v>3.347183113347076e-05</v>
+      </c>
+      <c r="L79" s="9" t="n">
+        <v>283721.8145603195</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>896276.0322365799</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>228749.2596874931</v>
+      </c>
+      <c r="O79" s="8" t="n">
+        <v>0.0001087378248093588</v>
+      </c>
+      <c r="P79" s="8" t="n">
+        <v>3.263727893466726e-05</v>
+      </c>
+      <c r="Q79" s="9" t="n">
+        <v>275892.9567755889</v>
+      </c>
+      <c r="R79" s="9" t="n">
+        <v>919194.2765833352</v>
+      </c>
+      <c r="S79" s="9" t="n">
+        <v>224939.7737461176</v>
+      </c>
+      <c r="T79" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U79" s="7" t="n">
+      <c r="U79" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="V79" s="16" t="n">
-        <v>0.02384259700177809</v>
-      </c>
-      <c r="W79" s="17" t="n">
-        <v>-6.673742502801977e-05</v>
-      </c>
-      <c r="X79" s="16" t="n">
-        <v>0.01517433803412101</v>
-      </c>
-      <c r="Y79" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V79" s="12" t="n">
+        <v>0.02837643220844743</v>
+      </c>
+      <c r="W79" s="13" t="n">
+        <v>-0.02493297111459725</v>
+      </c>
+      <c r="X79" s="12" t="n">
+        <v>0.01693558181344623</v>
+      </c>
+      <c r="Y79" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7236,74 +6927,54 @@
       <c r="I80" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="J80" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K80" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O80" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P80" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S80" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U80" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="V80" s="16" t="n">
-        <v>0.02956925545762166</v>
-      </c>
-      <c r="W80" s="17" t="n">
-        <v>-0.03587168994499602</v>
-      </c>
-      <c r="X80" s="16" t="n">
-        <v>0.008073716354650809</v>
-      </c>
-      <c r="Y80" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J80" s="8" t="n">
+        <v>7.506836631378157e-05</v>
+      </c>
+      <c r="K80" s="8" t="n">
+        <v>1.760407899833858e-05</v>
+      </c>
+      <c r="L80" s="9" t="n">
+        <v>399635.7117271165</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>1704150.498462959</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>340950.0395640988</v>
+      </c>
+      <c r="O80" s="8" t="n">
+        <v>7.785574972351582e-05</v>
+      </c>
+      <c r="P80" s="8" t="n">
+        <v>1.694088711428391e-05</v>
+      </c>
+      <c r="Q80" s="9" t="n">
+        <v>385327.9957682907</v>
+      </c>
+      <c r="R80" s="9" t="n">
+        <v>1770863.579788873</v>
+      </c>
+      <c r="S80" s="9" t="n">
+        <v>332653.8520085227</v>
+      </c>
+      <c r="T80" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>0.03713126509351672</v>
+      </c>
+      <c r="W80" s="13" t="n">
+        <v>-0.03767262599294519</v>
+      </c>
+      <c r="X80" s="12" t="n">
+        <v>0.0249394002368668</v>
+      </c>
+      <c r="Y80" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7337,74 +7008,54 @@
       <c r="I81" s="3" t="n">
         <v>894</v>
       </c>
-      <c r="J81" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K81" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P81" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S81" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="n">
+      <c r="J81" s="8" t="n">
+        <v>9.103369144592612e-05</v>
+      </c>
+      <c r="K81" s="8" t="n">
+        <v>2.682921778828021e-05</v>
+      </c>
+      <c r="L81" s="9" t="n">
+        <v>329548.319127759</v>
+      </c>
+      <c r="M81" s="9" t="n">
+        <v>1118183.923092416</v>
+      </c>
+      <c r="N81" s="9" t="n">
+        <v>269686.0419919757</v>
+      </c>
+      <c r="O81" s="8" t="n">
+        <v>9.333245453557871e-05</v>
+      </c>
+      <c r="P81" s="8" t="n">
+        <v>2.497947586827211e-05</v>
+      </c>
+      <c r="Q81" s="9" t="n">
+        <v>321431.597928927</v>
+      </c>
+      <c r="R81" s="9" t="n">
+        <v>1200985.967768233</v>
+      </c>
+      <c r="S81" s="9" t="n">
+        <v>267991.355360747</v>
+      </c>
+      <c r="T81" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="U81" s="7" t="n">
+      <c r="U81" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="V81" s="16" t="n">
-        <v>0.02944499699501742</v>
-      </c>
-      <c r="W81" s="17" t="n">
-        <v>-0.04778155168784919</v>
-      </c>
-      <c r="X81" s="16" t="n">
-        <v>0.01324325682337814</v>
-      </c>
-      <c r="Y81" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V81" s="12" t="n">
+        <v>0.02525178374226478</v>
+      </c>
+      <c r="W81" s="13" t="n">
+        <v>-0.06894505589410516</v>
+      </c>
+      <c r="X81" s="12" t="n">
+        <v>0.006323661555976301</v>
+      </c>
+      <c r="Y81" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7438,74 +7089,54 @@
       <c r="I82" s="3" t="n">
         <v>1251</v>
       </c>
-      <c r="J82" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K82" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O82" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P82" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S82" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T82" s="6" t="n">
+      <c r="J82" s="8" t="n">
+        <v>5.63515618939944e-05</v>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>1.149351857656254e-05</v>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>532372.1116450051</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>2610166.747472412</v>
+      </c>
+      <c r="N82" s="9" t="n">
+        <v>464012.9228021514</v>
+      </c>
+      <c r="O82" s="8" t="n">
+        <v>5.720488973795644e-05</v>
+      </c>
+      <c r="P82" s="8" t="n">
+        <v>1.102198354671438e-05</v>
+      </c>
+      <c r="Q82" s="9" t="n">
+        <v>524430.6935547588</v>
+      </c>
+      <c r="R82" s="9" t="n">
+        <v>2721833.132199049</v>
+      </c>
+      <c r="S82" s="9" t="n">
+        <v>460732.0384985926</v>
+      </c>
+      <c r="T82" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U82" s="7" t="n">
+      <c r="U82" s="11" t="n">
         <v>0.23</v>
       </c>
-      <c r="V82" s="16" t="n">
-        <v>0.02466009849518867</v>
-      </c>
-      <c r="W82" s="17" t="n">
-        <v>-0.02590025761712069</v>
-      </c>
-      <c r="X82" s="16" t="n">
-        <v>0.01473871975418196</v>
-      </c>
-      <c r="Y82" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V82" s="12" t="n">
+        <v>0.01514293154051827</v>
+      </c>
+      <c r="W82" s="13" t="n">
+        <v>-0.04102616850593577</v>
+      </c>
+      <c r="X82" s="12" t="n">
+        <v>0.007121024867839276</v>
+      </c>
+      <c r="Y82" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7539,74 +7170,54 @@
       <c r="I83" s="3" t="n">
         <v>1090</v>
       </c>
-      <c r="J83" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K83" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O83" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P83" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S83" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T83" s="6" t="n">
+      <c r="J83" s="8" t="n">
+        <v>6.040813012196459e-05</v>
+      </c>
+      <c r="K83" s="8" t="n">
+        <v>1.34303628854452e-05</v>
+      </c>
+      <c r="L83" s="9" t="n">
+        <v>496621.8940965349</v>
+      </c>
+      <c r="M83" s="9" t="n">
+        <v>2233744.557454341</v>
+      </c>
+      <c r="N83" s="9" t="n">
+        <v>427315.3846750979</v>
+      </c>
+      <c r="O83" s="8" t="n">
+        <v>6.205280492659416e-05</v>
+      </c>
+      <c r="P83" s="8" t="n">
+        <v>1.235746007488533e-05</v>
+      </c>
+      <c r="Q83" s="9" t="n">
+        <v>483459.2092249291</v>
+      </c>
+      <c r="R83" s="9" t="n">
+        <v>2427683.344166369</v>
+      </c>
+      <c r="S83" s="9" t="n">
+        <v>422809.1991098446</v>
+      </c>
+      <c r="T83" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U83" s="7" t="n">
+      <c r="U83" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="V83" s="16" t="n">
-        <v>0.02947546312149713</v>
-      </c>
-      <c r="W83" s="17" t="n">
-        <v>-0.0691440972024365</v>
-      </c>
-      <c r="X83" s="16" t="n">
-        <v>0.008959474068941549</v>
-      </c>
-      <c r="Y83" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V83" s="12" t="n">
+        <v>0.02722605055493288</v>
+      </c>
+      <c r="W83" s="13" t="n">
+        <v>-0.079886360458853</v>
+      </c>
+      <c r="X83" s="12" t="n">
+        <v>0.0106577282962157</v>
+      </c>
+      <c r="Y83" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7640,74 +7251,54 @@
       <c r="I84" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="J84" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K84" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O84" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P84" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S84" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T84" s="6" t="n">
+      <c r="J84" s="8" t="n">
+        <v>4.592632366274411e-05</v>
+      </c>
+      <c r="K84" s="8" t="n">
+        <v>7.618869694905184e-06</v>
+      </c>
+      <c r="L84" s="9" t="n">
+        <v>653220.1493048375</v>
+      </c>
+      <c r="M84" s="9" t="n">
+        <v>3937591.952788129</v>
+      </c>
+      <c r="N84" s="9" t="n">
+        <v>584811.7381955201</v>
+      </c>
+      <c r="O84" s="8" t="n">
+        <v>4.680693681223919e-05</v>
+      </c>
+      <c r="P84" s="8" t="n">
+        <v>6.894675086335634e-06</v>
+      </c>
+      <c r="Q84" s="9" t="n">
+        <v>640930.6406941701</v>
+      </c>
+      <c r="R84" s="9" t="n">
+        <v>4351184.0114781</v>
+      </c>
+      <c r="S84" s="9" t="n">
+        <v>581385.2513806247</v>
+      </c>
+      <c r="T84" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U84" s="7" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="V84" s="16" t="n">
-        <v>0.02785531471099252</v>
-      </c>
-      <c r="W84" s="17" t="n">
-        <v>-0.03895646647620556</v>
-      </c>
-      <c r="X84" s="16" t="n">
-        <v>0.01499565586382907</v>
-      </c>
-      <c r="Y84" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U84" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>0.019174475099766</v>
+      </c>
+      <c r="W84" s="13" t="n">
+        <v>-0.09505276209853364</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>0.005893659680493268</v>
+      </c>
+      <c r="Y84" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7741,74 +7332,54 @@
       <c r="I85" s="3" t="n">
         <v>933</v>
       </c>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K85" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O85" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P85" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S85" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T85" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U85" s="7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="V85" s="16" t="n">
-        <v>0.02974681935876975</v>
-      </c>
-      <c r="W85" s="17" t="n">
-        <v>-0.06397784909054448</v>
-      </c>
-      <c r="X85" s="16" t="n">
-        <v>0.01060840497871276</v>
-      </c>
-      <c r="Y85" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J85" s="8" t="n">
+        <v>6.233468527545303e-05</v>
+      </c>
+      <c r="K85" s="8" t="n">
+        <v>1.420868921808808e-05</v>
+      </c>
+      <c r="L85" s="9" t="n">
+        <v>481272.9841729672</v>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>2111384.065027555</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>412485.7287827052</v>
+      </c>
+      <c r="O85" s="8" t="n">
+        <v>6.424515669387969e-05</v>
+      </c>
+      <c r="P85" s="8" t="n">
+        <v>1.331151771442166e-05</v>
+      </c>
+      <c r="Q85" s="9" t="n">
+        <v>466961.2706051341</v>
+      </c>
+      <c r="R85" s="9" t="n">
+        <v>2253687.418940823</v>
+      </c>
+      <c r="S85" s="9" t="n">
+        <v>406076.9353352216</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U85" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>0.0306486093574454</v>
+      </c>
+      <c r="W85" s="13" t="n">
+        <v>-0.06314245388126949</v>
+      </c>
+      <c r="X85" s="12" t="n">
+        <v>0.01578221487066989</v>
+      </c>
+      <c r="Y85" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7842,74 +7413,54 @@
       <c r="I86" s="3" t="n">
         <v>887</v>
       </c>
-      <c r="J86" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K86" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O86" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P86" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S86" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T86" s="6" t="n">
+      <c r="J86" s="8" t="n">
+        <v>5.48761119567607e-05</v>
+      </c>
+      <c r="K86" s="8" t="n">
+        <v>9.709670607730128e-06</v>
+      </c>
+      <c r="L86" s="9" t="n">
+        <v>546685.9609813159</v>
+      </c>
+      <c r="M86" s="9" t="n">
+        <v>3089703.164195518</v>
+      </c>
+      <c r="N86" s="9" t="n">
+        <v>485637.2152837305</v>
+      </c>
+      <c r="O86" s="8" t="n">
+        <v>5.590477054964355e-05</v>
+      </c>
+      <c r="P86" s="8" t="n">
+        <v>8.64075740006776e-06</v>
+      </c>
+      <c r="Q86" s="9" t="n">
+        <v>536626.8335429431</v>
+      </c>
+      <c r="R86" s="9" t="n">
+        <v>3471917.866802364</v>
+      </c>
+      <c r="S86" s="9" t="n">
+        <v>484284.5627075023</v>
+      </c>
+      <c r="T86" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U86" s="7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="V86" s="16" t="n">
-        <v>0.02942884838337945</v>
-      </c>
-      <c r="W86" s="17" t="n">
-        <v>-0.06652006692015577</v>
-      </c>
-      <c r="X86" s="16" t="n">
-        <v>0.01144138106274604</v>
-      </c>
-      <c r="Y86" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U86" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>0.01874510704572852</v>
+      </c>
+      <c r="W86" s="13" t="n">
+        <v>-0.1100874839988267</v>
+      </c>
+      <c r="X86" s="12" t="n">
+        <v>0.002793094557187237</v>
+      </c>
+      <c r="Y86" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -7943,74 +7494,54 @@
       <c r="I87" s="3" t="n">
         <v>824</v>
       </c>
-      <c r="J87" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K87" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O87" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P87" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S87" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T87" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="U87" s="7" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="V87" s="16" t="n">
-        <v>0.02866748414870605</v>
-      </c>
-      <c r="W87" s="17" t="n">
-        <v>-0.03838887373040601</v>
-      </c>
-      <c r="X87" s="16" t="n">
-        <v>0.005344650798675589</v>
-      </c>
-      <c r="Y87" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J87" s="8" t="n">
+        <v>3.152634931356253e-05</v>
+      </c>
+      <c r="K87" s="8" t="n">
+        <v>1.470484301728102e-05</v>
+      </c>
+      <c r="L87" s="9" t="n">
+        <v>951584.9647423051</v>
+      </c>
+      <c r="M87" s="9" t="n">
+        <v>2040144.186833156</v>
+      </c>
+      <c r="N87" s="9" t="n">
+        <v>695006.9831234922</v>
+      </c>
+      <c r="O87" s="8" t="n">
+        <v>3.290770420716431e-05</v>
+      </c>
+      <c r="P87" s="8" t="n">
+        <v>1.480201583534361e-05</v>
+      </c>
+      <c r="Q87" s="9" t="n">
+        <v>911640.6240660424</v>
+      </c>
+      <c r="R87" s="9" t="n">
+        <v>2026750.973226721</v>
+      </c>
+      <c r="S87" s="9" t="n">
+        <v>672964.4051204396</v>
+      </c>
+      <c r="T87" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U87" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>0.043815884924155</v>
+      </c>
+      <c r="W87" s="12" t="n">
+        <v>0.006608218662953025</v>
+      </c>
+      <c r="X87" s="12" t="n">
+        <v>0.03275444857905629</v>
+      </c>
+      <c r="Y87" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8044,74 +7575,54 @@
       <c r="I88" s="3" t="n">
         <v>794</v>
       </c>
-      <c r="J88" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K88" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O88" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P88" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S88" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T88" s="6" t="n">
+      <c r="J88" s="8" t="n">
+        <v>4.496612774801311e-05</v>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>1.864027450936036e-05</v>
+      </c>
+      <c r="L88" s="9" t="n">
+        <v>667168.8558133759</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>1609418.358347419</v>
+      </c>
+      <c r="N88" s="9" t="n">
+        <v>503884.6780405871</v>
+      </c>
+      <c r="O88" s="8" t="n">
+        <v>4.548920992495928e-05</v>
+      </c>
+      <c r="P88" s="8" t="n">
+        <v>1.930220518896903e-05</v>
+      </c>
+      <c r="Q88" s="9" t="n">
+        <v>659497.0554443379</v>
+      </c>
+      <c r="R88" s="9" t="n">
+        <v>1554226.561488665</v>
+      </c>
+      <c r="S88" s="9" t="n">
+        <v>494923.8719624552</v>
+      </c>
+      <c r="T88" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="U88" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="V88" s="16" t="n">
-        <v>0.02612879221121276</v>
-      </c>
-      <c r="W88" s="17" t="n">
-        <v>-0.006826624824500502</v>
-      </c>
-      <c r="X88" s="16" t="n">
-        <v>0.01452374068536581</v>
-      </c>
-      <c r="Y88" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U88" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>0.01163280458298499</v>
+      </c>
+      <c r="W88" s="12" t="n">
+        <v>0.03551077959051874</v>
+      </c>
+      <c r="X88" s="12" t="n">
+        <v>0.01810542304738871</v>
+      </c>
+      <c r="Y88" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8145,74 +7656,54 @@
       <c r="I89" s="3" t="n">
         <v>597</v>
       </c>
-      <c r="J89" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K89" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O89" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P89" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S89" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T89" s="6" t="n">
+      <c r="J89" s="8" t="n">
+        <v>4.334433484403352e-05</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>8.454691556704626e-06</v>
+      </c>
+      <c r="L89" s="9" t="n">
+        <v>692131.9731390362</v>
+      </c>
+      <c r="M89" s="9" t="n">
+        <v>3548325.778509306</v>
+      </c>
+      <c r="N89" s="9" t="n">
+        <v>607045.3046615764</v>
+      </c>
+      <c r="O89" s="8" t="n">
+        <v>4.419966839515391e-05</v>
+      </c>
+      <c r="P89" s="8" t="n">
+        <v>7.565832798096206e-06</v>
+      </c>
+      <c r="Q89" s="9" t="n">
+        <v>678738.1238201603</v>
+      </c>
+      <c r="R89" s="9" t="n">
+        <v>3965194.685183753</v>
+      </c>
+      <c r="S89" s="9" t="n">
+        <v>605398.358829809</v>
+      </c>
+      <c r="T89" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U89" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V89" s="16" t="n">
-        <v>0.02907545796689225</v>
-      </c>
-      <c r="W89" s="17" t="n">
-        <v>-0.03832303552206908</v>
-      </c>
-      <c r="X89" s="16" t="n">
-        <v>0.01057698075853308</v>
-      </c>
-      <c r="Y89" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U89" s="11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>0.01973345661429904</v>
+      </c>
+      <c r="W89" s="13" t="n">
+        <v>-0.1051320148874679</v>
+      </c>
+      <c r="X89" s="12" t="n">
+        <v>0.002720433261416133</v>
+      </c>
+      <c r="Y89" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8246,74 +7737,54 @@
       <c r="I90" s="3" t="n">
         <v>821</v>
       </c>
-      <c r="J90" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K90" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O90" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P90" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S90" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U90" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V90" s="16" t="n">
-        <v>0.02972514556506745</v>
-      </c>
-      <c r="W90" s="17" t="n">
-        <v>-0.03055503967544428</v>
-      </c>
-      <c r="X90" s="16" t="n">
-        <v>0.01201241110171115</v>
-      </c>
-      <c r="Y90" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="J90" s="8" t="n">
+        <v>3.648023203496822e-05</v>
+      </c>
+      <c r="K90" s="8" t="n">
+        <v>9.150500427176857e-06</v>
+      </c>
+      <c r="L90" s="9" t="n">
+        <v>822363.1903230062</v>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>3278509.218020516</v>
+      </c>
+      <c r="N90" s="9" t="n">
+        <v>693670.7616069207</v>
+      </c>
+      <c r="O90" s="8" t="n">
+        <v>3.765314843313517e-05</v>
+      </c>
+      <c r="P90" s="8" t="n">
+        <v>9.068005335499695e-06</v>
+      </c>
+      <c r="Q90" s="9" t="n">
+        <v>796746.1221277232</v>
+      </c>
+      <c r="R90" s="9" t="n">
+        <v>3308335.062679674</v>
+      </c>
+      <c r="S90" s="9" t="n">
+        <v>676756.0256427254</v>
+      </c>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>0.03215210903929155</v>
+      </c>
+      <c r="W90" s="13" t="n">
+        <v>-0.009015363950167443</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>0.02499384611778099</v>
+      </c>
+      <c r="Y90" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정4회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8347,74 +7818,54 @@
       <c r="I91" s="3" t="n">
         <v>386</v>
       </c>
-      <c r="J91" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K91" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O91" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P91" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S91" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T91" s="6" t="n">
+      <c r="J91" s="8" t="n">
+        <v>4.723891022309342e-05</v>
+      </c>
+      <c r="K91" s="8" t="n">
+        <v>1.947088617557152e-05</v>
+      </c>
+      <c r="L91" s="9" t="n">
+        <v>635069.6884902748</v>
+      </c>
+      <c r="M91" s="9" t="n">
+        <v>1540761.921644762</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>480382.3043585097</v>
+      </c>
+      <c r="O91" s="8" t="n">
+        <v>4.811948967034048e-05</v>
+      </c>
+      <c r="P91" s="8" t="n">
+        <v>1.864035164595124e-05</v>
+      </c>
+      <c r="Q91" s="9" t="n">
+        <v>623448.0083958822</v>
+      </c>
+      <c r="R91" s="9" t="n">
+        <v>1609411.698331138</v>
+      </c>
+      <c r="S91" s="9" t="n">
+        <v>479343.4410592586</v>
+      </c>
+      <c r="T91" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U91" s="7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="V91" s="16" t="n">
-        <v>0.02355500554369445</v>
-      </c>
-      <c r="W91" s="17" t="n">
-        <v>-0.001920721751912629</v>
-      </c>
-      <c r="X91" s="16" t="n">
-        <v>0.01491744813313128</v>
-      </c>
-      <c r="Y91" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U91" s="11" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>0.01864097717513769</v>
+      </c>
+      <c r="W91" s="13" t="n">
+        <v>-0.04265519926166927</v>
+      </c>
+      <c r="X91" s="12" t="n">
+        <v>0.002167262989883456</v>
+      </c>
+      <c r="Y91" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정2회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8448,74 +7899,54 @@
       <c r="I92" s="3" t="n">
         <v>673</v>
       </c>
-      <c r="J92" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K92" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O92" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P92" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S92" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T92" s="6" t="n">
+      <c r="J92" s="8" t="n">
+        <v>3.205111098714966e-05</v>
+      </c>
+      <c r="K92" s="8" t="n">
+        <v>1.46405237960566e-05</v>
+      </c>
+      <c r="L92" s="9" t="n">
+        <v>936004.9956467339</v>
+      </c>
+      <c r="M92" s="9" t="n">
+        <v>2049107.014059186</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>687858.6270742761</v>
+      </c>
+      <c r="O92" s="8" t="n">
+        <v>3.298756192648303e-05</v>
+      </c>
+      <c r="P92" s="8" t="n">
+        <v>1.437628107249013e-05</v>
+      </c>
+      <c r="Q92" s="9" t="n">
+        <v>909433.6849403667</v>
+      </c>
+      <c r="R92" s="9" t="n">
+        <v>2086770.552740986</v>
+      </c>
+      <c r="S92" s="9" t="n">
+        <v>677424.1380194816</v>
+      </c>
+      <c r="T92" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U92" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="V92" s="16" t="n">
-        <v>0.02931514578294265</v>
-      </c>
-      <c r="W92" s="17" t="n">
-        <v>-0.01392091417200891</v>
-      </c>
-      <c r="X92" s="16" t="n">
-        <v>0.01408833019756016</v>
-      </c>
-      <c r="Y92" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U92" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <v>0.02921742524647031</v>
+      </c>
+      <c r="W92" s="13" t="n">
+        <v>-0.01804872060913876</v>
+      </c>
+      <c r="X92" s="12" t="n">
+        <v>0.01540318460647239</v>
+      </c>
+      <c r="Y92" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8792,74 +8223,54 @@
       <c r="I96" s="3" t="n">
         <v>924</v>
       </c>
-      <c r="J96" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K96" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O96" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P96" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S96" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T96" s="6" t="n">
+      <c r="J96" s="8" t="n">
+        <v>0.0006567761660575405</v>
+      </c>
+      <c r="K96" s="8" t="n">
+        <v>9.078585160836005e-05</v>
+      </c>
+      <c r="L96" s="9" t="n">
+        <v>45677.66242201256</v>
+      </c>
+      <c r="M96" s="9" t="n">
+        <v>330447.9659387525</v>
+      </c>
+      <c r="N96" s="9" t="n">
+        <v>41699.84521770157</v>
+      </c>
+      <c r="O96" s="8" t="n">
+        <v>0.00066825009764345</v>
+      </c>
+      <c r="P96" s="8" t="n">
+        <v>9.011201613655475e-05</v>
+      </c>
+      <c r="Q96" s="9" t="n">
+        <v>44893.3716669754</v>
+      </c>
+      <c r="R96" s="9" t="n">
+        <v>332918.9744743734</v>
+      </c>
+      <c r="S96" s="9" t="n">
+        <v>41081.63340474508</v>
+      </c>
+      <c r="T96" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U96" s="7" t="n">
+      <c r="U96" s="11" t="n">
         <v>0.19</v>
       </c>
-      <c r="V96" s="16" t="n">
-        <v>0.01867401552135085</v>
-      </c>
-      <c r="W96" s="16" t="n">
-        <v>0.00175453053249147</v>
-      </c>
-      <c r="X96" s="16" t="n">
-        <v>0.01509851746875004</v>
-      </c>
-      <c r="Y96" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V96" s="12" t="n">
+        <v>0.01747007912114817</v>
+      </c>
+      <c r="W96" s="13" t="n">
+        <v>-0.007422252034514742</v>
+      </c>
+      <c r="X96" s="12" t="n">
+        <v>0.01504837470471876</v>
+      </c>
+      <c r="Y96" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8893,74 +8304,54 @@
       <c r="I97" s="3" t="n">
         <v>935</v>
       </c>
-      <c r="J97" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K97" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O97" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P97" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S97" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T97" s="6" t="n">
+      <c r="J97" s="8" t="n">
+        <v>0.0005647183730343385</v>
+      </c>
+      <c r="K97" s="8" t="n">
+        <v>7.084264858575808e-05</v>
+      </c>
+      <c r="L97" s="9" t="n">
+        <v>53123.82495863262</v>
+      </c>
+      <c r="M97" s="9" t="n">
+        <v>423473.720970267</v>
+      </c>
+      <c r="N97" s="9" t="n">
+        <v>48936.02698517546</v>
+      </c>
+      <c r="O97" s="8" t="n">
+        <v>0.0005752529939308754</v>
+      </c>
+      <c r="P97" s="8" t="n">
+        <v>7.049801334494237e-05</v>
+      </c>
+      <c r="Q97" s="9" t="n">
+        <v>52150.9671683776</v>
+      </c>
+      <c r="R97" s="9" t="n">
+        <v>425543.9065099874</v>
+      </c>
+      <c r="S97" s="9" t="n">
+        <v>48137.80101505465</v>
+      </c>
+      <c r="T97" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U97" s="7" t="n">
+      <c r="U97" s="11" t="n">
         <v>0.17</v>
       </c>
-      <c r="V97" s="16" t="n">
-        <v>0.01793395011190457</v>
-      </c>
-      <c r="W97" s="16" t="n">
-        <v>0.003137755108694362</v>
-      </c>
-      <c r="X97" s="16" t="n">
-        <v>0.01493487641320354</v>
-      </c>
-      <c r="Y97" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V97" s="12" t="n">
+        <v>0.01865464521710591</v>
+      </c>
+      <c r="W97" s="13" t="n">
+        <v>-0.004864798926857095</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>0.01658210290642836</v>
+      </c>
+      <c r="Y97" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -8994,74 +8385,54 @@
       <c r="I98" s="3" t="n">
         <v>911</v>
       </c>
-      <c r="J98" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K98" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O98" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P98" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S98" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T98" s="6" t="n">
+      <c r="J98" s="8" t="n">
+        <v>0.0005482416739919038</v>
+      </c>
+      <c r="K98" s="8" t="n">
+        <v>6.640749720936246e-05</v>
+      </c>
+      <c r="L98" s="9" t="n">
+        <v>54720.39325569954</v>
+      </c>
+      <c r="M98" s="9" t="n">
+        <v>451756.221220312</v>
+      </c>
+      <c r="N98" s="9" t="n">
+        <v>50560.04911339481</v>
+      </c>
+      <c r="O98" s="8" t="n">
+        <v>0.0005599045710225361</v>
+      </c>
+      <c r="P98" s="8" t="n">
+        <v>6.65108021418182e-05</v>
+      </c>
+      <c r="Q98" s="9" t="n">
+        <v>53580.55917495359</v>
+      </c>
+      <c r="R98" s="9" t="n">
+        <v>451054.5510492003</v>
+      </c>
+      <c r="S98" s="9" t="n">
+        <v>49588.27589383747</v>
+      </c>
+      <c r="T98" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U98" s="7" t="n">
+      <c r="U98" s="11" t="n">
         <v>0.16</v>
       </c>
-      <c r="V98" s="16" t="n">
-        <v>0.01689460780279663</v>
-      </c>
-      <c r="W98" s="16" t="n">
-        <v>0.00645313627565719</v>
-      </c>
-      <c r="X98" s="16" t="n">
-        <v>0.01483877013054853</v>
-      </c>
-      <c r="Y98" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V98" s="12" t="n">
+        <v>0.02127327706723081</v>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>0.00155562153065425</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>0.01959683417180691</v>
+      </c>
+      <c r="Y98" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -9095,74 +8466,54 @@
       <c r="I99" s="3" t="n">
         <v>881</v>
       </c>
-      <c r="J99" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K99" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O99" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P99" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S99" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T99" s="6" t="n">
+      <c r="J99" s="8" t="n">
+        <v>0.0005306584484238895</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>8.822501012990453e-05</v>
+      </c>
+      <c r="L99" s="9" t="n">
+        <v>56533.53883105621</v>
+      </c>
+      <c r="M99" s="9" t="n">
+        <v>340039.6322519806</v>
+      </c>
+      <c r="N99" s="9" t="n">
+        <v>50600.13230534424</v>
+      </c>
+      <c r="O99" s="8" t="n">
+        <v>0.0005463964402433055</v>
+      </c>
+      <c r="P99" s="8" t="n">
+        <v>8.585695046484032e-05</v>
+      </c>
+      <c r="Q99" s="9" t="n">
+        <v>54905.18932854187</v>
+      </c>
+      <c r="R99" s="9" t="n">
+        <v>349418.4202627304</v>
+      </c>
+      <c r="S99" s="9" t="n">
+        <v>49459.97447262645</v>
+      </c>
+      <c r="T99" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U99" s="7" t="n">
+      <c r="U99" s="11" t="n">
         <v>0.21</v>
       </c>
-      <c r="V99" s="16" t="n">
-        <v>0.02574779277206688</v>
-      </c>
-      <c r="W99" s="17" t="n">
-        <v>-0.01369104192130139</v>
-      </c>
-      <c r="X99" s="16" t="n">
-        <v>0.01506559469777546</v>
-      </c>
-      <c r="Y99" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V99" s="12" t="n">
+        <v>0.02965747905485983</v>
+      </c>
+      <c r="W99" s="13" t="n">
+        <v>-0.02684113792197262</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>0.02305213144314933</v>
+      </c>
+      <c r="Y99" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -9196,74 +8547,54 @@
       <c r="I100" s="3" t="n">
         <v>797</v>
       </c>
-      <c r="J100" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K100" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O100" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P100" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S100" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T100" s="6" t="n">
+      <c r="J100" s="8" t="n">
+        <v>0.0003843471220020855</v>
+      </c>
+      <c r="K100" s="8" t="n">
+        <v>6.357260878208555e-05</v>
+      </c>
+      <c r="L100" s="9" t="n">
+        <v>78054.44163007736</v>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>471901.3514583635</v>
+      </c>
+      <c r="N100" s="9" t="n">
+        <v>69904.31482034622</v>
+      </c>
+      <c r="O100" s="8" t="n">
+        <v>0.0003907067301265338</v>
+      </c>
+      <c r="P100" s="8" t="n">
+        <v>5.764504921524471e-05</v>
+      </c>
+      <c r="Q100" s="9" t="n">
+        <v>76783.93456463942</v>
+      </c>
+      <c r="R100" s="9" t="n">
+        <v>520426.3056135314</v>
+      </c>
+      <c r="S100" s="9" t="n">
+        <v>69638.5579965644</v>
+      </c>
+      <c r="T100" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U100" s="7" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="V100" s="16" t="n">
-        <v>0.02963984666987799</v>
-      </c>
-      <c r="W100" s="17" t="n">
-        <v>-0.02456489365686738</v>
-      </c>
-      <c r="X100" s="16" t="n">
-        <v>0.01527920665522548</v>
-      </c>
-      <c r="Y100" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U100" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V100" s="12" t="n">
+        <v>0.01654652203799722</v>
+      </c>
+      <c r="W100" s="13" t="n">
+        <v>-0.09324077901473826</v>
+      </c>
+      <c r="X100" s="12" t="n">
+        <v>0.003816230999426073</v>
+      </c>
+      <c r="Y100" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -9297,74 +8628,54 @@
       <c r="I101" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="J101" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K101" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O101" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P101" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S101" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T101" s="6" t="n">
+      <c r="J101" s="8" t="n">
+        <v>0.0006326935904949823</v>
+      </c>
+      <c r="K101" s="8" t="n">
+        <v>0.0001516227870653128</v>
+      </c>
+      <c r="L101" s="9" t="n">
+        <v>47416.3172358515</v>
+      </c>
+      <c r="M101" s="9" t="n">
+        <v>197859.4417149003</v>
+      </c>
+      <c r="N101" s="9" t="n">
+        <v>40308.63264557783</v>
+      </c>
+      <c r="O101" s="8" t="n">
+        <v>0.0006512499927124694</v>
+      </c>
+      <c r="P101" s="8" t="n">
+        <v>0.0001410107226514595</v>
+      </c>
+      <c r="Q101" s="9" t="n">
+        <v>46065.25963255583</v>
+      </c>
+      <c r="R101" s="9" t="n">
+        <v>212749.7784275024</v>
+      </c>
+      <c r="S101" s="9" t="n">
+        <v>39797.98490344015</v>
+      </c>
+      <c r="T101" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U101" s="7" t="n">
+      <c r="U101" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="V101" s="16" t="n">
-        <v>0.02924870948886847</v>
-      </c>
-      <c r="W101" s="17" t="n">
-        <v>-0.04782450641342928</v>
-      </c>
-      <c r="X101" s="16" t="n">
-        <v>0.005451314681941837</v>
-      </c>
-      <c r="Y101" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V101" s="12" t="n">
+        <v>0.02932920847668097</v>
+      </c>
+      <c r="W101" s="13" t="n">
+        <v>-0.06998990467891963</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>0.01283099492038708</v>
+      </c>
+      <c r="Y101" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -9884,74 +9195,54 @@
       <c r="I108" s="3" t="n">
         <v>1553</v>
       </c>
-      <c r="J108" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K108" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O108" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P108" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S108" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T108" s="6" t="n">
+      <c r="J108" s="8" t="n">
+        <v>0.0007184363909783574</v>
+      </c>
+      <c r="K108" s="8" t="n">
+        <v>0.0001202721386835627</v>
+      </c>
+      <c r="L108" s="9" t="n">
+        <v>41757.35023548346</v>
+      </c>
+      <c r="M108" s="9" t="n">
+        <v>249434.3272545467</v>
+      </c>
+      <c r="N108" s="9" t="n">
+        <v>37344.39035572601</v>
+      </c>
+      <c r="O108" s="8" t="n">
+        <v>0.0007316718360285574</v>
+      </c>
+      <c r="P108" s="8" t="n">
+        <v>0.0001085265983433326</v>
+      </c>
+      <c r="Q108" s="9" t="n">
+        <v>41001.98821761002</v>
+      </c>
+      <c r="R108" s="9" t="n">
+        <v>276429.9301549339</v>
+      </c>
+      <c r="S108" s="9" t="n">
+        <v>37165.79460770459</v>
+      </c>
+      <c r="T108" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U108" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="V108" s="16" t="n">
-        <v>0.02974507459287388</v>
-      </c>
-      <c r="W108" s="17" t="n">
-        <v>-0.02513603623759195</v>
-      </c>
-      <c r="X108" s="16" t="n">
-        <v>0.0148719916698425</v>
-      </c>
-      <c r="Y108" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U108" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>0.01842257048279006</v>
+      </c>
+      <c r="W108" s="13" t="n">
+        <v>-0.09765803176688091</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>0.004805379513785457</v>
+      </c>
+      <c r="Y108" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -9985,74 +9276,54 @@
       <c r="I109" s="3" t="n">
         <v>1568</v>
       </c>
-      <c r="J109" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K109" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O109" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P109" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S109" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T109" s="6" t="n">
+      <c r="J109" s="8" t="n">
+        <v>0.0007838546773348444</v>
+      </c>
+      <c r="K109" s="8" t="n">
+        <v>0.0001322158892197082</v>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>38272.40031532618</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>226901.6241319366</v>
+      </c>
+      <c r="N109" s="9" t="n">
+        <v>34197.18905921809</v>
+      </c>
+      <c r="O109" s="8" t="n">
+        <v>0.0007979616370985518</v>
+      </c>
+      <c r="P109" s="8" t="n">
+        <v>0.0001188236354673356</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>37595.79233543387</v>
+      </c>
+      <c r="R109" s="9" t="n">
+        <v>252475.0221789581</v>
+      </c>
+      <c r="S109" s="9" t="n">
+        <v>34064.29738509287</v>
+      </c>
+      <c r="T109" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U109" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="V109" s="16" t="n">
-        <v>0.02950243701682774</v>
-      </c>
-      <c r="W109" s="17" t="n">
-        <v>-0.02735801428920922</v>
-      </c>
-      <c r="X109" s="16" t="n">
-        <v>0.01402890785031544</v>
-      </c>
-      <c r="Y109" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U109" s="11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V109" s="12" t="n">
+        <v>0.017996907043627</v>
+      </c>
+      <c r="W109" s="13" t="n">
+        <v>-0.1012908042400122</v>
+      </c>
+      <c r="X109" s="12" t="n">
+        <v>0.00390120109106884</v>
+      </c>
+      <c r="Y109" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -10086,74 +9357,54 @@
       <c r="I110" s="3" t="n">
         <v>1727</v>
       </c>
-      <c r="J110" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K110" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O110" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P110" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S110" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T110" s="6" t="n">
+      <c r="J110" s="8" t="n">
+        <v>0.0006640893365805279</v>
+      </c>
+      <c r="K110" s="8" t="n">
+        <v>0.0001045974947787894</v>
+      </c>
+      <c r="L110" s="9" t="n">
+        <v>45174.6449573689</v>
+      </c>
+      <c r="M110" s="9" t="n">
+        <v>286813.7526949975</v>
+      </c>
+      <c r="N110" s="9" t="n">
+        <v>40683.77421810018</v>
+      </c>
+      <c r="O110" s="8" t="n">
+        <v>0.000674331277507803</v>
+      </c>
+      <c r="P110" s="8" t="n">
+        <v>9.715063974122122e-05</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>44488.51921992133</v>
+      </c>
+      <c r="R110" s="9" t="n">
+        <v>308798.790001904</v>
+      </c>
+      <c r="S110" s="9" t="n">
+        <v>40447.38389561433</v>
+      </c>
+      <c r="T110" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U110" s="7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="V110" s="16" t="n">
-        <v>0.02551239961796974</v>
-      </c>
-      <c r="W110" s="17" t="n">
-        <v>-0.01336712455814691</v>
-      </c>
-      <c r="X110" s="16" t="n">
-        <v>0.01523126619972368</v>
-      </c>
-      <c r="Y110" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U110" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V110" s="12" t="n">
+        <v>0.01542253483546663</v>
+      </c>
+      <c r="W110" s="13" t="n">
+        <v>-0.07119534797001947</v>
+      </c>
+      <c r="X110" s="12" t="n">
+        <v>0.005844390902905339</v>
+      </c>
+      <c r="Y110" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -10187,74 +9438,54 @@
       <c r="I111" s="3" t="n">
         <v>1742</v>
       </c>
-      <c r="J111" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K111" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O111" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P111" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S111" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T111" s="6" t="n">
+      <c r="J111" s="8" t="n">
+        <v>0.0009965206449390009</v>
+      </c>
+      <c r="K111" s="8" t="n">
+        <v>0.0002053983059384486</v>
+      </c>
+      <c r="L111" s="9" t="n">
+        <v>30104.74509721408</v>
+      </c>
+      <c r="M111" s="9" t="n">
+        <v>146057.6797989271</v>
+      </c>
+      <c r="N111" s="9" t="n">
+        <v>26199.48113645749</v>
+      </c>
+      <c r="O111" s="8" t="n">
+        <v>0.001016720563638797</v>
+      </c>
+      <c r="P111" s="8" t="n">
+        <v>0.0001833653118186537</v>
+      </c>
+      <c r="Q111" s="9" t="n">
+        <v>29506.63247395268</v>
+      </c>
+      <c r="R111" s="9" t="n">
+        <v>163607.8258338724</v>
+      </c>
+      <c r="S111" s="9" t="n">
+        <v>26148.65813462537</v>
+      </c>
+      <c r="T111" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U111" s="7" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="V111" s="16" t="n">
-        <v>0.02936986803801268</v>
-      </c>
-      <c r="W111" s="17" t="n">
-        <v>-0.04548635785371302</v>
-      </c>
-      <c r="X111" s="16" t="n">
-        <v>0.006935690923445379</v>
-      </c>
-      <c r="Y111" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U111" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>0.02027044678139345</v>
+      </c>
+      <c r="W111" s="13" t="n">
+        <v>-0.1072696000053549</v>
+      </c>
+      <c r="X111" s="12" t="n">
+        <v>0.001943617969628164</v>
+      </c>
+      <c r="Y111" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -10288,74 +9519,54 @@
       <c r="I112" s="3" t="n">
         <v>1826</v>
       </c>
-      <c r="J112" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K112" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O112" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P112" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S112" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T112" s="6" t="n">
+      <c r="J112" s="8" t="n">
+        <v>0.001405419258883003</v>
+      </c>
+      <c r="K112" s="8" t="n">
+        <v>0.000380284654270251</v>
+      </c>
+      <c r="L112" s="9" t="n">
+        <v>21345.94343316695</v>
+      </c>
+      <c r="M112" s="9" t="n">
+        <v>78888.27398930583</v>
+      </c>
+      <c r="N112" s="9" t="n">
+        <v>17760.86093020571</v>
+      </c>
+      <c r="O112" s="8" t="n">
+        <v>0.001436237277879972</v>
+      </c>
+      <c r="P112" s="8" t="n">
+        <v>0.000369297119447909</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>20887.9134820139</v>
+      </c>
+      <c r="R112" s="9" t="n">
+        <v>81235.40211970604</v>
+      </c>
+      <c r="S112" s="9" t="n">
+        <v>17542.34941164629</v>
+      </c>
+      <c r="T112" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U112" s="7" t="n">
+      <c r="U112" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="V112" s="16" t="n">
-        <v>0.02416387611193758</v>
-      </c>
-      <c r="W112" s="17" t="n">
-        <v>-0.003744039362997077</v>
-      </c>
-      <c r="X112" s="16" t="n">
-        <v>0.01477285728386729</v>
-      </c>
-      <c r="Y112" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="V112" s="12" t="n">
+        <v>0.02192798967438514</v>
+      </c>
+      <c r="W112" s="13" t="n">
+        <v>-0.02889292191773174</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>0.0124562288341119</v>
+      </c>
+      <c r="Y112" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측, 저속, κ클립</t>
         </is>
       </c>
     </row>
@@ -10389,111 +9600,91 @@
       <c r="I113" s="3" t="n">
         <v>1671</v>
       </c>
-      <c r="J113" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K113" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="O113" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P113" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S113" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T113" s="6" t="n">
+      <c r="J113" s="8" t="n">
+        <v>0.0006486469456098391</v>
+      </c>
+      <c r="K113" s="8" t="n">
+        <v>0.0001012688064952733</v>
+      </c>
+      <c r="L113" s="9" t="n">
+        <v>46250.12143053393</v>
+      </c>
+      <c r="M113" s="9" t="n">
+        <v>296241.2715054586</v>
+      </c>
+      <c r="N113" s="9" t="n">
+        <v>41692.96773193261</v>
+      </c>
+      <c r="O113" s="8" t="n">
+        <v>0.0006575666949875927</v>
+      </c>
+      <c r="P113" s="8" t="n">
+        <v>9.368947946171168e-05</v>
+      </c>
+      <c r="Q113" s="9" t="n">
+        <v>45622.74857999926</v>
+      </c>
+      <c r="R113" s="9" t="n">
+        <v>320206.7102129666</v>
+      </c>
+      <c r="S113" s="9" t="n">
+        <v>41525.13104189937</v>
+      </c>
+      <c r="T113" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U113" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V113" s="16" t="n">
-        <v>0.02574682808752476</v>
-      </c>
-      <c r="W113" s="17" t="n">
-        <v>-0.01473735185138939</v>
-      </c>
-      <c r="X113" s="16" t="n">
-        <v>0.01507211403847456</v>
-      </c>
-      <c r="Y113" s="18" t="inlineStr">
-        <is>
-          <t>저속, κ클립</t>
+      <c r="U113" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>0.01375131639503424</v>
+      </c>
+      <c r="W113" s="13" t="n">
+        <v>-0.07484364925259956</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>0.004041810003293955</v>
+      </c>
+      <c r="Y113" s="3" t="inlineStr">
+        <is>
+          <t>MASTA 실측(보정1회), 저속, κ클립</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="19" t="inlineStr">
+      <c r="A115" s="14" t="inlineStr">
         <is>
           <t>■ 전 DLC 합산 (MASTA 기반)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>Σ D30 (상위 70 DLC 부분합, MASTA 참값)</t>
-        </is>
-      </c>
-      <c r="J116" s="14" t="n">
-        <v>6.734895578379972</v>
-      </c>
-      <c r="K116" s="14" t="n">
-        <v>1.237953692805305</v>
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>Σ D30 (상위 111 DLC 부분합, MASTA 참값)</t>
+        </is>
+      </c>
+      <c r="J116" s="16" t="n">
+        <v>6.750067677566146</v>
+      </c>
+      <c r="K116" s="16" t="n">
+        <v>1.24484361207655</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="20" t="inlineStr">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>수명 [yr] = 30/ΣD30 · Sys=와이블(e=9/8) — 부분합 기준</t>
         </is>
       </c>
-      <c r="L117" s="21" t="n">
-        <v>4.454412047056009</v>
-      </c>
-      <c r="M117" s="21" t="n">
-        <v>24.23353973121363</v>
-      </c>
-      <c r="N117" s="21" t="n">
-        <v>3.93786495573634</v>
+      <c r="L117" s="17" t="n">
+        <v>4.4443998835308</v>
+      </c>
+      <c r="M117" s="17" t="n">
+        <v>24.09941273663795</v>
+      </c>
+      <c r="N117" s="17" t="n">
+        <v>3.927332728696102</v>
       </c>
     </row>
   </sheetData>
